--- a/class_excel/data-files-optimization.xlsx
+++ b/class_excel/data-files-optimization.xlsx
@@ -8,46 +8,49 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABC8A3D-02B7-4B08-9C6A-7829A61217AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0839EA04-557A-4E5B-8347-B747B5C209D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="954" firstSheet="21" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="954" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sensitivity Report 1" sheetId="34" r:id="rId1"/>
-    <sheet name="ProductMix" sheetId="1" r:id="rId2"/>
-    <sheet name="ProductMix_add_on" sheetId="32" r:id="rId3"/>
-    <sheet name="ProductMix2 Sensitivity" sheetId="35" r:id="rId4"/>
-    <sheet name="ProductMix2" sheetId="2" r:id="rId5"/>
-    <sheet name="LM_2" sheetId="36" r:id="rId6"/>
-    <sheet name="Dual" sheetId="17" r:id="rId7"/>
-    <sheet name="ProdPlanning" sheetId="3" r:id="rId8"/>
-    <sheet name="project" sheetId="18" r:id="rId9"/>
-    <sheet name="BlendingOil" sheetId="4" r:id="rId10"/>
-    <sheet name="Transport1" sheetId="5" r:id="rId11"/>
-    <sheet name="AssignmentProblem" sheetId="20" r:id="rId12"/>
-    <sheet name="BinPacking" sheetId="27" r:id="rId13"/>
-    <sheet name="cuttingStock" sheetId="28" r:id="rId14"/>
-    <sheet name="MCNF" sheetId="31" r:id="rId15"/>
-    <sheet name="RedBrandLogistics" sheetId="6" r:id="rId16"/>
-    <sheet name="HW3" sheetId="37" r:id="rId17"/>
-    <sheet name="set_covering_model" sheetId="39" r:id="rId18"/>
-    <sheet name="ShortestPath" sheetId="26" r:id="rId19"/>
-    <sheet name="Aggregate1" sheetId="7" r:id="rId20"/>
-    <sheet name="CapitalBudget" sheetId="8" r:id="rId21"/>
-    <sheet name="FixedCost" sheetId="9" r:id="rId22"/>
-    <sheet name="Hub" sheetId="10" r:id="rId23"/>
-    <sheet name="WorkerScheduling" sheetId="11" r:id="rId24"/>
-    <sheet name="Transport1-2" sheetId="12" r:id="rId25"/>
-    <sheet name="MMULT" sheetId="13" r:id="rId26"/>
-    <sheet name="MDETERM" sheetId="21" r:id="rId27"/>
-    <sheet name="Peakload" sheetId="15" r:id="rId28"/>
-    <sheet name="GameTheory" sheetId="40" r:id="rId29"/>
-    <sheet name="Portfolio" sheetId="14" r:id="rId30"/>
-    <sheet name="EOQ" sheetId="23" r:id="rId31"/>
-    <sheet name="SVM1" sheetId="24" r:id="rId32"/>
-    <sheet name="MLE" sheetId="25" r:id="rId33"/>
-    <sheet name="OLS" sheetId="30" r:id="rId34"/>
-    <sheet name="Location" sheetId="29" r:id="rId35"/>
+    <sheet name="Advertising " sheetId="43" r:id="rId1"/>
+    <sheet name="Advertising _Sensitivity Report" sheetId="42" r:id="rId2"/>
+    <sheet name="monopolist" sheetId="41" r:id="rId3"/>
+    <sheet name="Sensitivity Report 1" sheetId="34" r:id="rId4"/>
+    <sheet name="ProductMix" sheetId="1" r:id="rId5"/>
+    <sheet name="ProductMix_add_on" sheetId="32" r:id="rId6"/>
+    <sheet name="ProductMix2 Sensitivity" sheetId="35" r:id="rId7"/>
+    <sheet name="ProductMix2" sheetId="2" r:id="rId8"/>
+    <sheet name="LM_2" sheetId="36" r:id="rId9"/>
+    <sheet name="Dual" sheetId="17" r:id="rId10"/>
+    <sheet name="ProdPlanning" sheetId="3" r:id="rId11"/>
+    <sheet name="project" sheetId="18" r:id="rId12"/>
+    <sheet name="BlendingOil" sheetId="4" r:id="rId13"/>
+    <sheet name="Transport1" sheetId="5" r:id="rId14"/>
+    <sheet name="AssignmentProblem" sheetId="20" r:id="rId15"/>
+    <sheet name="BinPacking" sheetId="27" r:id="rId16"/>
+    <sheet name="cuttingStock" sheetId="28" r:id="rId17"/>
+    <sheet name="MCNF" sheetId="31" r:id="rId18"/>
+    <sheet name="RedBrandLogistics" sheetId="6" r:id="rId19"/>
+    <sheet name="HW3" sheetId="37" r:id="rId20"/>
+    <sheet name="set_covering_model" sheetId="39" r:id="rId21"/>
+    <sheet name="ShortestPath" sheetId="26" r:id="rId22"/>
+    <sheet name="Aggregate1" sheetId="7" r:id="rId23"/>
+    <sheet name="CapitalBudget" sheetId="8" r:id="rId24"/>
+    <sheet name="FixedCost" sheetId="9" r:id="rId25"/>
+    <sheet name="Hub" sheetId="10" r:id="rId26"/>
+    <sheet name="WorkerScheduling" sheetId="11" r:id="rId27"/>
+    <sheet name="Transport1-2" sheetId="12" r:id="rId28"/>
+    <sheet name="MMULT" sheetId="13" r:id="rId29"/>
+    <sheet name="MDETERM" sheetId="21" r:id="rId30"/>
+    <sheet name="Peakload" sheetId="15" r:id="rId31"/>
+    <sheet name="GameTheory" sheetId="40" r:id="rId32"/>
+    <sheet name="Portfolio" sheetId="14" r:id="rId33"/>
+    <sheet name="EOQ" sheetId="23" r:id="rId34"/>
+    <sheet name="SVM1" sheetId="24" r:id="rId35"/>
+    <sheet name="MLE" sheetId="25" r:id="rId36"/>
+    <sheet name="OLS" sheetId="30" r:id="rId37"/>
+    <sheet name="Location" sheetId="29" r:id="rId38"/>
   </sheets>
   <definedNames>
     <definedName name="AFinish">project!$K$6</definedName>
@@ -79,808 +82,865 @@
     <definedName name="MStart">project!$I$18</definedName>
     <definedName name="NFinish">project!$K$19</definedName>
     <definedName name="NStart">project!$I$19</definedName>
-    <definedName name="solver_adj" localSheetId="11" hidden="1">AssignmentProblem!$C$13:$F$16</definedName>
-    <definedName name="solver_adj" localSheetId="20" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
-    <definedName name="solver_adj" localSheetId="6" hidden="1">Dual!$I$4:$L$4</definedName>
-    <definedName name="solver_adj" localSheetId="30" hidden="1">EOQ!$B$6</definedName>
-    <definedName name="solver_adj" localSheetId="21" hidden="1">FixedCost!$B$14:$F$15</definedName>
-    <definedName name="solver_adj" localSheetId="28" hidden="1">GameTheory!$B$2:$D$2</definedName>
-    <definedName name="solver_adj" localSheetId="22" hidden="1">Hub!$B$21:$M$21</definedName>
-    <definedName name="solver_adj" localSheetId="16" hidden="1">'HW3'!$E$5:$E$14</definedName>
-    <definedName name="solver_adj" localSheetId="5" hidden="1">LM_2!$B$10:$I$10</definedName>
-    <definedName name="solver_adj" localSheetId="34" hidden="1">Location!$B$6:$C$6</definedName>
-    <definedName name="solver_adj" localSheetId="14" hidden="1">MCNF!$D$8:$D$13</definedName>
-    <definedName name="solver_adj" localSheetId="27" hidden="1">Peakload!$B$13:$C$13,Peakload!$B$15</definedName>
-    <definedName name="solver_adj" localSheetId="7" hidden="1">ProdPlanning!$B$12:$G$12</definedName>
-    <definedName name="solver_adj" localSheetId="1" hidden="1">ProductMix!$B$16:$C$16</definedName>
-    <definedName name="solver_adj" localSheetId="2" hidden="1">ProductMix_add_on!$B$16:$D$16</definedName>
-    <definedName name="solver_adj" localSheetId="4" hidden="1">ProductMix2!$B$19:$I$20</definedName>
-    <definedName name="solver_adj" localSheetId="8" hidden="1">project!$I$6:$J$19,project!$I$22</definedName>
-    <definedName name="solver_adj" localSheetId="15" hidden="1">RedBrandLogistics!$D$8:$D$33</definedName>
-    <definedName name="solver_adj" localSheetId="17" hidden="1">set_covering_model!$B$2:$G$2</definedName>
-    <definedName name="solver_adj" localSheetId="31" hidden="1">'SVM1'!$B$2:$D$2,'SVM1'!$F$2</definedName>
-    <definedName name="solver_adj" localSheetId="10" hidden="1">Transport1!$C$13:$F$15</definedName>
-    <definedName name="solver_adj" localSheetId="23" hidden="1">WorkerScheduling!$N$3:$T$3</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">'Advertising '!$A$2:$B$2</definedName>
+    <definedName name="solver_adj" localSheetId="14" hidden="1">AssignmentProblem!$C$13:$F$16</definedName>
+    <definedName name="solver_adj" localSheetId="23" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
+    <definedName name="solver_adj" localSheetId="9" hidden="1">Dual!$I$4:$L$4</definedName>
+    <definedName name="solver_adj" localSheetId="33" hidden="1">EOQ!$B$6</definedName>
+    <definedName name="solver_adj" localSheetId="24" hidden="1">FixedCost!$B$14:$F$15</definedName>
+    <definedName name="solver_adj" localSheetId="31" hidden="1">GameTheory!$B$2:$D$2</definedName>
+    <definedName name="solver_adj" localSheetId="25" hidden="1">Hub!$B$21:$M$21</definedName>
+    <definedName name="solver_adj" localSheetId="19" hidden="1">'HW3'!$E$5:$E$14</definedName>
+    <definedName name="solver_adj" localSheetId="8" hidden="1">LM_2!$B$10:$I$10</definedName>
+    <definedName name="solver_adj" localSheetId="37" hidden="1">Location!$B$6:$C$6</definedName>
+    <definedName name="solver_adj" localSheetId="17" hidden="1">MCNF!$D$8:$D$13</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">monopolist!$A$2</definedName>
+    <definedName name="solver_adj" localSheetId="30" hidden="1">Peakload!$B$13:$C$13,Peakload!$B$15</definedName>
+    <definedName name="solver_adj" localSheetId="10" hidden="1">ProdPlanning!$B$12:$G$12</definedName>
+    <definedName name="solver_adj" localSheetId="4" hidden="1">ProductMix!$B$16:$C$16</definedName>
+    <definedName name="solver_adj" localSheetId="5" hidden="1">ProductMix_add_on!$B$16:$D$16</definedName>
+    <definedName name="solver_adj" localSheetId="7" hidden="1">ProductMix2!$B$19:$I$20</definedName>
+    <definedName name="solver_adj" localSheetId="11" hidden="1">project!$I$6:$J$19,project!$I$22</definedName>
+    <definedName name="solver_adj" localSheetId="18" hidden="1">RedBrandLogistics!$D$8:$D$33</definedName>
+    <definedName name="solver_adj" localSheetId="20" hidden="1">set_covering_model!$B$2:$G$2</definedName>
+    <definedName name="solver_adj" localSheetId="34" hidden="1">'SVM1'!$B$2:$D$2,'SVM1'!$F$2</definedName>
+    <definedName name="solver_adj" localSheetId="13" hidden="1">Transport1!$C$13:$F$15</definedName>
+    <definedName name="solver_adj" localSheetId="26" hidden="1">WorkerScheduling!$N$3:$T$3</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="14" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="23" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="9" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="33" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="24" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="31" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="25" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="19" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="8" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="37" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="17" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="30" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="10" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="4" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="5" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="7" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="11" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="18" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="20" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="6" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="30" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="21" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="28" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="22" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="16" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="5" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="34" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="14" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="27" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="7" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="4" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="8" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="15" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="17" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="10" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="23" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="13" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="26" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="24" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="31" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="25" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="19" hidden="1">2</definedName>
+    <definedName name="solver_drv" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="37" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="30" hidden="1">2</definedName>
+    <definedName name="solver_drv" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="18" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="20" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="30" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="21" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="28" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="22" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="16" hidden="1">2</definedName>
-    <definedName name="solver_drv" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="34" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="14" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="27" hidden="1">2</definedName>
-    <definedName name="solver_drv" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="8" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="15" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="17" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="10" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="13" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="26" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="23" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="9" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="24" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="31" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="25" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="19" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="37" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="17" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="30" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="7" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="11" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="18" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="20" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="30" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="21" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="28" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="22" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="16" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="34" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="14" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="27" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="7" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="4" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="8" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="15" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="17" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="31" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="10" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="23" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="13" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="26" hidden="1">2</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="24" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="31" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="25" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="19" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="37" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="30" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="18" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="20" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="30" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="21" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="28" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="22" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="16" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="34" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="14" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="27" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="8" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="15" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="17" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="10" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="13" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="26" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="14" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="23" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="9" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="33" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="24" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="31" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="25" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="19" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="37" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="17" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="30" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="10" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="4" hidden="1">100</definedName>
+    <definedName name="solver_itr" localSheetId="5" hidden="1">100</definedName>
+    <definedName name="solver_itr" localSheetId="7" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="11" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="18" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="20" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="6" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="30" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="21" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="28" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="22" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="16" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="5" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="34" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="14" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="27" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="7" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="1" hidden="1">100</definedName>
-    <definedName name="solver_itr" localSheetId="2" hidden="1">100</definedName>
-    <definedName name="solver_itr" localSheetId="4" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="8" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="15" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="17" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="10" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="23" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="11" hidden="1">AssignmentProblem!$C$17:$F$17</definedName>
-    <definedName name="solver_lhs1" localSheetId="20" hidden="1">CapitalBudget!$B$14</definedName>
-    <definedName name="solver_lhs1" localSheetId="6" hidden="1">Dual!$M$6:$M$7</definedName>
-    <definedName name="solver_lhs1" localSheetId="30" hidden="1">EOQ!$J$15</definedName>
-    <definedName name="solver_lhs1" localSheetId="21" hidden="1">FixedCost!$B$14:$F$14</definedName>
-    <definedName name="solver_lhs1" localSheetId="28" hidden="1">GameTheory!$B$2:$C$2</definedName>
-    <definedName name="solver_lhs1" localSheetId="22" hidden="1">Hub!$B$21:$M$21</definedName>
-    <definedName name="solver_lhs1" localSheetId="16" hidden="1">'HW3'!$L$14:$L$17</definedName>
-    <definedName name="solver_lhs1" localSheetId="5" hidden="1">LM_2!$J$12:$J$14</definedName>
-    <definedName name="solver_lhs1" localSheetId="14" hidden="1">MCNF!$D$8:$D$13</definedName>
-    <definedName name="solver_lhs1" localSheetId="27" hidden="1">Peakload!$B$19:$C$19</definedName>
-    <definedName name="solver_lhs1" localSheetId="7" hidden="1">ProdPlanning!$B$12:$G$12</definedName>
-    <definedName name="solver_lhs1" localSheetId="1" hidden="1">ProductMix!$B$16:$C$16</definedName>
-    <definedName name="solver_lhs1" localSheetId="2" hidden="1">ProductMix_add_on!$B$16:$D$16</definedName>
-    <definedName name="solver_lhs1" localSheetId="4" hidden="1">ProductMix2!$B$21:$I$21</definedName>
-    <definedName name="solver_lhs1" localSheetId="8" hidden="1">project!$I$22</definedName>
-    <definedName name="solver_lhs1" localSheetId="15" hidden="1">RedBrandLogistics!$D$8:$D$33</definedName>
-    <definedName name="solver_lhs1" localSheetId="17" hidden="1">set_covering_model!$B$2:$G$2</definedName>
-    <definedName name="solver_lhs1" localSheetId="10" hidden="1">Transport1!$C$16:$F$16</definedName>
-    <definedName name="solver_lhs1" localSheetId="23" hidden="1">WorkerScheduling!$N$3:$T$3</definedName>
-    <definedName name="solver_lhs10" localSheetId="8" hidden="1">project!$I$18</definedName>
-    <definedName name="solver_lhs11" localSheetId="8" hidden="1">project!$I$13</definedName>
-    <definedName name="solver_lhs12" localSheetId="8" hidden="1">project!$I$15</definedName>
-    <definedName name="solver_lhs13" localSheetId="8" hidden="1">project!$I$15</definedName>
-    <definedName name="solver_lhs14" localSheetId="8" hidden="1">project!$I$14</definedName>
-    <definedName name="solver_lhs15" localSheetId="8" hidden="1">project!$I$13</definedName>
-    <definedName name="solver_lhs16" localSheetId="8" hidden="1">project!$I$7</definedName>
-    <definedName name="solver_lhs17" localSheetId="8" hidden="1">project!$I$12</definedName>
-    <definedName name="solver_lhs18" localSheetId="8" hidden="1">project!$I$8</definedName>
-    <definedName name="solver_lhs19" localSheetId="8" hidden="1">project!$I$9</definedName>
-    <definedName name="solver_lhs2" localSheetId="11" hidden="1">AssignmentProblem!$G$13:$G$16</definedName>
-    <definedName name="solver_lhs2" localSheetId="20" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
-    <definedName name="solver_lhs2" localSheetId="21" hidden="1">FixedCost!$B$15:$F$15</definedName>
-    <definedName name="solver_lhs2" localSheetId="28" hidden="1">GameTheory!$E$4:$E$5</definedName>
-    <definedName name="solver_lhs2" localSheetId="22" hidden="1">Hub!$B$25:$B$36</definedName>
-    <definedName name="solver_lhs2" localSheetId="16" hidden="1">'HW3'!$L$5</definedName>
-    <definedName name="solver_lhs2" localSheetId="5" hidden="1">LM_2!$J$15</definedName>
-    <definedName name="solver_lhs2" localSheetId="14" hidden="1">MCNF!$L$9:$L$13</definedName>
-    <definedName name="solver_lhs2" localSheetId="7" hidden="1">ProdPlanning!$B$20:$G$20</definedName>
-    <definedName name="solver_lhs2" localSheetId="1" hidden="1">ProductMix!$B$21:$B$22</definedName>
-    <definedName name="solver_lhs2" localSheetId="2" hidden="1">ProductMix_add_on!$B$21:$B$22</definedName>
-    <definedName name="solver_lhs2" localSheetId="4" hidden="1">ProductMix2!$B$26:$B$28</definedName>
-    <definedName name="solver_lhs2" localSheetId="8" hidden="1">project!$I$22</definedName>
-    <definedName name="solver_lhs2" localSheetId="15" hidden="1">RedBrandLogistics!$K$15:$K$16</definedName>
-    <definedName name="solver_lhs2" localSheetId="17" hidden="1">set_covering_model!$H$3:$H$8</definedName>
-    <definedName name="solver_lhs2" localSheetId="10" hidden="1">Transport1!$G$13:$G$15</definedName>
-    <definedName name="solver_lhs2" localSheetId="23" hidden="1">WorkerScheduling!$U$5:$U$11</definedName>
-    <definedName name="solver_lhs20" localSheetId="8" hidden="1">project!$I$9</definedName>
-    <definedName name="solver_lhs21" localSheetId="8" hidden="1">project!$I$10</definedName>
-    <definedName name="solver_lhs22" localSheetId="8" hidden="1">project!$I$11</definedName>
-    <definedName name="solver_lhs3" localSheetId="20" hidden="1">CapitalBudget!$C$15</definedName>
-    <definedName name="solver_lhs3" localSheetId="21" hidden="1">FixedCost!$B$23:$B$24</definedName>
-    <definedName name="solver_lhs3" localSheetId="28" hidden="1">GameTheory!$E$6</definedName>
-    <definedName name="solver_lhs3" localSheetId="16" hidden="1">'HW3'!$E$5:$E$6</definedName>
-    <definedName name="solver_lhs3" localSheetId="5" hidden="1">LM_2!$J$15</definedName>
-    <definedName name="solver_lhs3" localSheetId="14" hidden="1">MCNF!$L$20:$L$21</definedName>
-    <definedName name="solver_lhs3" localSheetId="7" hidden="1">ProdPlanning!$B$20:$G$20</definedName>
-    <definedName name="solver_lhs3" localSheetId="1" hidden="1">ProductMix!$C$16</definedName>
-    <definedName name="solver_lhs3" localSheetId="2" hidden="1">ProductMix_add_on!$C$16</definedName>
-    <definedName name="solver_lhs3" localSheetId="4" hidden="1">ProductMix2!$B$26:$B$28</definedName>
-    <definedName name="solver_lhs3" localSheetId="8" hidden="1">project!$I$22</definedName>
-    <definedName name="solver_lhs3" localSheetId="15" hidden="1">RedBrandLogistics!$K$20:$K$21</definedName>
-    <definedName name="solver_lhs4" localSheetId="20" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
-    <definedName name="solver_lhs4" localSheetId="21" hidden="1">FixedCost!$B$23:$B$24</definedName>
-    <definedName name="solver_lhs4" localSheetId="28" hidden="1">GameTheory!$E$6</definedName>
-    <definedName name="solver_lhs4" localSheetId="16" hidden="1">'HW3'!$L$9:$L$10</definedName>
-    <definedName name="solver_lhs4" localSheetId="14" hidden="1">MCNF!$L$9:$L$11</definedName>
-    <definedName name="solver_lhs4" localSheetId="8" hidden="1">project!$I$22</definedName>
-    <definedName name="solver_lhs4" localSheetId="15" hidden="1">RedBrandLogistics!$K$9:$K$11</definedName>
-    <definedName name="solver_lhs5" localSheetId="20" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
-    <definedName name="solver_lhs5" localSheetId="8" hidden="1">project!$J$6:$J$19</definedName>
-    <definedName name="solver_lhs6" localSheetId="8" hidden="1">project!$I$19</definedName>
-    <definedName name="solver_lhs7" localSheetId="8" hidden="1">project!$I$19</definedName>
-    <definedName name="solver_lhs8" localSheetId="8" hidden="1">project!$I$16</definedName>
-    <definedName name="solver_lhs9" localSheetId="8" hidden="1">project!$I$17</definedName>
-    <definedName name="solver_lin" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_lin" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_itr" localSheetId="13" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="26" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Advertising '!$C$6</definedName>
+    <definedName name="solver_lhs1" localSheetId="14" hidden="1">AssignmentProblem!$C$17:$F$17</definedName>
+    <definedName name="solver_lhs1" localSheetId="23" hidden="1">CapitalBudget!$B$14</definedName>
+    <definedName name="solver_lhs1" localSheetId="9" hidden="1">Dual!$M$6:$M$7</definedName>
+    <definedName name="solver_lhs1" localSheetId="33" hidden="1">EOQ!$J$15</definedName>
+    <definedName name="solver_lhs1" localSheetId="24" hidden="1">FixedCost!$B$14:$F$14</definedName>
+    <definedName name="solver_lhs1" localSheetId="31" hidden="1">GameTheory!$B$2:$C$2</definedName>
+    <definedName name="solver_lhs1" localSheetId="25" hidden="1">Hub!$B$21:$M$21</definedName>
+    <definedName name="solver_lhs1" localSheetId="19" hidden="1">'HW3'!$L$14:$L$17</definedName>
+    <definedName name="solver_lhs1" localSheetId="8" hidden="1">LM_2!$J$12:$J$14</definedName>
+    <definedName name="solver_lhs1" localSheetId="17" hidden="1">MCNF!$D$8:$D$13</definedName>
+    <definedName name="solver_lhs1" localSheetId="30" hidden="1">Peakload!$B$19:$C$19</definedName>
+    <definedName name="solver_lhs1" localSheetId="10" hidden="1">ProdPlanning!$B$12:$G$12</definedName>
+    <definedName name="solver_lhs1" localSheetId="4" hidden="1">ProductMix!$B$16:$C$16</definedName>
+    <definedName name="solver_lhs1" localSheetId="5" hidden="1">ProductMix_add_on!$B$16:$D$16</definedName>
+    <definedName name="solver_lhs1" localSheetId="7" hidden="1">ProductMix2!$B$21:$I$21</definedName>
+    <definedName name="solver_lhs1" localSheetId="11" hidden="1">project!$I$22</definedName>
+    <definedName name="solver_lhs1" localSheetId="18" hidden="1">RedBrandLogistics!$D$8:$D$33</definedName>
+    <definedName name="solver_lhs1" localSheetId="20" hidden="1">set_covering_model!$B$2:$G$2</definedName>
+    <definedName name="solver_lhs1" localSheetId="13" hidden="1">Transport1!$C$16:$F$16</definedName>
+    <definedName name="solver_lhs1" localSheetId="26" hidden="1">WorkerScheduling!$N$3:$T$3</definedName>
+    <definedName name="solver_lhs10" localSheetId="11" hidden="1">project!$I$18</definedName>
+    <definedName name="solver_lhs11" localSheetId="11" hidden="1">project!$I$13</definedName>
+    <definedName name="solver_lhs12" localSheetId="11" hidden="1">project!$I$15</definedName>
+    <definedName name="solver_lhs13" localSheetId="11" hidden="1">project!$I$15</definedName>
+    <definedName name="solver_lhs14" localSheetId="11" hidden="1">project!$I$14</definedName>
+    <definedName name="solver_lhs15" localSheetId="11" hidden="1">project!$I$13</definedName>
+    <definedName name="solver_lhs16" localSheetId="11" hidden="1">project!$I$7</definedName>
+    <definedName name="solver_lhs17" localSheetId="11" hidden="1">project!$I$12</definedName>
+    <definedName name="solver_lhs18" localSheetId="11" hidden="1">project!$I$8</definedName>
+    <definedName name="solver_lhs19" localSheetId="11" hidden="1">project!$I$9</definedName>
+    <definedName name="solver_lhs2" localSheetId="14" hidden="1">AssignmentProblem!$G$13:$G$16</definedName>
+    <definedName name="solver_lhs2" localSheetId="23" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
+    <definedName name="solver_lhs2" localSheetId="24" hidden="1">FixedCost!$B$15:$F$15</definedName>
+    <definedName name="solver_lhs2" localSheetId="31" hidden="1">GameTheory!$E$4:$E$5</definedName>
+    <definedName name="solver_lhs2" localSheetId="25" hidden="1">Hub!$B$25:$B$36</definedName>
+    <definedName name="solver_lhs2" localSheetId="19" hidden="1">'HW3'!$L$5</definedName>
+    <definedName name="solver_lhs2" localSheetId="8" hidden="1">LM_2!$J$15</definedName>
+    <definedName name="solver_lhs2" localSheetId="17" hidden="1">MCNF!$L$9:$L$13</definedName>
+    <definedName name="solver_lhs2" localSheetId="10" hidden="1">ProdPlanning!$B$20:$G$20</definedName>
+    <definedName name="solver_lhs2" localSheetId="4" hidden="1">ProductMix!$B$21:$B$22</definedName>
+    <definedName name="solver_lhs2" localSheetId="5" hidden="1">ProductMix_add_on!$B$21:$B$22</definedName>
+    <definedName name="solver_lhs2" localSheetId="7" hidden="1">ProductMix2!$B$26:$B$28</definedName>
+    <definedName name="solver_lhs2" localSheetId="11" hidden="1">project!$I$22</definedName>
+    <definedName name="solver_lhs2" localSheetId="18" hidden="1">RedBrandLogistics!$K$15:$K$16</definedName>
+    <definedName name="solver_lhs2" localSheetId="20" hidden="1">set_covering_model!$H$3:$H$8</definedName>
+    <definedName name="solver_lhs2" localSheetId="13" hidden="1">Transport1!$G$13:$G$15</definedName>
+    <definedName name="solver_lhs2" localSheetId="26" hidden="1">WorkerScheduling!$U$5:$U$11</definedName>
+    <definedName name="solver_lhs20" localSheetId="11" hidden="1">project!$I$9</definedName>
+    <definedName name="solver_lhs21" localSheetId="11" hidden="1">project!$I$10</definedName>
+    <definedName name="solver_lhs22" localSheetId="11" hidden="1">project!$I$11</definedName>
+    <definedName name="solver_lhs3" localSheetId="23" hidden="1">CapitalBudget!$C$15</definedName>
+    <definedName name="solver_lhs3" localSheetId="24" hidden="1">FixedCost!$B$23:$B$24</definedName>
+    <definedName name="solver_lhs3" localSheetId="31" hidden="1">GameTheory!$E$6</definedName>
+    <definedName name="solver_lhs3" localSheetId="19" hidden="1">'HW3'!$E$5:$E$6</definedName>
+    <definedName name="solver_lhs3" localSheetId="8" hidden="1">LM_2!$J$15</definedName>
+    <definedName name="solver_lhs3" localSheetId="17" hidden="1">MCNF!$L$20:$L$21</definedName>
+    <definedName name="solver_lhs3" localSheetId="10" hidden="1">ProdPlanning!$B$20:$G$20</definedName>
+    <definedName name="solver_lhs3" localSheetId="4" hidden="1">ProductMix!$C$16</definedName>
+    <definedName name="solver_lhs3" localSheetId="5" hidden="1">ProductMix_add_on!$C$16</definedName>
+    <definedName name="solver_lhs3" localSheetId="7" hidden="1">ProductMix2!$B$26:$B$28</definedName>
+    <definedName name="solver_lhs3" localSheetId="11" hidden="1">project!$I$22</definedName>
+    <definedName name="solver_lhs3" localSheetId="18" hidden="1">RedBrandLogistics!$K$20:$K$21</definedName>
+    <definedName name="solver_lhs4" localSheetId="23" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
+    <definedName name="solver_lhs4" localSheetId="24" hidden="1">FixedCost!$B$23:$B$24</definedName>
+    <definedName name="solver_lhs4" localSheetId="31" hidden="1">GameTheory!$E$6</definedName>
+    <definedName name="solver_lhs4" localSheetId="19" hidden="1">'HW3'!$L$9:$L$10</definedName>
+    <definedName name="solver_lhs4" localSheetId="17" hidden="1">MCNF!$L$9:$L$11</definedName>
+    <definedName name="solver_lhs4" localSheetId="11" hidden="1">project!$I$22</definedName>
+    <definedName name="solver_lhs4" localSheetId="18" hidden="1">RedBrandLogistics!$K$9:$K$11</definedName>
+    <definedName name="solver_lhs5" localSheetId="23" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
+    <definedName name="solver_lhs5" localSheetId="11" hidden="1">project!$J$6:$J$19</definedName>
+    <definedName name="solver_lhs6" localSheetId="11" hidden="1">project!$I$19</definedName>
+    <definedName name="solver_lhs7" localSheetId="11" hidden="1">project!$I$19</definedName>
+    <definedName name="solver_lhs8" localSheetId="11" hidden="1">project!$I$16</definedName>
+    <definedName name="solver_lhs9" localSheetId="11" hidden="1">project!$I$17</definedName>
+    <definedName name="solver_lin" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_lin" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="14" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="23" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="9" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="33" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="24" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="31" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="25" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="19" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="37" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="17" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="30" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="10" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="7" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="11" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="18" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="20" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="6" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="30" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="21" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="28" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="22" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="16" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="5" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="34" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="14" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="27" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="7" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="4" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="8" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="15" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="17" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="10" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="23" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="13" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="26" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="14" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="23" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="9" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="33" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="24" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="31" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="25" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="19" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="8" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="37" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="17" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="30" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="10" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="4" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="5" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="7" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="11" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="18" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="20" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="6" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="30" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="21" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="28" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="22" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="16" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="5" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="34" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="14" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="27" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="7" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="4" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="8" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="15" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="17" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="10" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="23" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="13" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="26" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="14" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="23" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="9" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="33" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="24" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="31" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="25" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="19" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="8" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="37" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="17" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="30" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="10" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="4" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="5" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="7" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="11" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="18" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="20" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="6" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="30" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="21" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="28" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="22" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="16" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="5" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="34" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="14" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="27" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="7" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="4" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="8" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="15" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="17" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="10" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="23" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="13" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="26" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="23" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="9" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="33" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="24" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="31" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="25" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="19" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="37" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="17" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="30" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="7" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="11" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="18" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="20" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="30" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="21" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="28" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="22" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="16" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="34" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="14" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="27" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="7" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="4" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="8" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="15" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="17" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="10" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="23" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="13" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="26" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="24" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="31" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="25" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="19" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="37" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="30" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="18" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="20" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="30" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="21" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="28" hidden="1">2</definedName>
-    <definedName name="solver_neg" localSheetId="22" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="16" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="34" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="14" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="27" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="8" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="15" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="17" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="31" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="10" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="13" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="26" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="14" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="23" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="9" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="33" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="24" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="31" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="25" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="19" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="37" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="17" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="30" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="10" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="7" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="11" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="18" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="20" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="6" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="30" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="21" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="28" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="22" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="16" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="5" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="34" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="14" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="27" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="7" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="4" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="8" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="15" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="17" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="10" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="23" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="11" hidden="1">2</definedName>
+    <definedName name="solver_nod" localSheetId="13" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="26" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="23" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="33" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="24" hidden="1">3</definedName>
+    <definedName name="solver_num" localSheetId="31" hidden="1">3</definedName>
+    <definedName name="solver_num" localSheetId="25" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="19" hidden="1">4</definedName>
+    <definedName name="solver_num" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="37" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="17" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="30" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="10" hidden="1">3</definedName>
+    <definedName name="solver_num" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="7" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="11" hidden="1">22</definedName>
+    <definedName name="solver_num" localSheetId="18" hidden="1">4</definedName>
     <definedName name="solver_num" localSheetId="20" hidden="1">2</definedName>
-    <definedName name="solver_num" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_num" localSheetId="30" hidden="1">0</definedName>
-    <definedName name="solver_num" localSheetId="21" hidden="1">3</definedName>
-    <definedName name="solver_num" localSheetId="28" hidden="1">3</definedName>
-    <definedName name="solver_num" localSheetId="22" hidden="1">2</definedName>
-    <definedName name="solver_num" localSheetId="16" hidden="1">4</definedName>
-    <definedName name="solver_num" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="34" hidden="1">0</definedName>
-    <definedName name="solver_num" localSheetId="14" hidden="1">2</definedName>
-    <definedName name="solver_num" localSheetId="27" hidden="1">1</definedName>
-    <definedName name="solver_num" localSheetId="7" hidden="1">3</definedName>
-    <definedName name="solver_num" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
-    <definedName name="solver_num" localSheetId="4" hidden="1">2</definedName>
-    <definedName name="solver_num" localSheetId="8" hidden="1">22</definedName>
-    <definedName name="solver_num" localSheetId="15" hidden="1">4</definedName>
-    <definedName name="solver_num" localSheetId="17" hidden="1">2</definedName>
-    <definedName name="solver_num" localSheetId="31" hidden="1">0</definedName>
-    <definedName name="solver_num" localSheetId="10" hidden="1">2</definedName>
-    <definedName name="solver_num" localSheetId="23" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="13" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="26" hidden="1">2</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="24" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="31" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="25" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="19" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="37" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="30" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="18" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="20" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="30" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="21" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="28" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="22" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="16" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="34" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="14" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="27" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="8" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="15" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="17" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="10" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="23" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="11" hidden="1">AssignmentProblem!$B$22</definedName>
-    <definedName name="solver_opt" localSheetId="20" hidden="1">CapitalBudget!$B$17</definedName>
-    <definedName name="solver_opt" localSheetId="6" hidden="1">Dual!$M$5</definedName>
-    <definedName name="solver_opt" localSheetId="30" hidden="1">EOQ!$B$11</definedName>
-    <definedName name="solver_opt" localSheetId="21" hidden="1">FixedCost!$B$30</definedName>
-    <definedName name="solver_opt" localSheetId="28" hidden="1">GameTheory!$E$3</definedName>
-    <definedName name="solver_opt" localSheetId="22" hidden="1">Hub!$B$39</definedName>
-    <definedName name="solver_opt" localSheetId="16" hidden="1">'HW3'!$B$17</definedName>
-    <definedName name="solver_opt" localSheetId="5" hidden="1">LM_2!$K$11</definedName>
-    <definedName name="solver_opt" localSheetId="34" hidden="1">Location!$F$7</definedName>
-    <definedName name="solver_opt" localSheetId="14" hidden="1">MCNF!$B$17</definedName>
-    <definedName name="solver_opt" localSheetId="27" hidden="1">Peakload!$B$26</definedName>
-    <definedName name="solver_opt" localSheetId="7" hidden="1">ProdPlanning!$H$28</definedName>
-    <definedName name="solver_opt" localSheetId="1" hidden="1">ProductMix!$D$25</definedName>
-    <definedName name="solver_opt" localSheetId="2" hidden="1">ProductMix_add_on!$D$26</definedName>
-    <definedName name="solver_opt" localSheetId="4" hidden="1">ProductMix2!$J$33</definedName>
-    <definedName name="solver_opt" localSheetId="8" hidden="1">project!$I$24</definedName>
-    <definedName name="solver_opt" localSheetId="15" hidden="1">RedBrandLogistics!$B$36</definedName>
-    <definedName name="solver_opt" localSheetId="17" hidden="1">set_covering_model!$C$10</definedName>
-    <definedName name="solver_opt" localSheetId="31" hidden="1">'SVM1'!$F$2</definedName>
-    <definedName name="solver_opt" localSheetId="10" hidden="1">Transport1!$B$21</definedName>
-    <definedName name="solver_opt" localSheetId="23" hidden="1">WorkerScheduling!$U$4</definedName>
+    <definedName name="solver_nwt" localSheetId="13" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="26" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">'Advertising '!$C$2</definedName>
+    <definedName name="solver_opt" localSheetId="14" hidden="1">AssignmentProblem!$B$22</definedName>
+    <definedName name="solver_opt" localSheetId="23" hidden="1">CapitalBudget!$B$17</definedName>
+    <definedName name="solver_opt" localSheetId="9" hidden="1">Dual!$M$5</definedName>
+    <definedName name="solver_opt" localSheetId="33" hidden="1">EOQ!$B$11</definedName>
+    <definedName name="solver_opt" localSheetId="24" hidden="1">FixedCost!$B$30</definedName>
+    <definedName name="solver_opt" localSheetId="31" hidden="1">GameTheory!$E$3</definedName>
+    <definedName name="solver_opt" localSheetId="25" hidden="1">Hub!$B$39</definedName>
+    <definedName name="solver_opt" localSheetId="19" hidden="1">'HW3'!$B$17</definedName>
+    <definedName name="solver_opt" localSheetId="8" hidden="1">LM_2!$K$11</definedName>
+    <definedName name="solver_opt" localSheetId="37" hidden="1">Location!$F$7</definedName>
+    <definedName name="solver_opt" localSheetId="17" hidden="1">MCNF!$B$17</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">monopolist!$E$2</definedName>
+    <definedName name="solver_opt" localSheetId="30" hidden="1">Peakload!$B$26</definedName>
+    <definedName name="solver_opt" localSheetId="10" hidden="1">ProdPlanning!$H$28</definedName>
+    <definedName name="solver_opt" localSheetId="4" hidden="1">ProductMix!$D$25</definedName>
+    <definedName name="solver_opt" localSheetId="5" hidden="1">ProductMix_add_on!$D$26</definedName>
+    <definedName name="solver_opt" localSheetId="7" hidden="1">ProductMix2!$J$33</definedName>
+    <definedName name="solver_opt" localSheetId="11" hidden="1">project!$I$24</definedName>
+    <definedName name="solver_opt" localSheetId="18" hidden="1">RedBrandLogistics!$B$36</definedName>
+    <definedName name="solver_opt" localSheetId="20" hidden="1">set_covering_model!$C$10</definedName>
+    <definedName name="solver_opt" localSheetId="34" hidden="1">'SVM1'!$F$2</definedName>
+    <definedName name="solver_opt" localSheetId="13" hidden="1">Transport1!$B$21</definedName>
+    <definedName name="solver_opt" localSheetId="26" hidden="1">WorkerScheduling!$U$4</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="14" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="23" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="9" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="33" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="24" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="31" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="25" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="19" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="8" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="37" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="17" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="30" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="10" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="4" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="5" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="7" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="11" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="18" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="20" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="6" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="30" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="21" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="28" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="22" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="16" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="5" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="34" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="14" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="27" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="7" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="4" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="8" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="15" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="17" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="10" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="23" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="13" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="26" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="24" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="31" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="25" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="19" hidden="1">2</definedName>
+    <definedName name="solver_rbv" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="37" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="30" hidden="1">2</definedName>
+    <definedName name="solver_rbv" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="18" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="20" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="30" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="21" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="28" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="22" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="16" hidden="1">2</definedName>
-    <definedName name="solver_rbv" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="34" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="14" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="27" hidden="1">2</definedName>
-    <definedName name="solver_rbv" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="8" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="15" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="17" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="10" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="23" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="11" hidden="1">2</definedName>
-    <definedName name="solver_rel1" localSheetId="20" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="6" hidden="1">3</definedName>
+    <definedName name="solver_rbv" localSheetId="13" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="26" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="9" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="24" hidden="1">5</definedName>
+    <definedName name="solver_rel1" localSheetId="31" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="25" hidden="1">5</definedName>
+    <definedName name="solver_rel1" localSheetId="19" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="17" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="30" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="21" hidden="1">5</definedName>
-    <definedName name="solver_rel1" localSheetId="28" hidden="1">3</definedName>
-    <definedName name="solver_rel1" localSheetId="22" hidden="1">5</definedName>
-    <definedName name="solver_rel1" localSheetId="16" hidden="1">3</definedName>
-    <definedName name="solver_rel1" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_rel1" localSheetId="14" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="27" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel1" localSheetId="15" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="17" hidden="1">5</definedName>
-    <definedName name="solver_rel1" localSheetId="10" hidden="1">3</definedName>
-    <definedName name="solver_rel1" localSheetId="23" hidden="1">4</definedName>
-    <definedName name="solver_rel10" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel11" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel12" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel13" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel14" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel15" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel16" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel17" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel18" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel19" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel2" localSheetId="11" hidden="1">2</definedName>
-    <definedName name="solver_rel2" localSheetId="20" hidden="1">5</definedName>
-    <definedName name="solver_rel2" localSheetId="21" hidden="1">1</definedName>
-    <definedName name="solver_rel2" localSheetId="28" hidden="1">3</definedName>
-    <definedName name="solver_rel2" localSheetId="22" hidden="1">3</definedName>
-    <definedName name="solver_rel2" localSheetId="16" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="18" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="20" hidden="1">5</definedName>
+    <definedName name="solver_rel1" localSheetId="13" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="26" hidden="1">4</definedName>
+    <definedName name="solver_rel10" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel11" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel12" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel13" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel14" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel15" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel16" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel17" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel18" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel19" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="23" hidden="1">5</definedName>
+    <definedName name="solver_rel2" localSheetId="24" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="31" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="25" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="19" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="17" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_rel2" localSheetId="14" hidden="1">2</definedName>
     <definedName name="solver_rel2" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_rel2" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_rel2" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_rel2" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_rel2" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel2" localSheetId="15" hidden="1">2</definedName>
-    <definedName name="solver_rel2" localSheetId="17" hidden="1">3</definedName>
-    <definedName name="solver_rel2" localSheetId="10" hidden="1">1</definedName>
-    <definedName name="solver_rel2" localSheetId="23" hidden="1">3</definedName>
-    <definedName name="solver_rel20" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel21" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel22" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel3" localSheetId="20" hidden="1">1</definedName>
-    <definedName name="solver_rel3" localSheetId="21" hidden="1">1</definedName>
-    <definedName name="solver_rel3" localSheetId="28" hidden="1">2</definedName>
-    <definedName name="solver_rel3" localSheetId="16" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="18" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="20" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="13" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="26" hidden="1">3</definedName>
+    <definedName name="solver_rel20" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel21" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel22" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel3" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="24" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="31" hidden="1">2</definedName>
+    <definedName name="solver_rel3" localSheetId="19" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="17" hidden="1">3</definedName>
+    <definedName name="solver_rel3" localSheetId="10" hidden="1">3</definedName>
+    <definedName name="solver_rel3" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_rel3" localSheetId="14" hidden="1">3</definedName>
-    <definedName name="solver_rel3" localSheetId="7" hidden="1">3</definedName>
-    <definedName name="solver_rel3" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_rel3" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_rel3" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_rel3" localSheetId="8" hidden="1">2</definedName>
-    <definedName name="solver_rel3" localSheetId="15" hidden="1">3</definedName>
-    <definedName name="solver_rel4" localSheetId="20" hidden="1">1</definedName>
-    <definedName name="solver_rel4" localSheetId="21" hidden="1">1</definedName>
-    <definedName name="solver_rel4" localSheetId="28" hidden="1">3</definedName>
-    <definedName name="solver_rel4" localSheetId="16" hidden="1">2</definedName>
-    <definedName name="solver_rel4" localSheetId="14" hidden="1">1</definedName>
-    <definedName name="solver_rel4" localSheetId="8" hidden="1">1</definedName>
-    <definedName name="solver_rel4" localSheetId="15" hidden="1">1</definedName>
-    <definedName name="solver_rel5" localSheetId="20" hidden="1">5</definedName>
-    <definedName name="solver_rel5" localSheetId="8" hidden="1">1</definedName>
-    <definedName name="solver_rel6" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel7" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel8" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rel9" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_rhs1" localSheetId="11" hidden="1">1</definedName>
-    <definedName name="solver_rhs1" localSheetId="20" hidden="1">CapitalBudget!$D$14</definedName>
-    <definedName name="solver_rhs1" localSheetId="6" hidden="1">Dual!$O$6:$O$7</definedName>
-    <definedName name="solver_rhs1" localSheetId="30" hidden="1">EOQ!$L$15</definedName>
-    <definedName name="solver_rhs1" localSheetId="21" hidden="1">"binary"</definedName>
-    <definedName name="solver_rhs1" localSheetId="28" hidden="1">0</definedName>
-    <definedName name="solver_rhs1" localSheetId="22" hidden="1">binary</definedName>
-    <definedName name="solver_rhs1" localSheetId="16" hidden="1">'HW3'!$N$14:$N$17</definedName>
-    <definedName name="solver_rhs1" localSheetId="5" hidden="1">LM_2!$L$12:$L$14</definedName>
-    <definedName name="solver_rhs1" localSheetId="14" hidden="1">MCNF!$F$8:$F$13</definedName>
-    <definedName name="solver_rhs1" localSheetId="27" hidden="1">Peakload!$B$21:$C$21</definedName>
-    <definedName name="solver_rhs1" localSheetId="7" hidden="1">ProdPlanning!$B$14:$G$14</definedName>
-    <definedName name="solver_rhs1" localSheetId="1" hidden="1">ProductMix!$B$18:$C$18</definedName>
-    <definedName name="solver_rhs1" localSheetId="2" hidden="1">ProductMix_add_on!$B$18:$D$18</definedName>
-    <definedName name="solver_rhs1" localSheetId="4" hidden="1">ProductMix2!$B$23:$I$23</definedName>
-    <definedName name="solver_rhs1" localSheetId="8" hidden="1">NFinish</definedName>
-    <definedName name="solver_rhs1" localSheetId="15" hidden="1">RedBrandLogistics!$F$8:$F$33</definedName>
-    <definedName name="solver_rhs1" localSheetId="17" hidden="1">"binary"</definedName>
-    <definedName name="solver_rhs1" localSheetId="10" hidden="1">Transport1!$C$18:$F$18</definedName>
-    <definedName name="solver_rhs1" localSheetId="23" hidden="1">"integer"</definedName>
-    <definedName name="solver_rhs10" localSheetId="8" hidden="1">HFinish</definedName>
-    <definedName name="solver_rhs11" localSheetId="8" hidden="1">EFinish</definedName>
-    <definedName name="solver_rhs12" localSheetId="8" hidden="1">IFinish</definedName>
-    <definedName name="solver_rhs13" localSheetId="8" hidden="1">FFinish</definedName>
-    <definedName name="solver_rhs14" localSheetId="8" hidden="1">CFinish</definedName>
-    <definedName name="solver_rhs15" localSheetId="8" hidden="1">GFinish</definedName>
-    <definedName name="solver_rhs16" localSheetId="8" hidden="1">AFinish</definedName>
-    <definedName name="solver_rhs17" localSheetId="8" hidden="1">DFinish</definedName>
-    <definedName name="solver_rhs18" localSheetId="8" hidden="1">BFinish</definedName>
-    <definedName name="solver_rhs19" localSheetId="8" hidden="1">CFinish</definedName>
-    <definedName name="solver_rhs2" localSheetId="11" hidden="1">1</definedName>
-    <definedName name="solver_rhs2" localSheetId="20" hidden="1">"binary"</definedName>
-    <definedName name="solver_rhs2" localSheetId="21" hidden="1">FixedCost!$B$17:$F$17</definedName>
-    <definedName name="solver_rhs2" localSheetId="28" hidden="1">GameTheory!$G$4:$G$5</definedName>
-    <definedName name="solver_rhs2" localSheetId="22" hidden="1">Hub!$D$25:$D$36</definedName>
-    <definedName name="solver_rhs2" localSheetId="16" hidden="1">'HW3'!$N$5</definedName>
-    <definedName name="solver_rhs2" localSheetId="5" hidden="1">LM_2!$L$15</definedName>
-    <definedName name="solver_rhs2" localSheetId="14" hidden="1">MCNF!$N$9:$N$13</definedName>
-    <definedName name="solver_rhs2" localSheetId="7" hidden="1">ProdPlanning!$B$22:$G$22</definedName>
-    <definedName name="solver_rhs2" localSheetId="1" hidden="1">ProductMix!$D$21:$D$22</definedName>
-    <definedName name="solver_rhs2" localSheetId="2" hidden="1">ProductMix_add_on!$D$21:$D$22</definedName>
-    <definedName name="solver_rhs2" localSheetId="4" hidden="1">ProductMix2!$D$26:$D$28</definedName>
-    <definedName name="solver_rhs2" localSheetId="8" hidden="1">MFinish</definedName>
-    <definedName name="solver_rhs2" localSheetId="15" hidden="1">RedBrandLogistics!$M$15:$M$16</definedName>
-    <definedName name="solver_rhs2" localSheetId="17" hidden="1">set_covering_model!$J$3:$J$8</definedName>
-    <definedName name="solver_rhs2" localSheetId="10" hidden="1">Transport1!$I$13:$I$15</definedName>
-    <definedName name="solver_rhs2" localSheetId="23" hidden="1">WorkerScheduling!$W$5:$W$11</definedName>
-    <definedName name="solver_rhs20" localSheetId="8" hidden="1">CFinish</definedName>
-    <definedName name="solver_rhs21" localSheetId="8" hidden="1">CFinish</definedName>
-    <definedName name="solver_rhs22" localSheetId="8" hidden="1">EFinish</definedName>
-    <definedName name="solver_rhs3" localSheetId="20" hidden="1">0</definedName>
-    <definedName name="solver_rhs3" localSheetId="21" hidden="1">FixedCost!$D$23:$D$24</definedName>
-    <definedName name="solver_rhs3" localSheetId="28" hidden="1">1</definedName>
-    <definedName name="solver_rhs3" localSheetId="16" hidden="1">'HW3'!$G$5:$G$6</definedName>
-    <definedName name="solver_rhs3" localSheetId="5" hidden="1">LM_2!$L$15</definedName>
-    <definedName name="solver_rhs3" localSheetId="14" hidden="1">MCNF!$N$20:$N$21</definedName>
-    <definedName name="solver_rhs3" localSheetId="7" hidden="1">0</definedName>
-    <definedName name="solver_rhs3" localSheetId="1" hidden="1">ProductMix!$C$18</definedName>
-    <definedName name="solver_rhs3" localSheetId="2" hidden="1">ProductMix_add_on!$C$18</definedName>
-    <definedName name="solver_rhs3" localSheetId="4" hidden="1">ProductMix2!$D$26:$D$28</definedName>
-    <definedName name="solver_rhs3" localSheetId="8" hidden="1">NFinish</definedName>
-    <definedName name="solver_rhs3" localSheetId="15" hidden="1">RedBrandLogistics!$M$20:$M$21</definedName>
-    <definedName name="solver_rhs4" localSheetId="20" hidden="1">1</definedName>
-    <definedName name="solver_rhs4" localSheetId="21" hidden="1">FixedCost!$D$23:$D$24</definedName>
-    <definedName name="solver_rhs4" localSheetId="28" hidden="1">1</definedName>
-    <definedName name="solver_rhs4" localSheetId="16" hidden="1">'HW3'!$N$9:$N$10</definedName>
-    <definedName name="solver_rhs4" localSheetId="14" hidden="1">MCNF!$N$9:$N$11</definedName>
-    <definedName name="solver_rhs4" localSheetId="8" hidden="1">project!$K$22</definedName>
-    <definedName name="solver_rhs4" localSheetId="15" hidden="1">RedBrandLogistics!$M$9:$M$11</definedName>
-    <definedName name="solver_rhs5" localSheetId="20" hidden="1">binary</definedName>
-    <definedName name="solver_rhs5" localSheetId="8" hidden="1">project!$G$6:$G$19</definedName>
-    <definedName name="solver_rhs6" localSheetId="8" hidden="1">KFinish</definedName>
-    <definedName name="solver_rhs7" localSheetId="8" hidden="1">LFinish</definedName>
-    <definedName name="solver_rhs8" localSheetId="8" hidden="1">JFinish</definedName>
-    <definedName name="solver_rhs9" localSheetId="8" hidden="1">JFinish</definedName>
+    <definedName name="solver_rel3" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="11" hidden="1">2</definedName>
+    <definedName name="solver_rel3" localSheetId="18" hidden="1">3</definedName>
+    <definedName name="solver_rel4" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_rel4" localSheetId="24" hidden="1">1</definedName>
+    <definedName name="solver_rel4" localSheetId="31" hidden="1">3</definedName>
+    <definedName name="solver_rel4" localSheetId="19" hidden="1">2</definedName>
+    <definedName name="solver_rel4" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_rel4" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_rel4" localSheetId="18" hidden="1">1</definedName>
+    <definedName name="solver_rel5" localSheetId="23" hidden="1">5</definedName>
+    <definedName name="solver_rel5" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_rel6" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel7" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel8" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rel9" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">'Advertising '!$E$6</definedName>
+    <definedName name="solver_rhs1" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="23" hidden="1">CapitalBudget!$D$14</definedName>
+    <definedName name="solver_rhs1" localSheetId="9" hidden="1">Dual!$O$6:$O$7</definedName>
+    <definedName name="solver_rhs1" localSheetId="33" hidden="1">EOQ!$L$15</definedName>
+    <definedName name="solver_rhs1" localSheetId="24" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs1" localSheetId="31" hidden="1">0</definedName>
+    <definedName name="solver_rhs1" localSheetId="25" hidden="1">binary</definedName>
+    <definedName name="solver_rhs1" localSheetId="19" hidden="1">'HW3'!$N$14:$N$17</definedName>
+    <definedName name="solver_rhs1" localSheetId="8" hidden="1">LM_2!$L$12:$L$14</definedName>
+    <definedName name="solver_rhs1" localSheetId="17" hidden="1">MCNF!$F$8:$F$13</definedName>
+    <definedName name="solver_rhs1" localSheetId="30" hidden="1">Peakload!$B$21:$C$21</definedName>
+    <definedName name="solver_rhs1" localSheetId="10" hidden="1">ProdPlanning!$B$14:$G$14</definedName>
+    <definedName name="solver_rhs1" localSheetId="4" hidden="1">ProductMix!$B$18:$C$18</definedName>
+    <definedName name="solver_rhs1" localSheetId="5" hidden="1">ProductMix_add_on!$B$18:$D$18</definedName>
+    <definedName name="solver_rhs1" localSheetId="7" hidden="1">ProductMix2!$B$23:$I$23</definedName>
+    <definedName name="solver_rhs1" localSheetId="11" hidden="1">NFinish</definedName>
+    <definedName name="solver_rhs1" localSheetId="18" hidden="1">RedBrandLogistics!$F$8:$F$33</definedName>
+    <definedName name="solver_rhs1" localSheetId="20" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs1" localSheetId="13" hidden="1">Transport1!$C$18:$F$18</definedName>
+    <definedName name="solver_rhs1" localSheetId="26" hidden="1">"integer"</definedName>
+    <definedName name="solver_rhs10" localSheetId="11" hidden="1">HFinish</definedName>
+    <definedName name="solver_rhs11" localSheetId="11" hidden="1">EFinish</definedName>
+    <definedName name="solver_rhs12" localSheetId="11" hidden="1">IFinish</definedName>
+    <definedName name="solver_rhs13" localSheetId="11" hidden="1">FFinish</definedName>
+    <definedName name="solver_rhs14" localSheetId="11" hidden="1">CFinish</definedName>
+    <definedName name="solver_rhs15" localSheetId="11" hidden="1">GFinish</definedName>
+    <definedName name="solver_rhs16" localSheetId="11" hidden="1">AFinish</definedName>
+    <definedName name="solver_rhs17" localSheetId="11" hidden="1">DFinish</definedName>
+    <definedName name="solver_rhs18" localSheetId="11" hidden="1">BFinish</definedName>
+    <definedName name="solver_rhs19" localSheetId="11" hidden="1">CFinish</definedName>
+    <definedName name="solver_rhs2" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_rhs2" localSheetId="23" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs2" localSheetId="24" hidden="1">FixedCost!$B$17:$F$17</definedName>
+    <definedName name="solver_rhs2" localSheetId="31" hidden="1">GameTheory!$G$4:$G$5</definedName>
+    <definedName name="solver_rhs2" localSheetId="25" hidden="1">Hub!$D$25:$D$36</definedName>
+    <definedName name="solver_rhs2" localSheetId="19" hidden="1">'HW3'!$N$5</definedName>
+    <definedName name="solver_rhs2" localSheetId="8" hidden="1">LM_2!$L$15</definedName>
+    <definedName name="solver_rhs2" localSheetId="17" hidden="1">MCNF!$N$9:$N$13</definedName>
+    <definedName name="solver_rhs2" localSheetId="10" hidden="1">ProdPlanning!$B$22:$G$22</definedName>
+    <definedName name="solver_rhs2" localSheetId="4" hidden="1">ProductMix!$D$21:$D$22</definedName>
+    <definedName name="solver_rhs2" localSheetId="5" hidden="1">ProductMix_add_on!$D$21:$D$22</definedName>
+    <definedName name="solver_rhs2" localSheetId="7" hidden="1">ProductMix2!$D$26:$D$28</definedName>
+    <definedName name="solver_rhs2" localSheetId="11" hidden="1">MFinish</definedName>
+    <definedName name="solver_rhs2" localSheetId="18" hidden="1">RedBrandLogistics!$M$15:$M$16</definedName>
+    <definedName name="solver_rhs2" localSheetId="20" hidden="1">set_covering_model!$J$3:$J$8</definedName>
+    <definedName name="solver_rhs2" localSheetId="13" hidden="1">Transport1!$I$13:$I$15</definedName>
+    <definedName name="solver_rhs2" localSheetId="26" hidden="1">WorkerScheduling!$W$5:$W$11</definedName>
+    <definedName name="solver_rhs20" localSheetId="11" hidden="1">CFinish</definedName>
+    <definedName name="solver_rhs21" localSheetId="11" hidden="1">CFinish</definedName>
+    <definedName name="solver_rhs22" localSheetId="11" hidden="1">EFinish</definedName>
+    <definedName name="solver_rhs3" localSheetId="23" hidden="1">0</definedName>
+    <definedName name="solver_rhs3" localSheetId="24" hidden="1">FixedCost!$D$23:$D$24</definedName>
+    <definedName name="solver_rhs3" localSheetId="31" hidden="1">1</definedName>
+    <definedName name="solver_rhs3" localSheetId="19" hidden="1">'HW3'!$G$5:$G$6</definedName>
+    <definedName name="solver_rhs3" localSheetId="8" hidden="1">LM_2!$L$15</definedName>
+    <definedName name="solver_rhs3" localSheetId="17" hidden="1">MCNF!$N$20:$N$21</definedName>
+    <definedName name="solver_rhs3" localSheetId="10" hidden="1">0</definedName>
+    <definedName name="solver_rhs3" localSheetId="4" hidden="1">ProductMix!$C$18</definedName>
+    <definedName name="solver_rhs3" localSheetId="5" hidden="1">ProductMix_add_on!$C$18</definedName>
+    <definedName name="solver_rhs3" localSheetId="7" hidden="1">ProductMix2!$D$26:$D$28</definedName>
+    <definedName name="solver_rhs3" localSheetId="11" hidden="1">NFinish</definedName>
+    <definedName name="solver_rhs3" localSheetId="18" hidden="1">RedBrandLogistics!$M$20:$M$21</definedName>
+    <definedName name="solver_rhs4" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_rhs4" localSheetId="24" hidden="1">FixedCost!$D$23:$D$24</definedName>
+    <definedName name="solver_rhs4" localSheetId="31" hidden="1">1</definedName>
+    <definedName name="solver_rhs4" localSheetId="19" hidden="1">'HW3'!$N$9:$N$10</definedName>
+    <definedName name="solver_rhs4" localSheetId="17" hidden="1">MCNF!$N$9:$N$11</definedName>
+    <definedName name="solver_rhs4" localSheetId="11" hidden="1">project!$K$22</definedName>
+    <definedName name="solver_rhs4" localSheetId="18" hidden="1">RedBrandLogistics!$M$9:$M$11</definedName>
+    <definedName name="solver_rhs5" localSheetId="23" hidden="1">binary</definedName>
+    <definedName name="solver_rhs5" localSheetId="11" hidden="1">project!$G$6:$G$19</definedName>
+    <definedName name="solver_rhs6" localSheetId="11" hidden="1">KFinish</definedName>
+    <definedName name="solver_rhs7" localSheetId="11" hidden="1">LFinish</definedName>
+    <definedName name="solver_rhs8" localSheetId="11" hidden="1">JFinish</definedName>
+    <definedName name="solver_rhs9" localSheetId="11" hidden="1">JFinish</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="23" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="9" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="33" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="24" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="31" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="25" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="19" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="37" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="17" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="30" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_rlx" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_rlx" localSheetId="7" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="11" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="18" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="20" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="30" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="21" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="28" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="22" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="16" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="34" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="14" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="27" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="7" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_rlx" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_rlx" localSheetId="4" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="8" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="15" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="17" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="10" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="23" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="13" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="26" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="14" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="23" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="9" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="33" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="24" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="31" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="25" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="19" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="8" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="37" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="17" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="30" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="10" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="4" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="5" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="7" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="11" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="18" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="20" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="6" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="30" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="21" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="28" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="22" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="16" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="5" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="34" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="14" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="27" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="7" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="4" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="8" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="15" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="17" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="10" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="23" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="13" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="26" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="24" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="31" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="25" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="19" hidden="1">2</definedName>
+    <definedName name="solver_scl" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="37" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="30" hidden="1">2</definedName>
+    <definedName name="solver_scl" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_scl" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_scl" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="18" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="20" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="30" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="21" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="28" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="22" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="16" hidden="1">2</definedName>
-    <definedName name="solver_scl" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="34" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="14" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="27" hidden="1">2</definedName>
-    <definedName name="solver_scl" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_scl" localSheetId="2" hidden="1">2</definedName>
-    <definedName name="solver_scl" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="8" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="15" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="17" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="10" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="13" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="26" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="23" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="9" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="33" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="24" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="31" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="25" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="19" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="37" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="17" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="30" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="7" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="11" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="18" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="20" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="30" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="21" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="28" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="22" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="16" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="34" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="14" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="27" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="7" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="4" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="8" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="15" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="17" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="10" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="23" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="13" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="26" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="14" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="23" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="9" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="33" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="24" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="31" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="25" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="19" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="8" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="37" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="17" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="30" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="10" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="4" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="5" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="7" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="11" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="18" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="20" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="6" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="30" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="21" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="28" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="22" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="16" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="5" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="34" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="14" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="27" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="7" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="4" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="8" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="15" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="17" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="10" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="23" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="13" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="26" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="14" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="23" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="9" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="33" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="24" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="31" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="25" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="19" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="37" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="17" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="30" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="10" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="4" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="5" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="7" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="11" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="18" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="20" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="6" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="30" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="21" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="28" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="22" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="16" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="5" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="34" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="14" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="27" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="7" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="1" hidden="1">100</definedName>
-    <definedName name="solver_tim" localSheetId="2" hidden="1">100</definedName>
-    <definedName name="solver_tim" localSheetId="4" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="8" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="15" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="17" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="10" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="23" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="13" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="26" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="14" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="23" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="9" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="33" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="24" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="31" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="25" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="19" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="8" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="37" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="17" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="30" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="10" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="4" hidden="1">0.05</definedName>
+    <definedName name="solver_tol" localSheetId="5" hidden="1">0.05</definedName>
+    <definedName name="solver_tol" localSheetId="7" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="11" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="18" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="20" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="6" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="30" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="21" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="28" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="22" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="16" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="5" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="34" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="14" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="27" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="7" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="1" hidden="1">0.05</definedName>
-    <definedName name="solver_tol" localSheetId="2" hidden="1">0.05</definedName>
-    <definedName name="solver_tol" localSheetId="4" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="8" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="15" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="17" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="10" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="23" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="13" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="26" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="23" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="9" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="33" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="24" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="31" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="25" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="19" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="37" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="17" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="30" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="11" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="20" hidden="1">1</definedName>
-    <definedName name="solver_typ" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="30" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="21" hidden="1">1</definedName>
-    <definedName name="solver_typ" localSheetId="28" hidden="1">1</definedName>
-    <definedName name="solver_typ" localSheetId="22" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="16" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="34" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="14" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="27" hidden="1">1</definedName>
-    <definedName name="solver_typ" localSheetId="7" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_typ" localSheetId="4" hidden="1">1</definedName>
-    <definedName name="solver_typ" localSheetId="8" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="15" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="17" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="31" hidden="1">1</definedName>
-    <definedName name="solver_typ" localSheetId="10" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="23" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="18" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="20" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="34" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="13" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="26" hidden="1">2</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="14" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="23" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="9" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="33" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="24" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="31" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="25" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="19" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="8" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="37" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="17" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="30" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="10" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="4" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="5" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="7" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="11" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="18" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="20" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="6" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="30" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="21" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="28" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="22" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="16" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="5" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="34" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="14" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="27" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="7" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="4" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="8" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="15" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="17" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="31" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="10" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="23" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="13" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="26" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="14" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="23" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="9" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="33" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="24" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="31" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="25" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="19" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="8" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="37" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="17" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="30" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="10" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="4" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="5" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="7" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="18" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="20" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="6" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="30" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="21" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="28" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="22" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="16" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="5" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="34" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="14" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="27" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="7" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="4" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="8" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="15" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="17" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="31" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="10" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="23" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="13" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="26" hidden="1">3</definedName>
     <definedName name="yFinish">project!$I$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -989,7 +1049,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="621">
   <si>
     <t>Assembling and testing computers</t>
   </si>
@@ -3090,6 +3150,51 @@
   <si>
     <t>Con3</t>
   </si>
+  <si>
+    <t>profit</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revenue </t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>x (qty)</t>
+  </si>
+  <si>
+    <t>$B$6</t>
+  </si>
+  <si>
+    <t>Multiplier</t>
+  </si>
+  <si>
+    <t>Lagrange</t>
+  </si>
+  <si>
+    <t>$B$2</t>
+  </si>
+  <si>
+    <t>$A$2</t>
+  </si>
+  <si>
+    <t>Gradient</t>
+  </si>
+  <si>
+    <t>Report Created: 12/9/2569 11:20:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worksheet: [monopolist.xlsx]Advertising </t>
+  </si>
+  <si>
+    <t>budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f(x) revenue </t>
+  </si>
 </sst>
 </file>
 
@@ -3114,12 +3219,20 @@
     <numFmt numFmtId="202" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="203" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="222"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3320,8 +3433,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="18"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="222"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3385,6 +3507,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3618,22 +3746,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="190" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="191" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="192" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="191" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="192" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3648,81 +3777,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="190" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="196" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="195" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="190" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="196" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="193" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="193" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="197" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="187" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="197" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="187" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="197" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="197" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="197" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="197" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="197" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="197" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -3730,27 +3859,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="190" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="198" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="190" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="198" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="199" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -3760,49 +3889,49 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="5"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="5"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="192" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1"/>
     <xf numFmtId="192" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="198" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="198" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="201" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="197" fontId="4" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="201" fontId="4" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="192" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="192" fontId="4" fillId="8" borderId="11" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="197" fontId="5" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="201" fontId="5" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="192" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="192" fontId="5" fillId="8" borderId="11" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="2"/>
     </xf>
@@ -3815,36 +3944,48 @@
       <alignment horizontal="left" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="191" fontId="0" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="202" fontId="0" fillId="6" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="203" fontId="4" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="190" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="4" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="190" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="189" fontId="5" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="8" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="8" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="8" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="8" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="8" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="8">
+  <cellStyles count="9">
     <cellStyle name="Comma" xfId="6" builtinId="3"/>
     <cellStyle name="Currency" xfId="4" builtinId="4"/>
     <cellStyle name="Currency 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -3852,6 +3993,7 @@
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 3" xfId="8" xr:uid="{DED1A930-E856-4B42-8A68-9187EAEBCC94}"/>
     <cellStyle name="Percent" xfId="7" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5413,218 +5555,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5094E085-F6DB-4A3E-8201-010CC9E37480}">
-  <dimension ref="A1:H16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C0A51BD-032D-4C79-B55A-18F6864F9BF0}">
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="2.3125" customWidth="1"/>
-    <col min="2" max="2" width="6.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.6875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="16384" width="9" style="134"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="13.9" thickBot="1">
-      <c r="A6" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="B7" s="99"/>
-      <c r="C7" s="99"/>
-      <c r="D7" s="99" t="s">
-        <v>480</v>
-      </c>
-      <c r="E7" s="99" t="s">
-        <v>482</v>
-      </c>
-      <c r="F7" s="99" t="s">
-        <v>483</v>
-      </c>
-      <c r="G7" s="99" t="s">
-        <v>485</v>
-      </c>
-      <c r="H7" s="99" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="13.9" thickBot="1">
-      <c r="B8" s="100" t="s">
-        <v>478</v>
-      </c>
-      <c r="C8" s="100" t="s">
-        <v>479</v>
-      </c>
-      <c r="D8" s="100" t="s">
-        <v>481</v>
-      </c>
-      <c r="E8" s="100" t="s">
-        <v>294</v>
-      </c>
-      <c r="F8" s="100" t="s">
-        <v>484</v>
-      </c>
-      <c r="G8" s="100" t="s">
-        <v>486</v>
-      </c>
-      <c r="H8" s="100" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="B9" s="97" t="s">
-        <v>493</v>
-      </c>
-      <c r="C9" s="97" t="s">
-        <v>494</v>
-      </c>
-      <c r="D9" s="97">
-        <v>560</v>
-      </c>
-      <c r="E9" s="97">
-        <v>0</v>
-      </c>
-      <c r="F9" s="97">
-        <v>80</v>
-      </c>
-      <c r="G9" s="97">
-        <v>27.499999999999986</v>
-      </c>
-      <c r="H9" s="97">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="13.9" thickBot="1">
-      <c r="B10" s="98" t="s">
-        <v>495</v>
-      </c>
-      <c r="C10" s="98" t="s">
-        <v>496</v>
-      </c>
-      <c r="D10" s="98">
-        <v>1200</v>
-      </c>
-      <c r="E10" s="98">
-        <v>32.999999999999986</v>
-      </c>
-      <c r="F10" s="98">
-        <v>129</v>
-      </c>
-      <c r="G10" s="98">
-        <v>1E+30</v>
-      </c>
-      <c r="H10" s="98">
-        <v>32.999999999999986</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="13.9" thickBot="1">
-      <c r="A12" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="B13" s="99"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99" t="s">
-        <v>480</v>
-      </c>
-      <c r="E13" s="99" t="s">
-        <v>489</v>
-      </c>
-      <c r="F13" s="99" t="s">
-        <v>491</v>
-      </c>
-      <c r="G13" s="99" t="s">
-        <v>485</v>
-      </c>
-      <c r="H13" s="99" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="13.9" thickBot="1">
-      <c r="B14" s="100" t="s">
-        <v>478</v>
-      </c>
-      <c r="C14" s="100" t="s">
-        <v>479</v>
-      </c>
-      <c r="D14" s="100" t="s">
-        <v>481</v>
-      </c>
-      <c r="E14" s="100" t="s">
-        <v>490</v>
-      </c>
-      <c r="F14" s="100" t="s">
-        <v>492</v>
-      </c>
-      <c r="G14" s="100" t="s">
-        <v>486</v>
-      </c>
-      <c r="H14" s="100" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="B15" s="97" t="s">
-        <v>497</v>
-      </c>
-      <c r="C15" s="97" t="s">
-        <v>498</v>
-      </c>
-      <c r="D15" s="97">
-        <v>10000</v>
-      </c>
-      <c r="E15" s="97">
-        <v>16</v>
-      </c>
-      <c r="F15" s="97">
-        <v>10000</v>
-      </c>
-      <c r="G15" s="97">
-        <v>200</v>
-      </c>
-      <c r="H15" s="97">
-        <v>2800</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="13.9" thickBot="1">
-      <c r="B16" s="98" t="s">
-        <v>499</v>
-      </c>
-      <c r="C16" s="98" t="s">
-        <v>500</v>
-      </c>
-      <c r="D16" s="98">
-        <v>2960</v>
-      </c>
-      <c r="E16" s="98">
-        <v>0</v>
-      </c>
-      <c r="F16" s="98">
-        <v>3000</v>
-      </c>
-      <c r="G16" s="98">
-        <v>1E+30</v>
-      </c>
-      <c r="H16" s="98">
-        <v>40</v>
+    <row r="1" spans="1:5">
+      <c r="A1" s="134" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="134" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1" s="134" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="135">
+        <v>2.4642857142857153</v>
+      </c>
+      <c r="B2" s="135">
+        <v>2.6071428571428554</v>
+      </c>
+      <c r="C2" s="142">
+        <f>(-2*A2^2) - (B2^2) + (A2*B2) + (8*A2) + (3*B2)</f>
+        <v>15.017857142857146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="134" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="134">
+        <v>3</v>
+      </c>
+      <c r="B6" s="134">
+        <v>1</v>
+      </c>
+      <c r="C6" s="134">
+        <f>SUMPRODUCT(A6:B6,A2:B2)</f>
+        <v>10.000000000000002</v>
+      </c>
+      <c r="D6" s="134" t="s">
+        <v>278</v>
+      </c>
+      <c r="E6" s="141">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5633,6 +5614,1764 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="15.4375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="B3" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B4">
+        <v>560</v>
+      </c>
+      <c r="C4">
+        <v>1200</v>
+      </c>
+      <c r="H4" t="s">
+        <v>308</v>
+      </c>
+      <c r="I4">
+        <v>16</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B5">
+        <v>80</v>
+      </c>
+      <c r="C5">
+        <v>129</v>
+      </c>
+      <c r="D5">
+        <f>SUMPRODUCT($B$4:$C$4,B5:C5)</f>
+        <v>199600</v>
+      </c>
+      <c r="H5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I5">
+        <f t="array" ref="I5:L5">TRANSPOSE(F6:F9)</f>
+        <v>10000</v>
+      </c>
+      <c r="J5">
+        <v>3000</v>
+      </c>
+      <c r="K5">
+        <v>600</v>
+      </c>
+      <c r="L5">
+        <v>1200</v>
+      </c>
+      <c r="M5">
+        <f>SUMPRODUCT($I$4:$L$4,I5:L5)</f>
+        <v>199600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ref="D6:D9" si="0">SUMPRODUCT($B$4:$C$4,B6:C6)</f>
+        <v>10000</v>
+      </c>
+      <c r="E6" s="73" t="s">
+        <v>278</v>
+      </c>
+      <c r="F6">
+        <v>10000</v>
+      </c>
+      <c r="H6" t="s">
+        <v>298</v>
+      </c>
+      <c r="I6">
+        <f t="array" ref="I6:L7">TRANSPOSE(B6:C9)</f>
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f>SUMPRODUCT($I$4:$L$4,I6:L6)</f>
+        <v>80</v>
+      </c>
+      <c r="N6" s="73" t="s">
+        <v>220</v>
+      </c>
+      <c r="O6">
+        <f t="array" ref="O6:O7">TRANSPOSE(B5:C5)</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>2960</v>
+      </c>
+      <c r="E7" s="73" t="s">
+        <v>278</v>
+      </c>
+      <c r="F7">
+        <v>3000</v>
+      </c>
+      <c r="H7" t="s">
+        <v>299</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <f>SUMPRODUCT($I$4:$L$4,I7:L7)</f>
+        <v>129</v>
+      </c>
+      <c r="N7" s="73" t="s">
+        <v>220</v>
+      </c>
+      <c r="O7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>560</v>
+      </c>
+      <c r="E8" s="73" t="s">
+        <v>278</v>
+      </c>
+      <c r="F8">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="E9" s="73" t="s">
+        <v>278</v>
+      </c>
+      <c r="F9">
+        <v>1200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="28.5625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="11" customWidth="1"/>
+    <col min="3" max="7" width="9.125" style="11"/>
+    <col min="8" max="8" width="12.875" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="243" width="9.125" style="11"/>
+    <col min="244" max="244" width="26.5625" style="11" customWidth="1"/>
+    <col min="245" max="245" width="13.125" style="11" customWidth="1"/>
+    <col min="246" max="250" width="9.125" style="11"/>
+    <col min="251" max="251" width="10.875" style="11" customWidth="1"/>
+    <col min="252" max="252" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="253" max="253" width="10.5625" style="11" customWidth="1"/>
+    <col min="254" max="254" width="10.875" style="11" customWidth="1"/>
+    <col min="255" max="499" width="9.125" style="11"/>
+    <col min="500" max="500" width="26.5625" style="11" customWidth="1"/>
+    <col min="501" max="501" width="13.125" style="11" customWidth="1"/>
+    <col min="502" max="506" width="9.125" style="11"/>
+    <col min="507" max="507" width="10.875" style="11" customWidth="1"/>
+    <col min="508" max="508" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="509" max="509" width="10.5625" style="11" customWidth="1"/>
+    <col min="510" max="510" width="10.875" style="11" customWidth="1"/>
+    <col min="511" max="755" width="9.125" style="11"/>
+    <col min="756" max="756" width="26.5625" style="11" customWidth="1"/>
+    <col min="757" max="757" width="13.125" style="11" customWidth="1"/>
+    <col min="758" max="762" width="9.125" style="11"/>
+    <col min="763" max="763" width="10.875" style="11" customWidth="1"/>
+    <col min="764" max="764" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="765" max="765" width="10.5625" style="11" customWidth="1"/>
+    <col min="766" max="766" width="10.875" style="11" customWidth="1"/>
+    <col min="767" max="1011" width="9.125" style="11"/>
+    <col min="1012" max="1012" width="26.5625" style="11" customWidth="1"/>
+    <col min="1013" max="1013" width="13.125" style="11" customWidth="1"/>
+    <col min="1014" max="1018" width="9.125" style="11"/>
+    <col min="1019" max="1019" width="10.875" style="11" customWidth="1"/>
+    <col min="1020" max="1020" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="1021" max="1021" width="10.5625" style="11" customWidth="1"/>
+    <col min="1022" max="1022" width="10.875" style="11" customWidth="1"/>
+    <col min="1023" max="1267" width="9.125" style="11"/>
+    <col min="1268" max="1268" width="26.5625" style="11" customWidth="1"/>
+    <col min="1269" max="1269" width="13.125" style="11" customWidth="1"/>
+    <col min="1270" max="1274" width="9.125" style="11"/>
+    <col min="1275" max="1275" width="10.875" style="11" customWidth="1"/>
+    <col min="1276" max="1276" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="1277" max="1277" width="10.5625" style="11" customWidth="1"/>
+    <col min="1278" max="1278" width="10.875" style="11" customWidth="1"/>
+    <col min="1279" max="1523" width="9.125" style="11"/>
+    <col min="1524" max="1524" width="26.5625" style="11" customWidth="1"/>
+    <col min="1525" max="1525" width="13.125" style="11" customWidth="1"/>
+    <col min="1526" max="1530" width="9.125" style="11"/>
+    <col min="1531" max="1531" width="10.875" style="11" customWidth="1"/>
+    <col min="1532" max="1532" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="1533" max="1533" width="10.5625" style="11" customWidth="1"/>
+    <col min="1534" max="1534" width="10.875" style="11" customWidth="1"/>
+    <col min="1535" max="1779" width="9.125" style="11"/>
+    <col min="1780" max="1780" width="26.5625" style="11" customWidth="1"/>
+    <col min="1781" max="1781" width="13.125" style="11" customWidth="1"/>
+    <col min="1782" max="1786" width="9.125" style="11"/>
+    <col min="1787" max="1787" width="10.875" style="11" customWidth="1"/>
+    <col min="1788" max="1788" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="1789" max="1789" width="10.5625" style="11" customWidth="1"/>
+    <col min="1790" max="1790" width="10.875" style="11" customWidth="1"/>
+    <col min="1791" max="2035" width="9.125" style="11"/>
+    <col min="2036" max="2036" width="26.5625" style="11" customWidth="1"/>
+    <col min="2037" max="2037" width="13.125" style="11" customWidth="1"/>
+    <col min="2038" max="2042" width="9.125" style="11"/>
+    <col min="2043" max="2043" width="10.875" style="11" customWidth="1"/>
+    <col min="2044" max="2044" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="2045" max="2045" width="10.5625" style="11" customWidth="1"/>
+    <col min="2046" max="2046" width="10.875" style="11" customWidth="1"/>
+    <col min="2047" max="2291" width="9.125" style="11"/>
+    <col min="2292" max="2292" width="26.5625" style="11" customWidth="1"/>
+    <col min="2293" max="2293" width="13.125" style="11" customWidth="1"/>
+    <col min="2294" max="2298" width="9.125" style="11"/>
+    <col min="2299" max="2299" width="10.875" style="11" customWidth="1"/>
+    <col min="2300" max="2300" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="2301" max="2301" width="10.5625" style="11" customWidth="1"/>
+    <col min="2302" max="2302" width="10.875" style="11" customWidth="1"/>
+    <col min="2303" max="2547" width="9.125" style="11"/>
+    <col min="2548" max="2548" width="26.5625" style="11" customWidth="1"/>
+    <col min="2549" max="2549" width="13.125" style="11" customWidth="1"/>
+    <col min="2550" max="2554" width="9.125" style="11"/>
+    <col min="2555" max="2555" width="10.875" style="11" customWidth="1"/>
+    <col min="2556" max="2556" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="2557" max="2557" width="10.5625" style="11" customWidth="1"/>
+    <col min="2558" max="2558" width="10.875" style="11" customWidth="1"/>
+    <col min="2559" max="2803" width="9.125" style="11"/>
+    <col min="2804" max="2804" width="26.5625" style="11" customWidth="1"/>
+    <col min="2805" max="2805" width="13.125" style="11" customWidth="1"/>
+    <col min="2806" max="2810" width="9.125" style="11"/>
+    <col min="2811" max="2811" width="10.875" style="11" customWidth="1"/>
+    <col min="2812" max="2812" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="2813" max="2813" width="10.5625" style="11" customWidth="1"/>
+    <col min="2814" max="2814" width="10.875" style="11" customWidth="1"/>
+    <col min="2815" max="3059" width="9.125" style="11"/>
+    <col min="3060" max="3060" width="26.5625" style="11" customWidth="1"/>
+    <col min="3061" max="3061" width="13.125" style="11" customWidth="1"/>
+    <col min="3062" max="3066" width="9.125" style="11"/>
+    <col min="3067" max="3067" width="10.875" style="11" customWidth="1"/>
+    <col min="3068" max="3068" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="3069" max="3069" width="10.5625" style="11" customWidth="1"/>
+    <col min="3070" max="3070" width="10.875" style="11" customWidth="1"/>
+    <col min="3071" max="3315" width="9.125" style="11"/>
+    <col min="3316" max="3316" width="26.5625" style="11" customWidth="1"/>
+    <col min="3317" max="3317" width="13.125" style="11" customWidth="1"/>
+    <col min="3318" max="3322" width="9.125" style="11"/>
+    <col min="3323" max="3323" width="10.875" style="11" customWidth="1"/>
+    <col min="3324" max="3324" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="3325" max="3325" width="10.5625" style="11" customWidth="1"/>
+    <col min="3326" max="3326" width="10.875" style="11" customWidth="1"/>
+    <col min="3327" max="3571" width="9.125" style="11"/>
+    <col min="3572" max="3572" width="26.5625" style="11" customWidth="1"/>
+    <col min="3573" max="3573" width="13.125" style="11" customWidth="1"/>
+    <col min="3574" max="3578" width="9.125" style="11"/>
+    <col min="3579" max="3579" width="10.875" style="11" customWidth="1"/>
+    <col min="3580" max="3580" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="3581" max="3581" width="10.5625" style="11" customWidth="1"/>
+    <col min="3582" max="3582" width="10.875" style="11" customWidth="1"/>
+    <col min="3583" max="3827" width="9.125" style="11"/>
+    <col min="3828" max="3828" width="26.5625" style="11" customWidth="1"/>
+    <col min="3829" max="3829" width="13.125" style="11" customWidth="1"/>
+    <col min="3830" max="3834" width="9.125" style="11"/>
+    <col min="3835" max="3835" width="10.875" style="11" customWidth="1"/>
+    <col min="3836" max="3836" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="3837" max="3837" width="10.5625" style="11" customWidth="1"/>
+    <col min="3838" max="3838" width="10.875" style="11" customWidth="1"/>
+    <col min="3839" max="4083" width="9.125" style="11"/>
+    <col min="4084" max="4084" width="26.5625" style="11" customWidth="1"/>
+    <col min="4085" max="4085" width="13.125" style="11" customWidth="1"/>
+    <col min="4086" max="4090" width="9.125" style="11"/>
+    <col min="4091" max="4091" width="10.875" style="11" customWidth="1"/>
+    <col min="4092" max="4092" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="4093" max="4093" width="10.5625" style="11" customWidth="1"/>
+    <col min="4094" max="4094" width="10.875" style="11" customWidth="1"/>
+    <col min="4095" max="4339" width="9.125" style="11"/>
+    <col min="4340" max="4340" width="26.5625" style="11" customWidth="1"/>
+    <col min="4341" max="4341" width="13.125" style="11" customWidth="1"/>
+    <col min="4342" max="4346" width="9.125" style="11"/>
+    <col min="4347" max="4347" width="10.875" style="11" customWidth="1"/>
+    <col min="4348" max="4348" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="4349" max="4349" width="10.5625" style="11" customWidth="1"/>
+    <col min="4350" max="4350" width="10.875" style="11" customWidth="1"/>
+    <col min="4351" max="4595" width="9.125" style="11"/>
+    <col min="4596" max="4596" width="26.5625" style="11" customWidth="1"/>
+    <col min="4597" max="4597" width="13.125" style="11" customWidth="1"/>
+    <col min="4598" max="4602" width="9.125" style="11"/>
+    <col min="4603" max="4603" width="10.875" style="11" customWidth="1"/>
+    <col min="4604" max="4604" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="4605" max="4605" width="10.5625" style="11" customWidth="1"/>
+    <col min="4606" max="4606" width="10.875" style="11" customWidth="1"/>
+    <col min="4607" max="4851" width="9.125" style="11"/>
+    <col min="4852" max="4852" width="26.5625" style="11" customWidth="1"/>
+    <col min="4853" max="4853" width="13.125" style="11" customWidth="1"/>
+    <col min="4854" max="4858" width="9.125" style="11"/>
+    <col min="4859" max="4859" width="10.875" style="11" customWidth="1"/>
+    <col min="4860" max="4860" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="4861" max="4861" width="10.5625" style="11" customWidth="1"/>
+    <col min="4862" max="4862" width="10.875" style="11" customWidth="1"/>
+    <col min="4863" max="5107" width="9.125" style="11"/>
+    <col min="5108" max="5108" width="26.5625" style="11" customWidth="1"/>
+    <col min="5109" max="5109" width="13.125" style="11" customWidth="1"/>
+    <col min="5110" max="5114" width="9.125" style="11"/>
+    <col min="5115" max="5115" width="10.875" style="11" customWidth="1"/>
+    <col min="5116" max="5116" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="5117" max="5117" width="10.5625" style="11" customWidth="1"/>
+    <col min="5118" max="5118" width="10.875" style="11" customWidth="1"/>
+    <col min="5119" max="5363" width="9.125" style="11"/>
+    <col min="5364" max="5364" width="26.5625" style="11" customWidth="1"/>
+    <col min="5365" max="5365" width="13.125" style="11" customWidth="1"/>
+    <col min="5366" max="5370" width="9.125" style="11"/>
+    <col min="5371" max="5371" width="10.875" style="11" customWidth="1"/>
+    <col min="5372" max="5372" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="5373" max="5373" width="10.5625" style="11" customWidth="1"/>
+    <col min="5374" max="5374" width="10.875" style="11" customWidth="1"/>
+    <col min="5375" max="5619" width="9.125" style="11"/>
+    <col min="5620" max="5620" width="26.5625" style="11" customWidth="1"/>
+    <col min="5621" max="5621" width="13.125" style="11" customWidth="1"/>
+    <col min="5622" max="5626" width="9.125" style="11"/>
+    <col min="5627" max="5627" width="10.875" style="11" customWidth="1"/>
+    <col min="5628" max="5628" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="5629" max="5629" width="10.5625" style="11" customWidth="1"/>
+    <col min="5630" max="5630" width="10.875" style="11" customWidth="1"/>
+    <col min="5631" max="5875" width="9.125" style="11"/>
+    <col min="5876" max="5876" width="26.5625" style="11" customWidth="1"/>
+    <col min="5877" max="5877" width="13.125" style="11" customWidth="1"/>
+    <col min="5878" max="5882" width="9.125" style="11"/>
+    <col min="5883" max="5883" width="10.875" style="11" customWidth="1"/>
+    <col min="5884" max="5884" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="5885" max="5885" width="10.5625" style="11" customWidth="1"/>
+    <col min="5886" max="5886" width="10.875" style="11" customWidth="1"/>
+    <col min="5887" max="6131" width="9.125" style="11"/>
+    <col min="6132" max="6132" width="26.5625" style="11" customWidth="1"/>
+    <col min="6133" max="6133" width="13.125" style="11" customWidth="1"/>
+    <col min="6134" max="6138" width="9.125" style="11"/>
+    <col min="6139" max="6139" width="10.875" style="11" customWidth="1"/>
+    <col min="6140" max="6140" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="6141" max="6141" width="10.5625" style="11" customWidth="1"/>
+    <col min="6142" max="6142" width="10.875" style="11" customWidth="1"/>
+    <col min="6143" max="6387" width="9.125" style="11"/>
+    <col min="6388" max="6388" width="26.5625" style="11" customWidth="1"/>
+    <col min="6389" max="6389" width="13.125" style="11" customWidth="1"/>
+    <col min="6390" max="6394" width="9.125" style="11"/>
+    <col min="6395" max="6395" width="10.875" style="11" customWidth="1"/>
+    <col min="6396" max="6396" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="6397" max="6397" width="10.5625" style="11" customWidth="1"/>
+    <col min="6398" max="6398" width="10.875" style="11" customWidth="1"/>
+    <col min="6399" max="6643" width="9.125" style="11"/>
+    <col min="6644" max="6644" width="26.5625" style="11" customWidth="1"/>
+    <col min="6645" max="6645" width="13.125" style="11" customWidth="1"/>
+    <col min="6646" max="6650" width="9.125" style="11"/>
+    <col min="6651" max="6651" width="10.875" style="11" customWidth="1"/>
+    <col min="6652" max="6652" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="6653" max="6653" width="10.5625" style="11" customWidth="1"/>
+    <col min="6654" max="6654" width="10.875" style="11" customWidth="1"/>
+    <col min="6655" max="6899" width="9.125" style="11"/>
+    <col min="6900" max="6900" width="26.5625" style="11" customWidth="1"/>
+    <col min="6901" max="6901" width="13.125" style="11" customWidth="1"/>
+    <col min="6902" max="6906" width="9.125" style="11"/>
+    <col min="6907" max="6907" width="10.875" style="11" customWidth="1"/>
+    <col min="6908" max="6908" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="6909" max="6909" width="10.5625" style="11" customWidth="1"/>
+    <col min="6910" max="6910" width="10.875" style="11" customWidth="1"/>
+    <col min="6911" max="7155" width="9.125" style="11"/>
+    <col min="7156" max="7156" width="26.5625" style="11" customWidth="1"/>
+    <col min="7157" max="7157" width="13.125" style="11" customWidth="1"/>
+    <col min="7158" max="7162" width="9.125" style="11"/>
+    <col min="7163" max="7163" width="10.875" style="11" customWidth="1"/>
+    <col min="7164" max="7164" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="7165" max="7165" width="10.5625" style="11" customWidth="1"/>
+    <col min="7166" max="7166" width="10.875" style="11" customWidth="1"/>
+    <col min="7167" max="7411" width="9.125" style="11"/>
+    <col min="7412" max="7412" width="26.5625" style="11" customWidth="1"/>
+    <col min="7413" max="7413" width="13.125" style="11" customWidth="1"/>
+    <col min="7414" max="7418" width="9.125" style="11"/>
+    <col min="7419" max="7419" width="10.875" style="11" customWidth="1"/>
+    <col min="7420" max="7420" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="7421" max="7421" width="10.5625" style="11" customWidth="1"/>
+    <col min="7422" max="7422" width="10.875" style="11" customWidth="1"/>
+    <col min="7423" max="7667" width="9.125" style="11"/>
+    <col min="7668" max="7668" width="26.5625" style="11" customWidth="1"/>
+    <col min="7669" max="7669" width="13.125" style="11" customWidth="1"/>
+    <col min="7670" max="7674" width="9.125" style="11"/>
+    <col min="7675" max="7675" width="10.875" style="11" customWidth="1"/>
+    <col min="7676" max="7676" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="7677" max="7677" width="10.5625" style="11" customWidth="1"/>
+    <col min="7678" max="7678" width="10.875" style="11" customWidth="1"/>
+    <col min="7679" max="7923" width="9.125" style="11"/>
+    <col min="7924" max="7924" width="26.5625" style="11" customWidth="1"/>
+    <col min="7925" max="7925" width="13.125" style="11" customWidth="1"/>
+    <col min="7926" max="7930" width="9.125" style="11"/>
+    <col min="7931" max="7931" width="10.875" style="11" customWidth="1"/>
+    <col min="7932" max="7932" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="7933" max="7933" width="10.5625" style="11" customWidth="1"/>
+    <col min="7934" max="7934" width="10.875" style="11" customWidth="1"/>
+    <col min="7935" max="8179" width="9.125" style="11"/>
+    <col min="8180" max="8180" width="26.5625" style="11" customWidth="1"/>
+    <col min="8181" max="8181" width="13.125" style="11" customWidth="1"/>
+    <col min="8182" max="8186" width="9.125" style="11"/>
+    <col min="8187" max="8187" width="10.875" style="11" customWidth="1"/>
+    <col min="8188" max="8188" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="8189" max="8189" width="10.5625" style="11" customWidth="1"/>
+    <col min="8190" max="8190" width="10.875" style="11" customWidth="1"/>
+    <col min="8191" max="8435" width="9.125" style="11"/>
+    <col min="8436" max="8436" width="26.5625" style="11" customWidth="1"/>
+    <col min="8437" max="8437" width="13.125" style="11" customWidth="1"/>
+    <col min="8438" max="8442" width="9.125" style="11"/>
+    <col min="8443" max="8443" width="10.875" style="11" customWidth="1"/>
+    <col min="8444" max="8444" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="8445" max="8445" width="10.5625" style="11" customWidth="1"/>
+    <col min="8446" max="8446" width="10.875" style="11" customWidth="1"/>
+    <col min="8447" max="8691" width="9.125" style="11"/>
+    <col min="8692" max="8692" width="26.5625" style="11" customWidth="1"/>
+    <col min="8693" max="8693" width="13.125" style="11" customWidth="1"/>
+    <col min="8694" max="8698" width="9.125" style="11"/>
+    <col min="8699" max="8699" width="10.875" style="11" customWidth="1"/>
+    <col min="8700" max="8700" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="8701" max="8701" width="10.5625" style="11" customWidth="1"/>
+    <col min="8702" max="8702" width="10.875" style="11" customWidth="1"/>
+    <col min="8703" max="8947" width="9.125" style="11"/>
+    <col min="8948" max="8948" width="26.5625" style="11" customWidth="1"/>
+    <col min="8949" max="8949" width="13.125" style="11" customWidth="1"/>
+    <col min="8950" max="8954" width="9.125" style="11"/>
+    <col min="8955" max="8955" width="10.875" style="11" customWidth="1"/>
+    <col min="8956" max="8956" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="8957" max="8957" width="10.5625" style="11" customWidth="1"/>
+    <col min="8958" max="8958" width="10.875" style="11" customWidth="1"/>
+    <col min="8959" max="9203" width="9.125" style="11"/>
+    <col min="9204" max="9204" width="26.5625" style="11" customWidth="1"/>
+    <col min="9205" max="9205" width="13.125" style="11" customWidth="1"/>
+    <col min="9206" max="9210" width="9.125" style="11"/>
+    <col min="9211" max="9211" width="10.875" style="11" customWidth="1"/>
+    <col min="9212" max="9212" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="9213" max="9213" width="10.5625" style="11" customWidth="1"/>
+    <col min="9214" max="9214" width="10.875" style="11" customWidth="1"/>
+    <col min="9215" max="9459" width="9.125" style="11"/>
+    <col min="9460" max="9460" width="26.5625" style="11" customWidth="1"/>
+    <col min="9461" max="9461" width="13.125" style="11" customWidth="1"/>
+    <col min="9462" max="9466" width="9.125" style="11"/>
+    <col min="9467" max="9467" width="10.875" style="11" customWidth="1"/>
+    <col min="9468" max="9468" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="9469" max="9469" width="10.5625" style="11" customWidth="1"/>
+    <col min="9470" max="9470" width="10.875" style="11" customWidth="1"/>
+    <col min="9471" max="9715" width="9.125" style="11"/>
+    <col min="9716" max="9716" width="26.5625" style="11" customWidth="1"/>
+    <col min="9717" max="9717" width="13.125" style="11" customWidth="1"/>
+    <col min="9718" max="9722" width="9.125" style="11"/>
+    <col min="9723" max="9723" width="10.875" style="11" customWidth="1"/>
+    <col min="9724" max="9724" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="9725" max="9725" width="10.5625" style="11" customWidth="1"/>
+    <col min="9726" max="9726" width="10.875" style="11" customWidth="1"/>
+    <col min="9727" max="9971" width="9.125" style="11"/>
+    <col min="9972" max="9972" width="26.5625" style="11" customWidth="1"/>
+    <col min="9973" max="9973" width="13.125" style="11" customWidth="1"/>
+    <col min="9974" max="9978" width="9.125" style="11"/>
+    <col min="9979" max="9979" width="10.875" style="11" customWidth="1"/>
+    <col min="9980" max="9980" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="9981" max="9981" width="10.5625" style="11" customWidth="1"/>
+    <col min="9982" max="9982" width="10.875" style="11" customWidth="1"/>
+    <col min="9983" max="10227" width="9.125" style="11"/>
+    <col min="10228" max="10228" width="26.5625" style="11" customWidth="1"/>
+    <col min="10229" max="10229" width="13.125" style="11" customWidth="1"/>
+    <col min="10230" max="10234" width="9.125" style="11"/>
+    <col min="10235" max="10235" width="10.875" style="11" customWidth="1"/>
+    <col min="10236" max="10236" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="10237" max="10237" width="10.5625" style="11" customWidth="1"/>
+    <col min="10238" max="10238" width="10.875" style="11" customWidth="1"/>
+    <col min="10239" max="10483" width="9.125" style="11"/>
+    <col min="10484" max="10484" width="26.5625" style="11" customWidth="1"/>
+    <col min="10485" max="10485" width="13.125" style="11" customWidth="1"/>
+    <col min="10486" max="10490" width="9.125" style="11"/>
+    <col min="10491" max="10491" width="10.875" style="11" customWidth="1"/>
+    <col min="10492" max="10492" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="10493" max="10493" width="10.5625" style="11" customWidth="1"/>
+    <col min="10494" max="10494" width="10.875" style="11" customWidth="1"/>
+    <col min="10495" max="10739" width="9.125" style="11"/>
+    <col min="10740" max="10740" width="26.5625" style="11" customWidth="1"/>
+    <col min="10741" max="10741" width="13.125" style="11" customWidth="1"/>
+    <col min="10742" max="10746" width="9.125" style="11"/>
+    <col min="10747" max="10747" width="10.875" style="11" customWidth="1"/>
+    <col min="10748" max="10748" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="10749" max="10749" width="10.5625" style="11" customWidth="1"/>
+    <col min="10750" max="10750" width="10.875" style="11" customWidth="1"/>
+    <col min="10751" max="10995" width="9.125" style="11"/>
+    <col min="10996" max="10996" width="26.5625" style="11" customWidth="1"/>
+    <col min="10997" max="10997" width="13.125" style="11" customWidth="1"/>
+    <col min="10998" max="11002" width="9.125" style="11"/>
+    <col min="11003" max="11003" width="10.875" style="11" customWidth="1"/>
+    <col min="11004" max="11004" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="11005" max="11005" width="10.5625" style="11" customWidth="1"/>
+    <col min="11006" max="11006" width="10.875" style="11" customWidth="1"/>
+    <col min="11007" max="11251" width="9.125" style="11"/>
+    <col min="11252" max="11252" width="26.5625" style="11" customWidth="1"/>
+    <col min="11253" max="11253" width="13.125" style="11" customWidth="1"/>
+    <col min="11254" max="11258" width="9.125" style="11"/>
+    <col min="11259" max="11259" width="10.875" style="11" customWidth="1"/>
+    <col min="11260" max="11260" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="11261" max="11261" width="10.5625" style="11" customWidth="1"/>
+    <col min="11262" max="11262" width="10.875" style="11" customWidth="1"/>
+    <col min="11263" max="11507" width="9.125" style="11"/>
+    <col min="11508" max="11508" width="26.5625" style="11" customWidth="1"/>
+    <col min="11509" max="11509" width="13.125" style="11" customWidth="1"/>
+    <col min="11510" max="11514" width="9.125" style="11"/>
+    <col min="11515" max="11515" width="10.875" style="11" customWidth="1"/>
+    <col min="11516" max="11516" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="11517" max="11517" width="10.5625" style="11" customWidth="1"/>
+    <col min="11518" max="11518" width="10.875" style="11" customWidth="1"/>
+    <col min="11519" max="11763" width="9.125" style="11"/>
+    <col min="11764" max="11764" width="26.5625" style="11" customWidth="1"/>
+    <col min="11765" max="11765" width="13.125" style="11" customWidth="1"/>
+    <col min="11766" max="11770" width="9.125" style="11"/>
+    <col min="11771" max="11771" width="10.875" style="11" customWidth="1"/>
+    <col min="11772" max="11772" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="11773" max="11773" width="10.5625" style="11" customWidth="1"/>
+    <col min="11774" max="11774" width="10.875" style="11" customWidth="1"/>
+    <col min="11775" max="12019" width="9.125" style="11"/>
+    <col min="12020" max="12020" width="26.5625" style="11" customWidth="1"/>
+    <col min="12021" max="12021" width="13.125" style="11" customWidth="1"/>
+    <col min="12022" max="12026" width="9.125" style="11"/>
+    <col min="12027" max="12027" width="10.875" style="11" customWidth="1"/>
+    <col min="12028" max="12028" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="12029" max="12029" width="10.5625" style="11" customWidth="1"/>
+    <col min="12030" max="12030" width="10.875" style="11" customWidth="1"/>
+    <col min="12031" max="12275" width="9.125" style="11"/>
+    <col min="12276" max="12276" width="26.5625" style="11" customWidth="1"/>
+    <col min="12277" max="12277" width="13.125" style="11" customWidth="1"/>
+    <col min="12278" max="12282" width="9.125" style="11"/>
+    <col min="12283" max="12283" width="10.875" style="11" customWidth="1"/>
+    <col min="12284" max="12284" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="12285" max="12285" width="10.5625" style="11" customWidth="1"/>
+    <col min="12286" max="12286" width="10.875" style="11" customWidth="1"/>
+    <col min="12287" max="12531" width="9.125" style="11"/>
+    <col min="12532" max="12532" width="26.5625" style="11" customWidth="1"/>
+    <col min="12533" max="12533" width="13.125" style="11" customWidth="1"/>
+    <col min="12534" max="12538" width="9.125" style="11"/>
+    <col min="12539" max="12539" width="10.875" style="11" customWidth="1"/>
+    <col min="12540" max="12540" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="12541" max="12541" width="10.5625" style="11" customWidth="1"/>
+    <col min="12542" max="12542" width="10.875" style="11" customWidth="1"/>
+    <col min="12543" max="12787" width="9.125" style="11"/>
+    <col min="12788" max="12788" width="26.5625" style="11" customWidth="1"/>
+    <col min="12789" max="12789" width="13.125" style="11" customWidth="1"/>
+    <col min="12790" max="12794" width="9.125" style="11"/>
+    <col min="12795" max="12795" width="10.875" style="11" customWidth="1"/>
+    <col min="12796" max="12796" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="12797" max="12797" width="10.5625" style="11" customWidth="1"/>
+    <col min="12798" max="12798" width="10.875" style="11" customWidth="1"/>
+    <col min="12799" max="13043" width="9.125" style="11"/>
+    <col min="13044" max="13044" width="26.5625" style="11" customWidth="1"/>
+    <col min="13045" max="13045" width="13.125" style="11" customWidth="1"/>
+    <col min="13046" max="13050" width="9.125" style="11"/>
+    <col min="13051" max="13051" width="10.875" style="11" customWidth="1"/>
+    <col min="13052" max="13052" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="13053" max="13053" width="10.5625" style="11" customWidth="1"/>
+    <col min="13054" max="13054" width="10.875" style="11" customWidth="1"/>
+    <col min="13055" max="13299" width="9.125" style="11"/>
+    <col min="13300" max="13300" width="26.5625" style="11" customWidth="1"/>
+    <col min="13301" max="13301" width="13.125" style="11" customWidth="1"/>
+    <col min="13302" max="13306" width="9.125" style="11"/>
+    <col min="13307" max="13307" width="10.875" style="11" customWidth="1"/>
+    <col min="13308" max="13308" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="13309" max="13309" width="10.5625" style="11" customWidth="1"/>
+    <col min="13310" max="13310" width="10.875" style="11" customWidth="1"/>
+    <col min="13311" max="13555" width="9.125" style="11"/>
+    <col min="13556" max="13556" width="26.5625" style="11" customWidth="1"/>
+    <col min="13557" max="13557" width="13.125" style="11" customWidth="1"/>
+    <col min="13558" max="13562" width="9.125" style="11"/>
+    <col min="13563" max="13563" width="10.875" style="11" customWidth="1"/>
+    <col min="13564" max="13564" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="13565" max="13565" width="10.5625" style="11" customWidth="1"/>
+    <col min="13566" max="13566" width="10.875" style="11" customWidth="1"/>
+    <col min="13567" max="13811" width="9.125" style="11"/>
+    <col min="13812" max="13812" width="26.5625" style="11" customWidth="1"/>
+    <col min="13813" max="13813" width="13.125" style="11" customWidth="1"/>
+    <col min="13814" max="13818" width="9.125" style="11"/>
+    <col min="13819" max="13819" width="10.875" style="11" customWidth="1"/>
+    <col min="13820" max="13820" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="13821" max="13821" width="10.5625" style="11" customWidth="1"/>
+    <col min="13822" max="13822" width="10.875" style="11" customWidth="1"/>
+    <col min="13823" max="14067" width="9.125" style="11"/>
+    <col min="14068" max="14068" width="26.5625" style="11" customWidth="1"/>
+    <col min="14069" max="14069" width="13.125" style="11" customWidth="1"/>
+    <col min="14070" max="14074" width="9.125" style="11"/>
+    <col min="14075" max="14075" width="10.875" style="11" customWidth="1"/>
+    <col min="14076" max="14076" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="14077" max="14077" width="10.5625" style="11" customWidth="1"/>
+    <col min="14078" max="14078" width="10.875" style="11" customWidth="1"/>
+    <col min="14079" max="14323" width="9.125" style="11"/>
+    <col min="14324" max="14324" width="26.5625" style="11" customWidth="1"/>
+    <col min="14325" max="14325" width="13.125" style="11" customWidth="1"/>
+    <col min="14326" max="14330" width="9.125" style="11"/>
+    <col min="14331" max="14331" width="10.875" style="11" customWidth="1"/>
+    <col min="14332" max="14332" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="14333" max="14333" width="10.5625" style="11" customWidth="1"/>
+    <col min="14334" max="14334" width="10.875" style="11" customWidth="1"/>
+    <col min="14335" max="14579" width="9.125" style="11"/>
+    <col min="14580" max="14580" width="26.5625" style="11" customWidth="1"/>
+    <col min="14581" max="14581" width="13.125" style="11" customWidth="1"/>
+    <col min="14582" max="14586" width="9.125" style="11"/>
+    <col min="14587" max="14587" width="10.875" style="11" customWidth="1"/>
+    <col min="14588" max="14588" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="14589" max="14589" width="10.5625" style="11" customWidth="1"/>
+    <col min="14590" max="14590" width="10.875" style="11" customWidth="1"/>
+    <col min="14591" max="14835" width="9.125" style="11"/>
+    <col min="14836" max="14836" width="26.5625" style="11" customWidth="1"/>
+    <col min="14837" max="14837" width="13.125" style="11" customWidth="1"/>
+    <col min="14838" max="14842" width="9.125" style="11"/>
+    <col min="14843" max="14843" width="10.875" style="11" customWidth="1"/>
+    <col min="14844" max="14844" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="14845" max="14845" width="10.5625" style="11" customWidth="1"/>
+    <col min="14846" max="14846" width="10.875" style="11" customWidth="1"/>
+    <col min="14847" max="15091" width="9.125" style="11"/>
+    <col min="15092" max="15092" width="26.5625" style="11" customWidth="1"/>
+    <col min="15093" max="15093" width="13.125" style="11" customWidth="1"/>
+    <col min="15094" max="15098" width="9.125" style="11"/>
+    <col min="15099" max="15099" width="10.875" style="11" customWidth="1"/>
+    <col min="15100" max="15100" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="15101" max="15101" width="10.5625" style="11" customWidth="1"/>
+    <col min="15102" max="15102" width="10.875" style="11" customWidth="1"/>
+    <col min="15103" max="15347" width="9.125" style="11"/>
+    <col min="15348" max="15348" width="26.5625" style="11" customWidth="1"/>
+    <col min="15349" max="15349" width="13.125" style="11" customWidth="1"/>
+    <col min="15350" max="15354" width="9.125" style="11"/>
+    <col min="15355" max="15355" width="10.875" style="11" customWidth="1"/>
+    <col min="15356" max="15356" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="15357" max="15357" width="10.5625" style="11" customWidth="1"/>
+    <col min="15358" max="15358" width="10.875" style="11" customWidth="1"/>
+    <col min="15359" max="15603" width="9.125" style="11"/>
+    <col min="15604" max="15604" width="26.5625" style="11" customWidth="1"/>
+    <col min="15605" max="15605" width="13.125" style="11" customWidth="1"/>
+    <col min="15606" max="15610" width="9.125" style="11"/>
+    <col min="15611" max="15611" width="10.875" style="11" customWidth="1"/>
+    <col min="15612" max="15612" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="15613" max="15613" width="10.5625" style="11" customWidth="1"/>
+    <col min="15614" max="15614" width="10.875" style="11" customWidth="1"/>
+    <col min="15615" max="15859" width="9.125" style="11"/>
+    <col min="15860" max="15860" width="26.5625" style="11" customWidth="1"/>
+    <col min="15861" max="15861" width="13.125" style="11" customWidth="1"/>
+    <col min="15862" max="15866" width="9.125" style="11"/>
+    <col min="15867" max="15867" width="10.875" style="11" customWidth="1"/>
+    <col min="15868" max="15868" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="15869" max="15869" width="10.5625" style="11" customWidth="1"/>
+    <col min="15870" max="15870" width="10.875" style="11" customWidth="1"/>
+    <col min="15871" max="16115" width="9.125" style="11"/>
+    <col min="16116" max="16116" width="26.5625" style="11" customWidth="1"/>
+    <col min="16117" max="16117" width="13.125" style="11" customWidth="1"/>
+    <col min="16118" max="16122" width="9.125" style="11"/>
+    <col min="16123" max="16123" width="10.875" style="11" customWidth="1"/>
+    <col min="16124" max="16124" width="23" style="11" bestFit="1" customWidth="1"/>
+    <col min="16125" max="16125" width="10.5625" style="11" customWidth="1"/>
+    <col min="16126" max="16126" width="10.875" style="11" customWidth="1"/>
+    <col min="16127" max="16384" width="9.125" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="12"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="14">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="15">
+        <v>1</v>
+      </c>
+      <c r="C7" s="15">
+        <v>2</v>
+      </c>
+      <c r="D7" s="15">
+        <v>3</v>
+      </c>
+      <c r="E7" s="15">
+        <v>4</v>
+      </c>
+      <c r="F7" s="15">
+        <v>5</v>
+      </c>
+      <c r="G7" s="15">
+        <v>6</v>
+      </c>
+      <c r="H7" s="16"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="18">
+        <v>12.5</v>
+      </c>
+      <c r="C8" s="18">
+        <v>12.55</v>
+      </c>
+      <c r="D8" s="18">
+        <v>12.7</v>
+      </c>
+      <c r="E8" s="18">
+        <v>12.8</v>
+      </c>
+      <c r="F8" s="18">
+        <v>12.85</v>
+      </c>
+      <c r="G8" s="18">
+        <v>12.95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="B9" s="19">
+        <f>B8*0.05</f>
+        <v>0.625</v>
+      </c>
+      <c r="C9" s="19">
+        <f t="shared" ref="C9:G9" si="0">C8*0.05</f>
+        <v>0.62750000000000006</v>
+      </c>
+      <c r="D9" s="19">
+        <f t="shared" si="0"/>
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="E9" s="19">
+        <f t="shared" si="0"/>
+        <v>0.64000000000000012</v>
+      </c>
+      <c r="F9" s="19">
+        <f t="shared" si="0"/>
+        <v>0.64250000000000007</v>
+      </c>
+      <c r="G9" s="19">
+        <f t="shared" si="0"/>
+        <v>0.64749999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="15">
+        <v>1</v>
+      </c>
+      <c r="C11" s="15">
+        <v>2</v>
+      </c>
+      <c r="D11" s="15">
+        <v>3</v>
+      </c>
+      <c r="E11" s="15">
+        <v>4</v>
+      </c>
+      <c r="F11" s="15">
+        <v>5</v>
+      </c>
+      <c r="G11" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="47">
+        <v>5000</v>
+      </c>
+      <c r="C12" s="47">
+        <v>20000</v>
+      </c>
+      <c r="D12" s="47">
+        <v>30000</v>
+      </c>
+      <c r="E12" s="47">
+        <v>30000</v>
+      </c>
+      <c r="F12" s="47">
+        <v>25000</v>
+      </c>
+      <c r="G12" s="47">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="13">
+        <v>30000</v>
+      </c>
+      <c r="C14" s="13">
+        <v>30000</v>
+      </c>
+      <c r="D14" s="13">
+        <v>30000</v>
+      </c>
+      <c r="E14" s="13">
+        <v>30000</v>
+      </c>
+      <c r="F14" s="13">
+        <v>30000</v>
+      </c>
+      <c r="G14" s="13">
+        <v>30000</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="13">
+        <v>10000</v>
+      </c>
+      <c r="C18" s="13">
+        <v>15000</v>
+      </c>
+      <c r="D18" s="13">
+        <v>30000</v>
+      </c>
+      <c r="E18" s="13">
+        <v>35000</v>
+      </c>
+      <c r="F18" s="13">
+        <v>25000</v>
+      </c>
+      <c r="G18" s="13">
+        <v>10000</v>
+      </c>
+      <c r="H18" s="11">
+        <f>SUM(B18:G18)</f>
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="24">
+        <f>$B$4 + B12- B18</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="24">
+        <f>B20 + C12- C18</f>
+        <v>5000</v>
+      </c>
+      <c r="D20" s="24">
+        <f t="shared" ref="D20:F20" si="1">C20 + D12- D18</f>
+        <v>5000</v>
+      </c>
+      <c r="E20" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="24">
+        <f>F20 + G12- G18</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>572</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="B21" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="13">
+        <v>10000</v>
+      </c>
+      <c r="C22" s="13">
+        <v>10000</v>
+      </c>
+      <c r="D22" s="13">
+        <v>10000</v>
+      </c>
+      <c r="E22" s="13">
+        <v>10000</v>
+      </c>
+      <c r="F22" s="13">
+        <v>10000</v>
+      </c>
+      <c r="G22" s="13">
+        <v>10000</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="20"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="19"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="15">
+        <v>1</v>
+      </c>
+      <c r="C25" s="15">
+        <v>2</v>
+      </c>
+      <c r="D25" s="15">
+        <v>3</v>
+      </c>
+      <c r="E25" s="15">
+        <v>4</v>
+      </c>
+      <c r="F25" s="15">
+        <v>5</v>
+      </c>
+      <c r="G25" s="15">
+        <v>6</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="H26" s="105">
+        <f>SUMPRODUCT(B9:G9, B20:G20)</f>
+        <v>6312.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="H27" s="105">
+        <f>SUMPRODUCT(B8:G8,B12:G12)</f>
+        <v>1529250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="H28" s="106">
+        <f>SUM(H26:H27)</f>
+        <v>1535562.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="B3:K24"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="1.4375" customWidth="1"/>
+    <col min="2" max="2" width="7.4375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.125" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:11">
+      <c r="G3" t="s">
+        <v>327</v>
+      </c>
+      <c r="H3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="C4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E4" t="s">
+        <v>294</v>
+      </c>
+      <c r="G4" t="s">
+        <v>326</v>
+      </c>
+      <c r="H4" t="s">
+        <v>330</v>
+      </c>
+      <c r="I4" t="s">
+        <v>332</v>
+      </c>
+      <c r="J4" t="s">
+        <v>333</v>
+      </c>
+      <c r="K4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11">
+      <c r="B5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D5" t="s">
+        <v>311</v>
+      </c>
+      <c r="E5" t="s">
+        <v>310</v>
+      </c>
+      <c r="F5" t="s">
+        <v>311</v>
+      </c>
+      <c r="G5" t="s">
+        <v>328</v>
+      </c>
+      <c r="H5" t="s">
+        <v>331</v>
+      </c>
+      <c r="I5" t="s">
+        <v>326</v>
+      </c>
+      <c r="J5" t="s">
+        <v>328</v>
+      </c>
+      <c r="K5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="B6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6" s="75">
+        <v>2</v>
+      </c>
+      <c r="D6" s="75">
+        <v>1</v>
+      </c>
+      <c r="E6" s="76">
+        <v>180000</v>
+      </c>
+      <c r="F6" s="76">
+        <v>280000</v>
+      </c>
+      <c r="G6">
+        <f>C6-D6</f>
+        <v>1</v>
+      </c>
+      <c r="H6" s="74">
+        <f>(F6-E6)/G6</f>
+        <v>100000</v>
+      </c>
+      <c r="I6" s="52">
+        <v>0</v>
+      </c>
+      <c r="J6" s="52">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f>I6+C6-J6</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C7" s="75">
+        <v>4</v>
+      </c>
+      <c r="D7" s="75">
+        <v>2</v>
+      </c>
+      <c r="E7" s="76">
+        <v>320000</v>
+      </c>
+      <c r="F7" s="76">
+        <v>420000</v>
+      </c>
+      <c r="G7">
+        <f t="shared" ref="G7:G19" si="0">C7-D7</f>
+        <v>2</v>
+      </c>
+      <c r="H7" s="74">
+        <f t="shared" ref="H7:H19" si="1">(F7-E7)/G7</f>
+        <v>50000</v>
+      </c>
+      <c r="I7" s="52">
+        <v>2</v>
+      </c>
+      <c r="J7" s="52">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <f t="shared" ref="K7:K19" si="2">I7+C7-J7</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" s="75">
+        <v>10</v>
+      </c>
+      <c r="D8" s="75">
+        <v>7</v>
+      </c>
+      <c r="E8" s="76">
+        <v>620000</v>
+      </c>
+      <c r="F8" s="76">
+        <v>860000</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H8" s="74">
+        <f t="shared" si="1"/>
+        <v>80000</v>
+      </c>
+      <c r="I8" s="52">
+        <v>6</v>
+      </c>
+      <c r="J8" s="52">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="B9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" s="75">
+        <v>6</v>
+      </c>
+      <c r="D9" s="75">
+        <v>4</v>
+      </c>
+      <c r="E9" s="76">
+        <v>260000</v>
+      </c>
+      <c r="F9" s="76">
+        <v>340000</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H9" s="74">
+        <f t="shared" si="1"/>
+        <v>40000</v>
+      </c>
+      <c r="I9" s="52">
+        <v>16</v>
+      </c>
+      <c r="J9" s="52">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" t="s">
+        <v>316</v>
+      </c>
+      <c r="C10" s="75">
+        <v>4</v>
+      </c>
+      <c r="D10" s="75">
+        <v>3</v>
+      </c>
+      <c r="E10" s="76">
+        <v>410000</v>
+      </c>
+      <c r="F10" s="76">
+        <v>570000</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H10" s="74">
+        <f t="shared" si="1"/>
+        <v>160000</v>
+      </c>
+      <c r="I10" s="52">
+        <v>16</v>
+      </c>
+      <c r="J10" s="52">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="75">
+        <v>5</v>
+      </c>
+      <c r="D11" s="75">
+        <v>3</v>
+      </c>
+      <c r="E11" s="76">
+        <v>180000</v>
+      </c>
+      <c r="F11" s="76">
+        <v>260000</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H11" s="74">
+        <f t="shared" si="1"/>
+        <v>40000</v>
+      </c>
+      <c r="I11" s="52">
+        <v>20</v>
+      </c>
+      <c r="J11" s="52">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" t="s">
+        <v>318</v>
+      </c>
+      <c r="C12" s="75">
+        <v>7</v>
+      </c>
+      <c r="D12" s="75">
+        <v>4</v>
+      </c>
+      <c r="E12" s="76">
+        <v>900000</v>
+      </c>
+      <c r="F12" s="76">
+        <v>1020000</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H12" s="74">
+        <f t="shared" si="1"/>
+        <v>40000</v>
+      </c>
+      <c r="I12" s="52">
+        <v>22</v>
+      </c>
+      <c r="J12" s="52">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11">
+      <c r="B13" t="s">
+        <v>319</v>
+      </c>
+      <c r="C13" s="75">
+        <v>9</v>
+      </c>
+      <c r="D13" s="75">
+        <v>6</v>
+      </c>
+      <c r="E13" s="76">
+        <v>200000</v>
+      </c>
+      <c r="F13" s="76">
+        <v>380000</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H13" s="74">
+        <f t="shared" si="1"/>
+        <v>60000</v>
+      </c>
+      <c r="I13" s="52">
+        <v>29</v>
+      </c>
+      <c r="J13" s="52">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11">
+      <c r="B14" t="s">
+        <v>320</v>
+      </c>
+      <c r="C14" s="75">
+        <v>7</v>
+      </c>
+      <c r="D14" s="75">
+        <v>5</v>
+      </c>
+      <c r="E14" s="76">
+        <v>210000</v>
+      </c>
+      <c r="F14" s="76">
+        <v>270000</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H14" s="74">
+        <f t="shared" si="1"/>
+        <v>30000</v>
+      </c>
+      <c r="I14" s="52">
+        <v>16</v>
+      </c>
+      <c r="J14" s="52">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" t="s">
+        <v>321</v>
+      </c>
+      <c r="C15" s="75">
+        <v>8</v>
+      </c>
+      <c r="D15" s="75">
+        <v>6</v>
+      </c>
+      <c r="E15" s="76">
+        <v>430000</v>
+      </c>
+      <c r="F15" s="76">
+        <v>490000</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H15" s="74">
+        <f t="shared" si="1"/>
+        <v>30000</v>
+      </c>
+      <c r="I15" s="52">
+        <v>23</v>
+      </c>
+      <c r="J15" s="52">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11">
+      <c r="B16" t="s">
+        <v>322</v>
+      </c>
+      <c r="C16" s="75">
+        <v>4</v>
+      </c>
+      <c r="D16" s="75">
+        <v>3</v>
+      </c>
+      <c r="E16" s="76">
+        <v>160000</v>
+      </c>
+      <c r="F16" s="76">
+        <v>200000</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H16" s="74">
+        <f t="shared" si="1"/>
+        <v>40000</v>
+      </c>
+      <c r="I16" s="52">
+        <v>30</v>
+      </c>
+      <c r="J16" s="52">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" t="s">
+        <v>323</v>
+      </c>
+      <c r="C17" s="75">
+        <v>5</v>
+      </c>
+      <c r="D17" s="75">
+        <v>3</v>
+      </c>
+      <c r="E17" s="76">
+        <v>250000</v>
+      </c>
+      <c r="F17" s="76">
+        <v>350000</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H17" s="74">
+        <f t="shared" si="1"/>
+        <v>50000</v>
+      </c>
+      <c r="I17" s="52">
+        <v>29</v>
+      </c>
+      <c r="J17" s="52">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" t="s">
+        <v>324</v>
+      </c>
+      <c r="C18" s="75">
+        <v>2</v>
+      </c>
+      <c r="D18" s="75">
+        <v>1</v>
+      </c>
+      <c r="E18" s="76">
+        <v>100000</v>
+      </c>
+      <c r="F18" s="76">
+        <v>200000</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H18" s="74">
+        <f t="shared" si="1"/>
+        <v>100000</v>
+      </c>
+      <c r="I18" s="52">
+        <v>38</v>
+      </c>
+      <c r="J18" s="52">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" t="s">
+        <v>325</v>
+      </c>
+      <c r="C19" s="75">
+        <v>6</v>
+      </c>
+      <c r="D19" s="75">
+        <v>3</v>
+      </c>
+      <c r="E19" s="76">
+        <v>330000</v>
+      </c>
+      <c r="F19" s="76">
+        <v>510000</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H19" s="74">
+        <f t="shared" si="1"/>
+        <v>60000</v>
+      </c>
+      <c r="I19" s="52">
+        <v>34</v>
+      </c>
+      <c r="J19" s="52">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="K21" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11">
+      <c r="H22" t="s">
+        <v>335</v>
+      </c>
+      <c r="I22" s="52">
+        <v>40</v>
+      </c>
+      <c r="J22" s="78" t="s">
+        <v>278</v>
+      </c>
+      <c r="K22">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" ht="13.9" thickBot="1"/>
+    <row r="24" spans="2:11" ht="13.9" thickBot="1">
+      <c r="H24" t="s">
+        <v>92</v>
+      </c>
+      <c r="I24" s="77">
+        <f>SUM(E6:E19)+SUMPRODUCT(H6:H19,J6:J19)</f>
+        <v>4690000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -6350,7 +8089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:V21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -7027,7 +8766,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -7901,12 +9640,12 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32EF314-017F-4330-8EC3-C4F5979707FD}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -8038,7 +9777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507B525D-8CA6-4025-AEB1-68EFB4069FDC}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -8187,7 +9926,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{885E5C17-D921-4574-A082-7E0E95290DFB}">
   <dimension ref="A1:Z38"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -9770,12 +11509,12 @@
       <c r="A38" s="20"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:O38"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -11444,7 +13183,139 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27AE6086-7CC8-4035-82C0-4B5E0BB66C79}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="2.0625" style="134" customWidth="1"/>
+    <col min="2" max="2" width="4.75" style="134" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.0625" style="134" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.6875" style="134" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="134"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="140" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="140" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="140" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="13.9" thickBot="1">
+      <c r="A6" s="134" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138" t="s">
+        <v>480</v>
+      </c>
+      <c r="E7" s="138" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="13.9" thickBot="1">
+      <c r="B8" s="137" t="s">
+        <v>478</v>
+      </c>
+      <c r="C8" s="137" t="s">
+        <v>479</v>
+      </c>
+      <c r="D8" s="137" t="s">
+        <v>481</v>
+      </c>
+      <c r="E8" s="137" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="139" t="s">
+        <v>615</v>
+      </c>
+      <c r="C9" s="139" t="s">
+        <v>296</v>
+      </c>
+      <c r="D9" s="139">
+        <v>2.4642857142857153</v>
+      </c>
+      <c r="E9" s="139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="13.9" thickBot="1">
+      <c r="B10" s="136" t="s">
+        <v>614</v>
+      </c>
+      <c r="C10" s="136" t="s">
+        <v>297</v>
+      </c>
+      <c r="D10" s="136">
+        <v>2.6071428571428554</v>
+      </c>
+      <c r="E10" s="136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="13.9" thickBot="1">
+      <c r="A12" s="134" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" s="138"/>
+      <c r="C13" s="138"/>
+      <c r="D13" s="138" t="s">
+        <v>480</v>
+      </c>
+      <c r="E13" s="138" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="13.9" thickBot="1">
+      <c r="B14" s="137" t="s">
+        <v>478</v>
+      </c>
+      <c r="C14" s="137" t="s">
+        <v>479</v>
+      </c>
+      <c r="D14" s="137" t="s">
+        <v>481</v>
+      </c>
+      <c r="E14" s="137" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="13.9" thickBot="1">
+      <c r="B15" s="136" t="s">
+        <v>611</v>
+      </c>
+      <c r="C15" s="136" t="s">
+        <v>297</v>
+      </c>
+      <c r="D15" s="136">
+        <v>10.000000000000002</v>
+      </c>
+      <c r="E15" s="136">
+        <v>0.24999671274622132</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416C8E38-3B77-4A74-A10C-2B5B49E38902}">
   <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -11942,7 +13813,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D83977B3-D0D2-4DB8-ACAA-07FCA3AB95F4}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -12218,7 +14089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18366C5-FFA6-46D0-9617-B8FE446A0FFB}">
   <dimension ref="A1:V12"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -12544,246 +14415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr codeName="Sheet1">
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="47.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.6875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="B7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3">
-        <v>5</v>
-      </c>
-      <c r="C8" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5">
-        <v>150</v>
-      </c>
-      <c r="C10" s="5">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5">
-        <v>300</v>
-      </c>
-      <c r="C11" s="5">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6">
-        <f>B11-(B10+SUMPRODUCT($B$3:$B$4,B8:B9))</f>
-        <v>80</v>
-      </c>
-      <c r="C12" s="6">
-        <f>C11-(C10+SUMPRODUCT($B$3:$B$4,C8:C9))</f>
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="B15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="4">
-        <v>560</v>
-      </c>
-      <c r="C16" s="4">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="B17" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3">
-        <v>600</v>
-      </c>
-      <c r="C18" s="3">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21">
-        <f>SUMPRODUCT(B16:C16,B8:C8)</f>
-        <v>10000</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="D21" s="3">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22">
-        <f>SUMPRODUCT(B16:C16,B9:C9)</f>
-        <v>2960</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="D22" s="3">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="B25" s="6">
-        <f>B12*B16</f>
-        <v>44800</v>
-      </c>
-      <c r="C25" s="6">
-        <f>C12*C16</f>
-        <v>154800</v>
-      </c>
-      <c r="D25" s="7">
-        <f>SUM(B25:C25)</f>
-        <v>199600</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="D26">
-        <f>SUMPRODUCT(B12:C12,B16:C16)</f>
-        <v>199600</v>
-      </c>
-      <c r="E26" t="s">
-        <v>474</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="1" gridLines="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:I48"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -13584,7 +15216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -14718,7 +16350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -15543,7 +17175,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:AY39"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -17355,7 +18987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:W27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -18319,12 +19951,12 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -18561,7 +20193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -19062,7 +20694,58 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F823F1C-5A45-43E5-A048-56060299D179}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="134"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="134" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1" s="134" t="s">
+        <v>609</v>
+      </c>
+      <c r="C1" s="134" t="s">
+        <v>608</v>
+      </c>
+      <c r="D1" s="134" t="s">
+        <v>607</v>
+      </c>
+      <c r="E1" s="134" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="135">
+        <v>2.5</v>
+      </c>
+      <c r="B2" s="134">
+        <f>(10-A2)</f>
+        <v>7.5</v>
+      </c>
+      <c r="C2" s="134">
+        <f>B2*A2</f>
+        <v>18.75</v>
+      </c>
+      <c r="D2" s="134">
+        <f>5 *A2</f>
+        <v>12.5</v>
+      </c>
+      <c r="E2" s="134">
+        <f>C2-D2</f>
+        <v>6.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -19145,7 +20828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -19806,7 +21489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E329189-507B-492C-B892-EA89AEC44AA6}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -19836,7 +21519,6 @@
       <c r="D2" s="52">
         <v>-4.3636363636363633</v>
       </c>
-      <c r="E2" s="134"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
@@ -19930,283 +21612,12 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03746BD-BE34-41ED-A93B-E2B7AB36F190}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="47.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.6875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="B7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3">
-        <v>5</v>
-      </c>
-      <c r="C8" s="3">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5">
-        <v>150</v>
-      </c>
-      <c r="C10" s="5">
-        <v>225</v>
-      </c>
-      <c r="D10">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5">
-        <v>300</v>
-      </c>
-      <c r="C11" s="5">
-        <v>450</v>
-      </c>
-      <c r="D11">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6">
-        <f>B11-(B10+SUMPRODUCT($B$3:$B$4,B8:B9))</f>
-        <v>80</v>
-      </c>
-      <c r="C12" s="6">
-        <f t="shared" ref="C12" si="0">C11-(C10+SUMPRODUCT($B$3:$B$4,C8:C9))</f>
-        <v>129</v>
-      </c>
-      <c r="D12" s="6">
-        <f>D11-(D10+SUMPRODUCT($B$3:$B$4,D8:D9))</f>
-        <v>152</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="B15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="4">
-        <v>514.28571428571433</v>
-      </c>
-      <c r="C16" s="4">
-        <v>1200</v>
-      </c>
-      <c r="D16" s="2">
-        <v>28.571428571428569</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="B17" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3">
-        <v>600</v>
-      </c>
-      <c r="C18" s="3">
-        <v>1200</v>
-      </c>
-      <c r="D18" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21">
-        <f>SUMPRODUCT(B16:D16,B8:D8)</f>
-        <v>10000.000000000002</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="D21" s="3">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22">
-        <f>SUMPRODUCT(B16:D16,B9:D9)</f>
-        <v>3000</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="D22" s="3">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="B25" s="6">
-        <f>B12*B16</f>
-        <v>41142.857142857145</v>
-      </c>
-      <c r="C25" s="6">
-        <f>C12*C16</f>
-        <v>154800</v>
-      </c>
-      <c r="D25" s="7">
-        <f>SUM(B25:C25)</f>
-        <v>195942.85714285716</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="D26">
-        <f>SUMPRODUCT(B12:D12,B16:D16)</f>
-        <v>200285.71428571429</v>
-      </c>
-      <c r="E26" t="s">
-        <v>474</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="1" gridLines="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -20768,7 +22179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EAD1EC8-752F-43D6-B790-5A15DDCDB8C8}">
   <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -20973,7 +22384,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60333241-7CED-4A17-BDC1-56C6BD21859E}">
   <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -21353,7 +22764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63314198-B56A-4E6A-9111-45ED4BF145FD}">
   <dimension ref="A2:J21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -21672,7 +23083,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC3221A-5E02-4AAB-87CE-F72249FF67DB}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -21806,7 +23217,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A71A95-F527-448F-A238-508D8B187D7B}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -21972,6 +23383,736 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5094E085-F6DB-4A3E-8201-010CC9E37480}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="2.3125" customWidth="1"/>
+    <col min="2" max="2" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.6875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="13.9" thickBot="1">
+      <c r="A6" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" s="99"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99" t="s">
+        <v>480</v>
+      </c>
+      <c r="E7" s="99" t="s">
+        <v>482</v>
+      </c>
+      <c r="F7" s="99" t="s">
+        <v>483</v>
+      </c>
+      <c r="G7" s="99" t="s">
+        <v>485</v>
+      </c>
+      <c r="H7" s="99" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="13.9" thickBot="1">
+      <c r="B8" s="100" t="s">
+        <v>478</v>
+      </c>
+      <c r="C8" s="100" t="s">
+        <v>479</v>
+      </c>
+      <c r="D8" s="100" t="s">
+        <v>481</v>
+      </c>
+      <c r="E8" s="100" t="s">
+        <v>294</v>
+      </c>
+      <c r="F8" s="100" t="s">
+        <v>484</v>
+      </c>
+      <c r="G8" s="100" t="s">
+        <v>486</v>
+      </c>
+      <c r="H8" s="100" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="97" t="s">
+        <v>493</v>
+      </c>
+      <c r="C9" s="97" t="s">
+        <v>494</v>
+      </c>
+      <c r="D9" s="97">
+        <v>560</v>
+      </c>
+      <c r="E9" s="97">
+        <v>0</v>
+      </c>
+      <c r="F9" s="97">
+        <v>80</v>
+      </c>
+      <c r="G9" s="97">
+        <v>27.499999999999986</v>
+      </c>
+      <c r="H9" s="97">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="13.9" thickBot="1">
+      <c r="B10" s="98" t="s">
+        <v>495</v>
+      </c>
+      <c r="C10" s="98" t="s">
+        <v>496</v>
+      </c>
+      <c r="D10" s="98">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="98">
+        <v>32.999999999999986</v>
+      </c>
+      <c r="F10" s="98">
+        <v>129</v>
+      </c>
+      <c r="G10" s="98">
+        <v>1E+30</v>
+      </c>
+      <c r="H10" s="98">
+        <v>32.999999999999986</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="13.9" thickBot="1">
+      <c r="A12" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13" s="99"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99" t="s">
+        <v>480</v>
+      </c>
+      <c r="E13" s="99" t="s">
+        <v>489</v>
+      </c>
+      <c r="F13" s="99" t="s">
+        <v>491</v>
+      </c>
+      <c r="G13" s="99" t="s">
+        <v>485</v>
+      </c>
+      <c r="H13" s="99" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="13.9" thickBot="1">
+      <c r="B14" s="100" t="s">
+        <v>478</v>
+      </c>
+      <c r="C14" s="100" t="s">
+        <v>479</v>
+      </c>
+      <c r="D14" s="100" t="s">
+        <v>481</v>
+      </c>
+      <c r="E14" s="100" t="s">
+        <v>490</v>
+      </c>
+      <c r="F14" s="100" t="s">
+        <v>492</v>
+      </c>
+      <c r="G14" s="100" t="s">
+        <v>486</v>
+      </c>
+      <c r="H14" s="100" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="B15" s="97" t="s">
+        <v>497</v>
+      </c>
+      <c r="C15" s="97" t="s">
+        <v>498</v>
+      </c>
+      <c r="D15" s="97">
+        <v>10000</v>
+      </c>
+      <c r="E15" s="97">
+        <v>16</v>
+      </c>
+      <c r="F15" s="97">
+        <v>10000</v>
+      </c>
+      <c r="G15" s="97">
+        <v>200</v>
+      </c>
+      <c r="H15" s="97">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="13.9" thickBot="1">
+      <c r="B16" s="98" t="s">
+        <v>499</v>
+      </c>
+      <c r="C16" s="98" t="s">
+        <v>500</v>
+      </c>
+      <c r="D16" s="98">
+        <v>2960</v>
+      </c>
+      <c r="E16" s="98">
+        <v>0</v>
+      </c>
+      <c r="F16" s="98">
+        <v>3000</v>
+      </c>
+      <c r="G16" s="98">
+        <v>1E+30</v>
+      </c>
+      <c r="H16" s="98">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Sheet1">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="47.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.6875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5">
+        <v>150</v>
+      </c>
+      <c r="C10" s="5">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5">
+        <v>300</v>
+      </c>
+      <c r="C11" s="5">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6">
+        <f>B11-(B10+SUMPRODUCT($B$3:$B$4,B8:B9))</f>
+        <v>80</v>
+      </c>
+      <c r="C12" s="6">
+        <f>C11-(C10+SUMPRODUCT($B$3:$B$4,C8:C9))</f>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="4">
+        <v>560</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="B17" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>600</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21">
+        <f>SUMPRODUCT(B16:C16,B8:C8)</f>
+        <v>10000</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D21" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22">
+        <f>SUMPRODUCT(B16:C16,B9:C9)</f>
+        <v>2960</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D22" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="B25" s="6">
+        <f>B12*B16</f>
+        <v>44800</v>
+      </c>
+      <c r="C25" s="6">
+        <f>C12*C16</f>
+        <v>154800</v>
+      </c>
+      <c r="D25" s="7">
+        <f>SUM(B25:C25)</f>
+        <v>199600</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="D26">
+        <f>SUMPRODUCT(B12:C12,B16:C16)</f>
+        <v>199600</v>
+      </c>
+      <c r="E26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03746BD-BE34-41ED-A93B-E2B7AB36F190}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="47.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.6875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5">
+        <v>150</v>
+      </c>
+      <c r="C10" s="5">
+        <v>225</v>
+      </c>
+      <c r="D10">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5">
+        <v>300</v>
+      </c>
+      <c r="C11" s="5">
+        <v>450</v>
+      </c>
+      <c r="D11">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6">
+        <f>B11-(B10+SUMPRODUCT($B$3:$B$4,B8:B9))</f>
+        <v>80</v>
+      </c>
+      <c r="C12" s="6">
+        <f t="shared" ref="C12" si="0">C11-(C10+SUMPRODUCT($B$3:$B$4,C8:C9))</f>
+        <v>129</v>
+      </c>
+      <c r="D12" s="6">
+        <f>D11-(D10+SUMPRODUCT($B$3:$B$4,D8:D9))</f>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="4">
+        <v>514.28571428571433</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D16" s="2">
+        <v>28.571428571428569</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="B17" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>600</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="D18" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21">
+        <f>SUMPRODUCT(B16:D16,B8:D8)</f>
+        <v>10000.000000000002</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D21" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22">
+        <f>SUMPRODUCT(B16:D16,B9:D9)</f>
+        <v>3000</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D22" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="B25" s="6">
+        <f>B12*B16</f>
+        <v>41142.857142857145</v>
+      </c>
+      <c r="C25" s="6">
+        <f>C12*C16</f>
+        <v>154800</v>
+      </c>
+      <c r="D25" s="7">
+        <f>SUM(B25:C25)</f>
+        <v>195942.85714285716</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="D26">
+        <f>SUMPRODUCT(B12:D12,B16:D16)</f>
+        <v>200285.71428571429</v>
+      </c>
+      <c r="E26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15067897-AD8C-4F2F-AE88-1E868F26AB92}">
   <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -22720,7 +24861,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -23350,7 +25491,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B78A46D7-F536-4A36-BE9C-0C9B37BB46E2}">
   <dimension ref="A2:L17"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -23716,1770 +25857,21 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="15.4375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="2.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" t="s">
-        <v>295</v>
-      </c>
-      <c r="I1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="B3" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B4">
-        <v>560</v>
-      </c>
-      <c r="C4">
-        <v>1200</v>
-      </c>
-      <c r="H4" t="s">
-        <v>308</v>
-      </c>
-      <c r="I4">
-        <v>16</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B5">
-        <v>80</v>
-      </c>
-      <c r="C5">
-        <v>129</v>
-      </c>
-      <c r="D5">
-        <f>SUMPRODUCT($B$4:$C$4,B5:C5)</f>
-        <v>199600</v>
-      </c>
-      <c r="H5" t="s">
-        <v>302</v>
-      </c>
-      <c r="I5">
-        <f t="array" ref="I5:L5">TRANSPOSE(F6:F9)</f>
-        <v>10000</v>
-      </c>
-      <c r="J5">
-        <v>3000</v>
-      </c>
-      <c r="K5">
-        <v>600</v>
-      </c>
-      <c r="L5">
-        <v>1200</v>
-      </c>
-      <c r="M5">
-        <f>SUMPRODUCT($I$4:$L$4,I5:L5)</f>
-        <v>199600</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" t="s">
-        <v>298</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <f t="shared" ref="D6:D9" si="0">SUMPRODUCT($B$4:$C$4,B6:C6)</f>
-        <v>10000</v>
-      </c>
-      <c r="E6" s="73" t="s">
-        <v>278</v>
-      </c>
-      <c r="F6">
-        <v>10000</v>
-      </c>
-      <c r="H6" t="s">
-        <v>298</v>
-      </c>
-      <c r="I6">
-        <f t="array" ref="I6:L7">TRANSPOSE(B6:C9)</f>
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <f>SUMPRODUCT($I$4:$L$4,I6:L6)</f>
-        <v>80</v>
-      </c>
-      <c r="N6" s="73" t="s">
-        <v>220</v>
-      </c>
-      <c r="O6">
-        <f t="array" ref="O6:O7">TRANSPOSE(B5:C5)</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>2960</v>
-      </c>
-      <c r="E7" s="73" t="s">
-        <v>278</v>
-      </c>
-      <c r="F7">
-        <v>3000</v>
-      </c>
-      <c r="H7" t="s">
-        <v>299</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <f>SUMPRODUCT($I$4:$L$4,I7:L7)</f>
-        <v>129</v>
-      </c>
-      <c r="N7" s="73" t="s">
-        <v>220</v>
-      </c>
-      <c r="O7">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" t="s">
-        <v>300</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>560</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>278</v>
-      </c>
-      <c r="F8">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" t="s">
-        <v>301</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>1200</v>
-      </c>
-      <c r="E9" s="73" t="s">
-        <v>278</v>
-      </c>
-      <c r="F9">
-        <v>1200</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="28.5625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="11" customWidth="1"/>
-    <col min="3" max="7" width="9.125" style="11"/>
-    <col min="8" max="8" width="12.875" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="243" width="9.125" style="11"/>
-    <col min="244" max="244" width="26.5625" style="11" customWidth="1"/>
-    <col min="245" max="245" width="13.125" style="11" customWidth="1"/>
-    <col min="246" max="250" width="9.125" style="11"/>
-    <col min="251" max="251" width="10.875" style="11" customWidth="1"/>
-    <col min="252" max="252" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="253" max="253" width="10.5625" style="11" customWidth="1"/>
-    <col min="254" max="254" width="10.875" style="11" customWidth="1"/>
-    <col min="255" max="499" width="9.125" style="11"/>
-    <col min="500" max="500" width="26.5625" style="11" customWidth="1"/>
-    <col min="501" max="501" width="13.125" style="11" customWidth="1"/>
-    <col min="502" max="506" width="9.125" style="11"/>
-    <col min="507" max="507" width="10.875" style="11" customWidth="1"/>
-    <col min="508" max="508" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="509" max="509" width="10.5625" style="11" customWidth="1"/>
-    <col min="510" max="510" width="10.875" style="11" customWidth="1"/>
-    <col min="511" max="755" width="9.125" style="11"/>
-    <col min="756" max="756" width="26.5625" style="11" customWidth="1"/>
-    <col min="757" max="757" width="13.125" style="11" customWidth="1"/>
-    <col min="758" max="762" width="9.125" style="11"/>
-    <col min="763" max="763" width="10.875" style="11" customWidth="1"/>
-    <col min="764" max="764" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="765" max="765" width="10.5625" style="11" customWidth="1"/>
-    <col min="766" max="766" width="10.875" style="11" customWidth="1"/>
-    <col min="767" max="1011" width="9.125" style="11"/>
-    <col min="1012" max="1012" width="26.5625" style="11" customWidth="1"/>
-    <col min="1013" max="1013" width="13.125" style="11" customWidth="1"/>
-    <col min="1014" max="1018" width="9.125" style="11"/>
-    <col min="1019" max="1019" width="10.875" style="11" customWidth="1"/>
-    <col min="1020" max="1020" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="1021" max="1021" width="10.5625" style="11" customWidth="1"/>
-    <col min="1022" max="1022" width="10.875" style="11" customWidth="1"/>
-    <col min="1023" max="1267" width="9.125" style="11"/>
-    <col min="1268" max="1268" width="26.5625" style="11" customWidth="1"/>
-    <col min="1269" max="1269" width="13.125" style="11" customWidth="1"/>
-    <col min="1270" max="1274" width="9.125" style="11"/>
-    <col min="1275" max="1275" width="10.875" style="11" customWidth="1"/>
-    <col min="1276" max="1276" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="1277" max="1277" width="10.5625" style="11" customWidth="1"/>
-    <col min="1278" max="1278" width="10.875" style="11" customWidth="1"/>
-    <col min="1279" max="1523" width="9.125" style="11"/>
-    <col min="1524" max="1524" width="26.5625" style="11" customWidth="1"/>
-    <col min="1525" max="1525" width="13.125" style="11" customWidth="1"/>
-    <col min="1526" max="1530" width="9.125" style="11"/>
-    <col min="1531" max="1531" width="10.875" style="11" customWidth="1"/>
-    <col min="1532" max="1532" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="1533" max="1533" width="10.5625" style="11" customWidth="1"/>
-    <col min="1534" max="1534" width="10.875" style="11" customWidth="1"/>
-    <col min="1535" max="1779" width="9.125" style="11"/>
-    <col min="1780" max="1780" width="26.5625" style="11" customWidth="1"/>
-    <col min="1781" max="1781" width="13.125" style="11" customWidth="1"/>
-    <col min="1782" max="1786" width="9.125" style="11"/>
-    <col min="1787" max="1787" width="10.875" style="11" customWidth="1"/>
-    <col min="1788" max="1788" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="1789" max="1789" width="10.5625" style="11" customWidth="1"/>
-    <col min="1790" max="1790" width="10.875" style="11" customWidth="1"/>
-    <col min="1791" max="2035" width="9.125" style="11"/>
-    <col min="2036" max="2036" width="26.5625" style="11" customWidth="1"/>
-    <col min="2037" max="2037" width="13.125" style="11" customWidth="1"/>
-    <col min="2038" max="2042" width="9.125" style="11"/>
-    <col min="2043" max="2043" width="10.875" style="11" customWidth="1"/>
-    <col min="2044" max="2044" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="2045" max="2045" width="10.5625" style="11" customWidth="1"/>
-    <col min="2046" max="2046" width="10.875" style="11" customWidth="1"/>
-    <col min="2047" max="2291" width="9.125" style="11"/>
-    <col min="2292" max="2292" width="26.5625" style="11" customWidth="1"/>
-    <col min="2293" max="2293" width="13.125" style="11" customWidth="1"/>
-    <col min="2294" max="2298" width="9.125" style="11"/>
-    <col min="2299" max="2299" width="10.875" style="11" customWidth="1"/>
-    <col min="2300" max="2300" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="2301" max="2301" width="10.5625" style="11" customWidth="1"/>
-    <col min="2302" max="2302" width="10.875" style="11" customWidth="1"/>
-    <col min="2303" max="2547" width="9.125" style="11"/>
-    <col min="2548" max="2548" width="26.5625" style="11" customWidth="1"/>
-    <col min="2549" max="2549" width="13.125" style="11" customWidth="1"/>
-    <col min="2550" max="2554" width="9.125" style="11"/>
-    <col min="2555" max="2555" width="10.875" style="11" customWidth="1"/>
-    <col min="2556" max="2556" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="2557" max="2557" width="10.5625" style="11" customWidth="1"/>
-    <col min="2558" max="2558" width="10.875" style="11" customWidth="1"/>
-    <col min="2559" max="2803" width="9.125" style="11"/>
-    <col min="2804" max="2804" width="26.5625" style="11" customWidth="1"/>
-    <col min="2805" max="2805" width="13.125" style="11" customWidth="1"/>
-    <col min="2806" max="2810" width="9.125" style="11"/>
-    <col min="2811" max="2811" width="10.875" style="11" customWidth="1"/>
-    <col min="2812" max="2812" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="2813" max="2813" width="10.5625" style="11" customWidth="1"/>
-    <col min="2814" max="2814" width="10.875" style="11" customWidth="1"/>
-    <col min="2815" max="3059" width="9.125" style="11"/>
-    <col min="3060" max="3060" width="26.5625" style="11" customWidth="1"/>
-    <col min="3061" max="3061" width="13.125" style="11" customWidth="1"/>
-    <col min="3062" max="3066" width="9.125" style="11"/>
-    <col min="3067" max="3067" width="10.875" style="11" customWidth="1"/>
-    <col min="3068" max="3068" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="3069" max="3069" width="10.5625" style="11" customWidth="1"/>
-    <col min="3070" max="3070" width="10.875" style="11" customWidth="1"/>
-    <col min="3071" max="3315" width="9.125" style="11"/>
-    <col min="3316" max="3316" width="26.5625" style="11" customWidth="1"/>
-    <col min="3317" max="3317" width="13.125" style="11" customWidth="1"/>
-    <col min="3318" max="3322" width="9.125" style="11"/>
-    <col min="3323" max="3323" width="10.875" style="11" customWidth="1"/>
-    <col min="3324" max="3324" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="3325" max="3325" width="10.5625" style="11" customWidth="1"/>
-    <col min="3326" max="3326" width="10.875" style="11" customWidth="1"/>
-    <col min="3327" max="3571" width="9.125" style="11"/>
-    <col min="3572" max="3572" width="26.5625" style="11" customWidth="1"/>
-    <col min="3573" max="3573" width="13.125" style="11" customWidth="1"/>
-    <col min="3574" max="3578" width="9.125" style="11"/>
-    <col min="3579" max="3579" width="10.875" style="11" customWidth="1"/>
-    <col min="3580" max="3580" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="3581" max="3581" width="10.5625" style="11" customWidth="1"/>
-    <col min="3582" max="3582" width="10.875" style="11" customWidth="1"/>
-    <col min="3583" max="3827" width="9.125" style="11"/>
-    <col min="3828" max="3828" width="26.5625" style="11" customWidth="1"/>
-    <col min="3829" max="3829" width="13.125" style="11" customWidth="1"/>
-    <col min="3830" max="3834" width="9.125" style="11"/>
-    <col min="3835" max="3835" width="10.875" style="11" customWidth="1"/>
-    <col min="3836" max="3836" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="3837" max="3837" width="10.5625" style="11" customWidth="1"/>
-    <col min="3838" max="3838" width="10.875" style="11" customWidth="1"/>
-    <col min="3839" max="4083" width="9.125" style="11"/>
-    <col min="4084" max="4084" width="26.5625" style="11" customWidth="1"/>
-    <col min="4085" max="4085" width="13.125" style="11" customWidth="1"/>
-    <col min="4086" max="4090" width="9.125" style="11"/>
-    <col min="4091" max="4091" width="10.875" style="11" customWidth="1"/>
-    <col min="4092" max="4092" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="4093" max="4093" width="10.5625" style="11" customWidth="1"/>
-    <col min="4094" max="4094" width="10.875" style="11" customWidth="1"/>
-    <col min="4095" max="4339" width="9.125" style="11"/>
-    <col min="4340" max="4340" width="26.5625" style="11" customWidth="1"/>
-    <col min="4341" max="4341" width="13.125" style="11" customWidth="1"/>
-    <col min="4342" max="4346" width="9.125" style="11"/>
-    <col min="4347" max="4347" width="10.875" style="11" customWidth="1"/>
-    <col min="4348" max="4348" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="4349" max="4349" width="10.5625" style="11" customWidth="1"/>
-    <col min="4350" max="4350" width="10.875" style="11" customWidth="1"/>
-    <col min="4351" max="4595" width="9.125" style="11"/>
-    <col min="4596" max="4596" width="26.5625" style="11" customWidth="1"/>
-    <col min="4597" max="4597" width="13.125" style="11" customWidth="1"/>
-    <col min="4598" max="4602" width="9.125" style="11"/>
-    <col min="4603" max="4603" width="10.875" style="11" customWidth="1"/>
-    <col min="4604" max="4604" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="4605" max="4605" width="10.5625" style="11" customWidth="1"/>
-    <col min="4606" max="4606" width="10.875" style="11" customWidth="1"/>
-    <col min="4607" max="4851" width="9.125" style="11"/>
-    <col min="4852" max="4852" width="26.5625" style="11" customWidth="1"/>
-    <col min="4853" max="4853" width="13.125" style="11" customWidth="1"/>
-    <col min="4854" max="4858" width="9.125" style="11"/>
-    <col min="4859" max="4859" width="10.875" style="11" customWidth="1"/>
-    <col min="4860" max="4860" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="4861" max="4861" width="10.5625" style="11" customWidth="1"/>
-    <col min="4862" max="4862" width="10.875" style="11" customWidth="1"/>
-    <col min="4863" max="5107" width="9.125" style="11"/>
-    <col min="5108" max="5108" width="26.5625" style="11" customWidth="1"/>
-    <col min="5109" max="5109" width="13.125" style="11" customWidth="1"/>
-    <col min="5110" max="5114" width="9.125" style="11"/>
-    <col min="5115" max="5115" width="10.875" style="11" customWidth="1"/>
-    <col min="5116" max="5116" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="5117" max="5117" width="10.5625" style="11" customWidth="1"/>
-    <col min="5118" max="5118" width="10.875" style="11" customWidth="1"/>
-    <col min="5119" max="5363" width="9.125" style="11"/>
-    <col min="5364" max="5364" width="26.5625" style="11" customWidth="1"/>
-    <col min="5365" max="5365" width="13.125" style="11" customWidth="1"/>
-    <col min="5366" max="5370" width="9.125" style="11"/>
-    <col min="5371" max="5371" width="10.875" style="11" customWidth="1"/>
-    <col min="5372" max="5372" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="5373" max="5373" width="10.5625" style="11" customWidth="1"/>
-    <col min="5374" max="5374" width="10.875" style="11" customWidth="1"/>
-    <col min="5375" max="5619" width="9.125" style="11"/>
-    <col min="5620" max="5620" width="26.5625" style="11" customWidth="1"/>
-    <col min="5621" max="5621" width="13.125" style="11" customWidth="1"/>
-    <col min="5622" max="5626" width="9.125" style="11"/>
-    <col min="5627" max="5627" width="10.875" style="11" customWidth="1"/>
-    <col min="5628" max="5628" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="5629" max="5629" width="10.5625" style="11" customWidth="1"/>
-    <col min="5630" max="5630" width="10.875" style="11" customWidth="1"/>
-    <col min="5631" max="5875" width="9.125" style="11"/>
-    <col min="5876" max="5876" width="26.5625" style="11" customWidth="1"/>
-    <col min="5877" max="5877" width="13.125" style="11" customWidth="1"/>
-    <col min="5878" max="5882" width="9.125" style="11"/>
-    <col min="5883" max="5883" width="10.875" style="11" customWidth="1"/>
-    <col min="5884" max="5884" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="5885" max="5885" width="10.5625" style="11" customWidth="1"/>
-    <col min="5886" max="5886" width="10.875" style="11" customWidth="1"/>
-    <col min="5887" max="6131" width="9.125" style="11"/>
-    <col min="6132" max="6132" width="26.5625" style="11" customWidth="1"/>
-    <col min="6133" max="6133" width="13.125" style="11" customWidth="1"/>
-    <col min="6134" max="6138" width="9.125" style="11"/>
-    <col min="6139" max="6139" width="10.875" style="11" customWidth="1"/>
-    <col min="6140" max="6140" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="6141" max="6141" width="10.5625" style="11" customWidth="1"/>
-    <col min="6142" max="6142" width="10.875" style="11" customWidth="1"/>
-    <col min="6143" max="6387" width="9.125" style="11"/>
-    <col min="6388" max="6388" width="26.5625" style="11" customWidth="1"/>
-    <col min="6389" max="6389" width="13.125" style="11" customWidth="1"/>
-    <col min="6390" max="6394" width="9.125" style="11"/>
-    <col min="6395" max="6395" width="10.875" style="11" customWidth="1"/>
-    <col min="6396" max="6396" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="6397" max="6397" width="10.5625" style="11" customWidth="1"/>
-    <col min="6398" max="6398" width="10.875" style="11" customWidth="1"/>
-    <col min="6399" max="6643" width="9.125" style="11"/>
-    <col min="6644" max="6644" width="26.5625" style="11" customWidth="1"/>
-    <col min="6645" max="6645" width="13.125" style="11" customWidth="1"/>
-    <col min="6646" max="6650" width="9.125" style="11"/>
-    <col min="6651" max="6651" width="10.875" style="11" customWidth="1"/>
-    <col min="6652" max="6652" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="6653" max="6653" width="10.5625" style="11" customWidth="1"/>
-    <col min="6654" max="6654" width="10.875" style="11" customWidth="1"/>
-    <col min="6655" max="6899" width="9.125" style="11"/>
-    <col min="6900" max="6900" width="26.5625" style="11" customWidth="1"/>
-    <col min="6901" max="6901" width="13.125" style="11" customWidth="1"/>
-    <col min="6902" max="6906" width="9.125" style="11"/>
-    <col min="6907" max="6907" width="10.875" style="11" customWidth="1"/>
-    <col min="6908" max="6908" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="6909" max="6909" width="10.5625" style="11" customWidth="1"/>
-    <col min="6910" max="6910" width="10.875" style="11" customWidth="1"/>
-    <col min="6911" max="7155" width="9.125" style="11"/>
-    <col min="7156" max="7156" width="26.5625" style="11" customWidth="1"/>
-    <col min="7157" max="7157" width="13.125" style="11" customWidth="1"/>
-    <col min="7158" max="7162" width="9.125" style="11"/>
-    <col min="7163" max="7163" width="10.875" style="11" customWidth="1"/>
-    <col min="7164" max="7164" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="7165" max="7165" width="10.5625" style="11" customWidth="1"/>
-    <col min="7166" max="7166" width="10.875" style="11" customWidth="1"/>
-    <col min="7167" max="7411" width="9.125" style="11"/>
-    <col min="7412" max="7412" width="26.5625" style="11" customWidth="1"/>
-    <col min="7413" max="7413" width="13.125" style="11" customWidth="1"/>
-    <col min="7414" max="7418" width="9.125" style="11"/>
-    <col min="7419" max="7419" width="10.875" style="11" customWidth="1"/>
-    <col min="7420" max="7420" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="7421" max="7421" width="10.5625" style="11" customWidth="1"/>
-    <col min="7422" max="7422" width="10.875" style="11" customWidth="1"/>
-    <col min="7423" max="7667" width="9.125" style="11"/>
-    <col min="7668" max="7668" width="26.5625" style="11" customWidth="1"/>
-    <col min="7669" max="7669" width="13.125" style="11" customWidth="1"/>
-    <col min="7670" max="7674" width="9.125" style="11"/>
-    <col min="7675" max="7675" width="10.875" style="11" customWidth="1"/>
-    <col min="7676" max="7676" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="7677" max="7677" width="10.5625" style="11" customWidth="1"/>
-    <col min="7678" max="7678" width="10.875" style="11" customWidth="1"/>
-    <col min="7679" max="7923" width="9.125" style="11"/>
-    <col min="7924" max="7924" width="26.5625" style="11" customWidth="1"/>
-    <col min="7925" max="7925" width="13.125" style="11" customWidth="1"/>
-    <col min="7926" max="7930" width="9.125" style="11"/>
-    <col min="7931" max="7931" width="10.875" style="11" customWidth="1"/>
-    <col min="7932" max="7932" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="7933" max="7933" width="10.5625" style="11" customWidth="1"/>
-    <col min="7934" max="7934" width="10.875" style="11" customWidth="1"/>
-    <col min="7935" max="8179" width="9.125" style="11"/>
-    <col min="8180" max="8180" width="26.5625" style="11" customWidth="1"/>
-    <col min="8181" max="8181" width="13.125" style="11" customWidth="1"/>
-    <col min="8182" max="8186" width="9.125" style="11"/>
-    <col min="8187" max="8187" width="10.875" style="11" customWidth="1"/>
-    <col min="8188" max="8188" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="8189" max="8189" width="10.5625" style="11" customWidth="1"/>
-    <col min="8190" max="8190" width="10.875" style="11" customWidth="1"/>
-    <col min="8191" max="8435" width="9.125" style="11"/>
-    <col min="8436" max="8436" width="26.5625" style="11" customWidth="1"/>
-    <col min="8437" max="8437" width="13.125" style="11" customWidth="1"/>
-    <col min="8438" max="8442" width="9.125" style="11"/>
-    <col min="8443" max="8443" width="10.875" style="11" customWidth="1"/>
-    <col min="8444" max="8444" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="8445" max="8445" width="10.5625" style="11" customWidth="1"/>
-    <col min="8446" max="8446" width="10.875" style="11" customWidth="1"/>
-    <col min="8447" max="8691" width="9.125" style="11"/>
-    <col min="8692" max="8692" width="26.5625" style="11" customWidth="1"/>
-    <col min="8693" max="8693" width="13.125" style="11" customWidth="1"/>
-    <col min="8694" max="8698" width="9.125" style="11"/>
-    <col min="8699" max="8699" width="10.875" style="11" customWidth="1"/>
-    <col min="8700" max="8700" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="8701" max="8701" width="10.5625" style="11" customWidth="1"/>
-    <col min="8702" max="8702" width="10.875" style="11" customWidth="1"/>
-    <col min="8703" max="8947" width="9.125" style="11"/>
-    <col min="8948" max="8948" width="26.5625" style="11" customWidth="1"/>
-    <col min="8949" max="8949" width="13.125" style="11" customWidth="1"/>
-    <col min="8950" max="8954" width="9.125" style="11"/>
-    <col min="8955" max="8955" width="10.875" style="11" customWidth="1"/>
-    <col min="8956" max="8956" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="8957" max="8957" width="10.5625" style="11" customWidth="1"/>
-    <col min="8958" max="8958" width="10.875" style="11" customWidth="1"/>
-    <col min="8959" max="9203" width="9.125" style="11"/>
-    <col min="9204" max="9204" width="26.5625" style="11" customWidth="1"/>
-    <col min="9205" max="9205" width="13.125" style="11" customWidth="1"/>
-    <col min="9206" max="9210" width="9.125" style="11"/>
-    <col min="9211" max="9211" width="10.875" style="11" customWidth="1"/>
-    <col min="9212" max="9212" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="9213" max="9213" width="10.5625" style="11" customWidth="1"/>
-    <col min="9214" max="9214" width="10.875" style="11" customWidth="1"/>
-    <col min="9215" max="9459" width="9.125" style="11"/>
-    <col min="9460" max="9460" width="26.5625" style="11" customWidth="1"/>
-    <col min="9461" max="9461" width="13.125" style="11" customWidth="1"/>
-    <col min="9462" max="9466" width="9.125" style="11"/>
-    <col min="9467" max="9467" width="10.875" style="11" customWidth="1"/>
-    <col min="9468" max="9468" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="9469" max="9469" width="10.5625" style="11" customWidth="1"/>
-    <col min="9470" max="9470" width="10.875" style="11" customWidth="1"/>
-    <col min="9471" max="9715" width="9.125" style="11"/>
-    <col min="9716" max="9716" width="26.5625" style="11" customWidth="1"/>
-    <col min="9717" max="9717" width="13.125" style="11" customWidth="1"/>
-    <col min="9718" max="9722" width="9.125" style="11"/>
-    <col min="9723" max="9723" width="10.875" style="11" customWidth="1"/>
-    <col min="9724" max="9724" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="9725" max="9725" width="10.5625" style="11" customWidth="1"/>
-    <col min="9726" max="9726" width="10.875" style="11" customWidth="1"/>
-    <col min="9727" max="9971" width="9.125" style="11"/>
-    <col min="9972" max="9972" width="26.5625" style="11" customWidth="1"/>
-    <col min="9973" max="9973" width="13.125" style="11" customWidth="1"/>
-    <col min="9974" max="9978" width="9.125" style="11"/>
-    <col min="9979" max="9979" width="10.875" style="11" customWidth="1"/>
-    <col min="9980" max="9980" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="9981" max="9981" width="10.5625" style="11" customWidth="1"/>
-    <col min="9982" max="9982" width="10.875" style="11" customWidth="1"/>
-    <col min="9983" max="10227" width="9.125" style="11"/>
-    <col min="10228" max="10228" width="26.5625" style="11" customWidth="1"/>
-    <col min="10229" max="10229" width="13.125" style="11" customWidth="1"/>
-    <col min="10230" max="10234" width="9.125" style="11"/>
-    <col min="10235" max="10235" width="10.875" style="11" customWidth="1"/>
-    <col min="10236" max="10236" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="10237" max="10237" width="10.5625" style="11" customWidth="1"/>
-    <col min="10238" max="10238" width="10.875" style="11" customWidth="1"/>
-    <col min="10239" max="10483" width="9.125" style="11"/>
-    <col min="10484" max="10484" width="26.5625" style="11" customWidth="1"/>
-    <col min="10485" max="10485" width="13.125" style="11" customWidth="1"/>
-    <col min="10486" max="10490" width="9.125" style="11"/>
-    <col min="10491" max="10491" width="10.875" style="11" customWidth="1"/>
-    <col min="10492" max="10492" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="10493" max="10493" width="10.5625" style="11" customWidth="1"/>
-    <col min="10494" max="10494" width="10.875" style="11" customWidth="1"/>
-    <col min="10495" max="10739" width="9.125" style="11"/>
-    <col min="10740" max="10740" width="26.5625" style="11" customWidth="1"/>
-    <col min="10741" max="10741" width="13.125" style="11" customWidth="1"/>
-    <col min="10742" max="10746" width="9.125" style="11"/>
-    <col min="10747" max="10747" width="10.875" style="11" customWidth="1"/>
-    <col min="10748" max="10748" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="10749" max="10749" width="10.5625" style="11" customWidth="1"/>
-    <col min="10750" max="10750" width="10.875" style="11" customWidth="1"/>
-    <col min="10751" max="10995" width="9.125" style="11"/>
-    <col min="10996" max="10996" width="26.5625" style="11" customWidth="1"/>
-    <col min="10997" max="10997" width="13.125" style="11" customWidth="1"/>
-    <col min="10998" max="11002" width="9.125" style="11"/>
-    <col min="11003" max="11003" width="10.875" style="11" customWidth="1"/>
-    <col min="11004" max="11004" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="11005" max="11005" width="10.5625" style="11" customWidth="1"/>
-    <col min="11006" max="11006" width="10.875" style="11" customWidth="1"/>
-    <col min="11007" max="11251" width="9.125" style="11"/>
-    <col min="11252" max="11252" width="26.5625" style="11" customWidth="1"/>
-    <col min="11253" max="11253" width="13.125" style="11" customWidth="1"/>
-    <col min="11254" max="11258" width="9.125" style="11"/>
-    <col min="11259" max="11259" width="10.875" style="11" customWidth="1"/>
-    <col min="11260" max="11260" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="11261" max="11261" width="10.5625" style="11" customWidth="1"/>
-    <col min="11262" max="11262" width="10.875" style="11" customWidth="1"/>
-    <col min="11263" max="11507" width="9.125" style="11"/>
-    <col min="11508" max="11508" width="26.5625" style="11" customWidth="1"/>
-    <col min="11509" max="11509" width="13.125" style="11" customWidth="1"/>
-    <col min="11510" max="11514" width="9.125" style="11"/>
-    <col min="11515" max="11515" width="10.875" style="11" customWidth="1"/>
-    <col min="11516" max="11516" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="11517" max="11517" width="10.5625" style="11" customWidth="1"/>
-    <col min="11518" max="11518" width="10.875" style="11" customWidth="1"/>
-    <col min="11519" max="11763" width="9.125" style="11"/>
-    <col min="11764" max="11764" width="26.5625" style="11" customWidth="1"/>
-    <col min="11765" max="11765" width="13.125" style="11" customWidth="1"/>
-    <col min="11766" max="11770" width="9.125" style="11"/>
-    <col min="11771" max="11771" width="10.875" style="11" customWidth="1"/>
-    <col min="11772" max="11772" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="11773" max="11773" width="10.5625" style="11" customWidth="1"/>
-    <col min="11774" max="11774" width="10.875" style="11" customWidth="1"/>
-    <col min="11775" max="12019" width="9.125" style="11"/>
-    <col min="12020" max="12020" width="26.5625" style="11" customWidth="1"/>
-    <col min="12021" max="12021" width="13.125" style="11" customWidth="1"/>
-    <col min="12022" max="12026" width="9.125" style="11"/>
-    <col min="12027" max="12027" width="10.875" style="11" customWidth="1"/>
-    <col min="12028" max="12028" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="12029" max="12029" width="10.5625" style="11" customWidth="1"/>
-    <col min="12030" max="12030" width="10.875" style="11" customWidth="1"/>
-    <col min="12031" max="12275" width="9.125" style="11"/>
-    <col min="12276" max="12276" width="26.5625" style="11" customWidth="1"/>
-    <col min="12277" max="12277" width="13.125" style="11" customWidth="1"/>
-    <col min="12278" max="12282" width="9.125" style="11"/>
-    <col min="12283" max="12283" width="10.875" style="11" customWidth="1"/>
-    <col min="12284" max="12284" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="12285" max="12285" width="10.5625" style="11" customWidth="1"/>
-    <col min="12286" max="12286" width="10.875" style="11" customWidth="1"/>
-    <col min="12287" max="12531" width="9.125" style="11"/>
-    <col min="12532" max="12532" width="26.5625" style="11" customWidth="1"/>
-    <col min="12533" max="12533" width="13.125" style="11" customWidth="1"/>
-    <col min="12534" max="12538" width="9.125" style="11"/>
-    <col min="12539" max="12539" width="10.875" style="11" customWidth="1"/>
-    <col min="12540" max="12540" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="12541" max="12541" width="10.5625" style="11" customWidth="1"/>
-    <col min="12542" max="12542" width="10.875" style="11" customWidth="1"/>
-    <col min="12543" max="12787" width="9.125" style="11"/>
-    <col min="12788" max="12788" width="26.5625" style="11" customWidth="1"/>
-    <col min="12789" max="12789" width="13.125" style="11" customWidth="1"/>
-    <col min="12790" max="12794" width="9.125" style="11"/>
-    <col min="12795" max="12795" width="10.875" style="11" customWidth="1"/>
-    <col min="12796" max="12796" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="12797" max="12797" width="10.5625" style="11" customWidth="1"/>
-    <col min="12798" max="12798" width="10.875" style="11" customWidth="1"/>
-    <col min="12799" max="13043" width="9.125" style="11"/>
-    <col min="13044" max="13044" width="26.5625" style="11" customWidth="1"/>
-    <col min="13045" max="13045" width="13.125" style="11" customWidth="1"/>
-    <col min="13046" max="13050" width="9.125" style="11"/>
-    <col min="13051" max="13051" width="10.875" style="11" customWidth="1"/>
-    <col min="13052" max="13052" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="13053" max="13053" width="10.5625" style="11" customWidth="1"/>
-    <col min="13054" max="13054" width="10.875" style="11" customWidth="1"/>
-    <col min="13055" max="13299" width="9.125" style="11"/>
-    <col min="13300" max="13300" width="26.5625" style="11" customWidth="1"/>
-    <col min="13301" max="13301" width="13.125" style="11" customWidth="1"/>
-    <col min="13302" max="13306" width="9.125" style="11"/>
-    <col min="13307" max="13307" width="10.875" style="11" customWidth="1"/>
-    <col min="13308" max="13308" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="13309" max="13309" width="10.5625" style="11" customWidth="1"/>
-    <col min="13310" max="13310" width="10.875" style="11" customWidth="1"/>
-    <col min="13311" max="13555" width="9.125" style="11"/>
-    <col min="13556" max="13556" width="26.5625" style="11" customWidth="1"/>
-    <col min="13557" max="13557" width="13.125" style="11" customWidth="1"/>
-    <col min="13558" max="13562" width="9.125" style="11"/>
-    <col min="13563" max="13563" width="10.875" style="11" customWidth="1"/>
-    <col min="13564" max="13564" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="13565" max="13565" width="10.5625" style="11" customWidth="1"/>
-    <col min="13566" max="13566" width="10.875" style="11" customWidth="1"/>
-    <col min="13567" max="13811" width="9.125" style="11"/>
-    <col min="13812" max="13812" width="26.5625" style="11" customWidth="1"/>
-    <col min="13813" max="13813" width="13.125" style="11" customWidth="1"/>
-    <col min="13814" max="13818" width="9.125" style="11"/>
-    <col min="13819" max="13819" width="10.875" style="11" customWidth="1"/>
-    <col min="13820" max="13820" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="13821" max="13821" width="10.5625" style="11" customWidth="1"/>
-    <col min="13822" max="13822" width="10.875" style="11" customWidth="1"/>
-    <col min="13823" max="14067" width="9.125" style="11"/>
-    <col min="14068" max="14068" width="26.5625" style="11" customWidth="1"/>
-    <col min="14069" max="14069" width="13.125" style="11" customWidth="1"/>
-    <col min="14070" max="14074" width="9.125" style="11"/>
-    <col min="14075" max="14075" width="10.875" style="11" customWidth="1"/>
-    <col min="14076" max="14076" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="14077" max="14077" width="10.5625" style="11" customWidth="1"/>
-    <col min="14078" max="14078" width="10.875" style="11" customWidth="1"/>
-    <col min="14079" max="14323" width="9.125" style="11"/>
-    <col min="14324" max="14324" width="26.5625" style="11" customWidth="1"/>
-    <col min="14325" max="14325" width="13.125" style="11" customWidth="1"/>
-    <col min="14326" max="14330" width="9.125" style="11"/>
-    <col min="14331" max="14331" width="10.875" style="11" customWidth="1"/>
-    <col min="14332" max="14332" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="14333" max="14333" width="10.5625" style="11" customWidth="1"/>
-    <col min="14334" max="14334" width="10.875" style="11" customWidth="1"/>
-    <col min="14335" max="14579" width="9.125" style="11"/>
-    <col min="14580" max="14580" width="26.5625" style="11" customWidth="1"/>
-    <col min="14581" max="14581" width="13.125" style="11" customWidth="1"/>
-    <col min="14582" max="14586" width="9.125" style="11"/>
-    <col min="14587" max="14587" width="10.875" style="11" customWidth="1"/>
-    <col min="14588" max="14588" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="14589" max="14589" width="10.5625" style="11" customWidth="1"/>
-    <col min="14590" max="14590" width="10.875" style="11" customWidth="1"/>
-    <col min="14591" max="14835" width="9.125" style="11"/>
-    <col min="14836" max="14836" width="26.5625" style="11" customWidth="1"/>
-    <col min="14837" max="14837" width="13.125" style="11" customWidth="1"/>
-    <col min="14838" max="14842" width="9.125" style="11"/>
-    <col min="14843" max="14843" width="10.875" style="11" customWidth="1"/>
-    <col min="14844" max="14844" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="14845" max="14845" width="10.5625" style="11" customWidth="1"/>
-    <col min="14846" max="14846" width="10.875" style="11" customWidth="1"/>
-    <col min="14847" max="15091" width="9.125" style="11"/>
-    <col min="15092" max="15092" width="26.5625" style="11" customWidth="1"/>
-    <col min="15093" max="15093" width="13.125" style="11" customWidth="1"/>
-    <col min="15094" max="15098" width="9.125" style="11"/>
-    <col min="15099" max="15099" width="10.875" style="11" customWidth="1"/>
-    <col min="15100" max="15100" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="15101" max="15101" width="10.5625" style="11" customWidth="1"/>
-    <col min="15102" max="15102" width="10.875" style="11" customWidth="1"/>
-    <col min="15103" max="15347" width="9.125" style="11"/>
-    <col min="15348" max="15348" width="26.5625" style="11" customWidth="1"/>
-    <col min="15349" max="15349" width="13.125" style="11" customWidth="1"/>
-    <col min="15350" max="15354" width="9.125" style="11"/>
-    <col min="15355" max="15355" width="10.875" style="11" customWidth="1"/>
-    <col min="15356" max="15356" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="15357" max="15357" width="10.5625" style="11" customWidth="1"/>
-    <col min="15358" max="15358" width="10.875" style="11" customWidth="1"/>
-    <col min="15359" max="15603" width="9.125" style="11"/>
-    <col min="15604" max="15604" width="26.5625" style="11" customWidth="1"/>
-    <col min="15605" max="15605" width="13.125" style="11" customWidth="1"/>
-    <col min="15606" max="15610" width="9.125" style="11"/>
-    <col min="15611" max="15611" width="10.875" style="11" customWidth="1"/>
-    <col min="15612" max="15612" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="15613" max="15613" width="10.5625" style="11" customWidth="1"/>
-    <col min="15614" max="15614" width="10.875" style="11" customWidth="1"/>
-    <col min="15615" max="15859" width="9.125" style="11"/>
-    <col min="15860" max="15860" width="26.5625" style="11" customWidth="1"/>
-    <col min="15861" max="15861" width="13.125" style="11" customWidth="1"/>
-    <col min="15862" max="15866" width="9.125" style="11"/>
-    <col min="15867" max="15867" width="10.875" style="11" customWidth="1"/>
-    <col min="15868" max="15868" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="15869" max="15869" width="10.5625" style="11" customWidth="1"/>
-    <col min="15870" max="15870" width="10.875" style="11" customWidth="1"/>
-    <col min="15871" max="16115" width="9.125" style="11"/>
-    <col min="16116" max="16116" width="26.5625" style="11" customWidth="1"/>
-    <col min="16117" max="16117" width="13.125" style="11" customWidth="1"/>
-    <col min="16118" max="16122" width="9.125" style="11"/>
-    <col min="16123" max="16123" width="10.875" style="11" customWidth="1"/>
-    <col min="16124" max="16124" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="16125" max="16125" width="10.5625" style="11" customWidth="1"/>
-    <col min="16126" max="16126" width="10.875" style="11" customWidth="1"/>
-    <col min="16127" max="16384" width="9.125" style="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="12"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="13">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="14">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="15">
-        <v>1</v>
-      </c>
-      <c r="C7" s="15">
-        <v>2</v>
-      </c>
-      <c r="D7" s="15">
-        <v>3</v>
-      </c>
-      <c r="E7" s="15">
-        <v>4</v>
-      </c>
-      <c r="F7" s="15">
-        <v>5</v>
-      </c>
-      <c r="G7" s="15">
-        <v>6</v>
-      </c>
-      <c r="H7" s="16"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="18">
-        <v>12.5</v>
-      </c>
-      <c r="C8" s="18">
-        <v>12.55</v>
-      </c>
-      <c r="D8" s="18">
-        <v>12.7</v>
-      </c>
-      <c r="E8" s="18">
-        <v>12.8</v>
-      </c>
-      <c r="F8" s="18">
-        <v>12.85</v>
-      </c>
-      <c r="G8" s="18">
-        <v>12.95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="17" t="s">
-        <v>573</v>
-      </c>
-      <c r="B9" s="19">
-        <f>B8*0.05</f>
-        <v>0.625</v>
-      </c>
-      <c r="C9" s="19">
-        <f t="shared" ref="C9:G9" si="0">C8*0.05</f>
-        <v>0.62750000000000006</v>
-      </c>
-      <c r="D9" s="19">
-        <f t="shared" si="0"/>
-        <v>0.63500000000000001</v>
-      </c>
-      <c r="E9" s="19">
-        <f t="shared" si="0"/>
-        <v>0.64000000000000012</v>
-      </c>
-      <c r="F9" s="19">
-        <f t="shared" si="0"/>
-        <v>0.64250000000000007</v>
-      </c>
-      <c r="G9" s="19">
-        <f t="shared" si="0"/>
-        <v>0.64749999999999996</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="15">
-        <v>1</v>
-      </c>
-      <c r="C11" s="15">
-        <v>2</v>
-      </c>
-      <c r="D11" s="15">
-        <v>3</v>
-      </c>
-      <c r="E11" s="15">
-        <v>4</v>
-      </c>
-      <c r="F11" s="15">
-        <v>5</v>
-      </c>
-      <c r="G11" s="15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="47">
-        <v>5000</v>
-      </c>
-      <c r="C12" s="47">
-        <v>20000</v>
-      </c>
-      <c r="D12" s="47">
-        <v>30000</v>
-      </c>
-      <c r="E12" s="47">
-        <v>30000</v>
-      </c>
-      <c r="F12" s="47">
-        <v>25000</v>
-      </c>
-      <c r="G12" s="47">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="B13" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="13">
-        <v>30000</v>
-      </c>
-      <c r="C14" s="13">
-        <v>30000</v>
-      </c>
-      <c r="D14" s="13">
-        <v>30000</v>
-      </c>
-      <c r="E14" s="13">
-        <v>30000</v>
-      </c>
-      <c r="F14" s="13">
-        <v>30000</v>
-      </c>
-      <c r="G14" s="13">
-        <v>30000</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="13">
-        <v>10000</v>
-      </c>
-      <c r="C18" s="13">
-        <v>15000</v>
-      </c>
-      <c r="D18" s="13">
-        <v>30000</v>
-      </c>
-      <c r="E18" s="13">
-        <v>35000</v>
-      </c>
-      <c r="F18" s="13">
-        <v>25000</v>
-      </c>
-      <c r="G18" s="13">
-        <v>10000</v>
-      </c>
-      <c r="H18" s="11">
-        <f>SUM(B18:G18)</f>
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="24">
-        <f>$B$4 + B12- B18</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="24">
-        <f>B20 + C12- C18</f>
-        <v>5000</v>
-      </c>
-      <c r="D20" s="24">
-        <f t="shared" ref="D20:F20" si="1">C20 + D12- D18</f>
-        <v>5000</v>
-      </c>
-      <c r="E20" s="24">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="24">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="24">
-        <f>F20 + G12- G18</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="23" t="s">
-        <v>572</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="B21" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="13">
-        <v>10000</v>
-      </c>
-      <c r="C22" s="13">
-        <v>10000</v>
-      </c>
-      <c r="D22" s="13">
-        <v>10000</v>
-      </c>
-      <c r="E22" s="13">
-        <v>10000</v>
-      </c>
-      <c r="F22" s="13">
-        <v>10000</v>
-      </c>
-      <c r="G22" s="13">
-        <v>10000</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="20"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="19"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="15">
-        <v>1</v>
-      </c>
-      <c r="C25" s="15">
-        <v>2</v>
-      </c>
-      <c r="D25" s="15">
-        <v>3</v>
-      </c>
-      <c r="E25" s="15">
-        <v>4</v>
-      </c>
-      <c r="F25" s="15">
-        <v>5</v>
-      </c>
-      <c r="G25" s="15">
-        <v>6</v>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="H26" s="105">
-        <f>SUMPRODUCT(B9:G9, B20:G20)</f>
-        <v>6312.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="11" t="s">
-        <v>574</v>
-      </c>
-      <c r="H27" s="105">
-        <f>SUMPRODUCT(B8:G8,B12:G12)</f>
-        <v>1529250</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="H28" s="106">
-        <f>SUM(H26:H27)</f>
-        <v>1535562.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="B3:K24"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="1.4375" customWidth="1"/>
-    <col min="2" max="2" width="7.4375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.125" customWidth="1"/>
-    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:11">
-      <c r="G3" t="s">
-        <v>327</v>
-      </c>
-      <c r="H3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="C4" t="s">
-        <v>326</v>
-      </c>
-      <c r="E4" t="s">
-        <v>294</v>
-      </c>
-      <c r="G4" t="s">
-        <v>326</v>
-      </c>
-      <c r="H4" t="s">
-        <v>330</v>
-      </c>
-      <c r="I4" t="s">
-        <v>332</v>
-      </c>
-      <c r="J4" t="s">
-        <v>333</v>
-      </c>
-      <c r="K4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11">
-      <c r="B5" t="s">
-        <v>309</v>
-      </c>
-      <c r="C5" t="s">
-        <v>310</v>
-      </c>
-      <c r="D5" t="s">
-        <v>311</v>
-      </c>
-      <c r="E5" t="s">
-        <v>310</v>
-      </c>
-      <c r="F5" t="s">
-        <v>311</v>
-      </c>
-      <c r="G5" t="s">
-        <v>328</v>
-      </c>
-      <c r="H5" t="s">
-        <v>331</v>
-      </c>
-      <c r="I5" t="s">
-        <v>326</v>
-      </c>
-      <c r="J5" t="s">
-        <v>328</v>
-      </c>
-      <c r="K5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11">
-      <c r="B6" t="s">
-        <v>312</v>
-      </c>
-      <c r="C6" s="75">
-        <v>2</v>
-      </c>
-      <c r="D6" s="75">
-        <v>1</v>
-      </c>
-      <c r="E6" s="76">
-        <v>180000</v>
-      </c>
-      <c r="F6" s="76">
-        <v>280000</v>
-      </c>
-      <c r="G6">
-        <f>C6-D6</f>
-        <v>1</v>
-      </c>
-      <c r="H6" s="74">
-        <f>(F6-E6)/G6</f>
-        <v>100000</v>
-      </c>
-      <c r="I6" s="52">
-        <v>0</v>
-      </c>
-      <c r="J6" s="52">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <f>I6+C6-J6</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11">
-      <c r="B7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C7" s="75">
-        <v>4</v>
-      </c>
-      <c r="D7" s="75">
-        <v>2</v>
-      </c>
-      <c r="E7" s="76">
-        <v>320000</v>
-      </c>
-      <c r="F7" s="76">
-        <v>420000</v>
-      </c>
-      <c r="G7">
-        <f t="shared" ref="G7:G19" si="0">C7-D7</f>
-        <v>2</v>
-      </c>
-      <c r="H7" s="74">
-        <f t="shared" ref="H7:H19" si="1">(F7-E7)/G7</f>
-        <v>50000</v>
-      </c>
-      <c r="I7" s="52">
-        <v>2</v>
-      </c>
-      <c r="J7" s="52">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <f t="shared" ref="K7:K19" si="2">I7+C7-J7</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11">
-      <c r="B8" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="75">
-        <v>10</v>
-      </c>
-      <c r="D8" s="75">
-        <v>7</v>
-      </c>
-      <c r="E8" s="76">
-        <v>620000</v>
-      </c>
-      <c r="F8" s="76">
-        <v>860000</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H8" s="74">
-        <f t="shared" si="1"/>
-        <v>80000</v>
-      </c>
-      <c r="I8" s="52">
-        <v>6</v>
-      </c>
-      <c r="J8" s="52">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11">
-      <c r="B9" t="s">
-        <v>315</v>
-      </c>
-      <c r="C9" s="75">
-        <v>6</v>
-      </c>
-      <c r="D9" s="75">
-        <v>4</v>
-      </c>
-      <c r="E9" s="76">
-        <v>260000</v>
-      </c>
-      <c r="F9" s="76">
-        <v>340000</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H9" s="74">
-        <f t="shared" si="1"/>
-        <v>40000</v>
-      </c>
-      <c r="I9" s="52">
-        <v>16</v>
-      </c>
-      <c r="J9" s="52">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10" t="s">
-        <v>316</v>
-      </c>
-      <c r="C10" s="75">
-        <v>4</v>
-      </c>
-      <c r="D10" s="75">
-        <v>3</v>
-      </c>
-      <c r="E10" s="76">
-        <v>410000</v>
-      </c>
-      <c r="F10" s="76">
-        <v>570000</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H10" s="74">
-        <f t="shared" si="1"/>
-        <v>160000</v>
-      </c>
-      <c r="I10" s="52">
-        <v>16</v>
-      </c>
-      <c r="J10" s="52">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="B11" t="s">
-        <v>317</v>
-      </c>
-      <c r="C11" s="75">
-        <v>5</v>
-      </c>
-      <c r="D11" s="75">
-        <v>3</v>
-      </c>
-      <c r="E11" s="76">
-        <v>180000</v>
-      </c>
-      <c r="F11" s="76">
-        <v>260000</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H11" s="74">
-        <f t="shared" si="1"/>
-        <v>40000</v>
-      </c>
-      <c r="I11" s="52">
-        <v>20</v>
-      </c>
-      <c r="J11" s="52">
-        <v>2</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="2"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11">
-      <c r="B12" t="s">
-        <v>318</v>
-      </c>
-      <c r="C12" s="75">
-        <v>7</v>
-      </c>
-      <c r="D12" s="75">
-        <v>4</v>
-      </c>
-      <c r="E12" s="76">
-        <v>900000</v>
-      </c>
-      <c r="F12" s="76">
-        <v>1020000</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H12" s="74">
-        <f t="shared" si="1"/>
-        <v>40000</v>
-      </c>
-      <c r="I12" s="52">
-        <v>22</v>
-      </c>
-      <c r="J12" s="52">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="2"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11">
-      <c r="B13" t="s">
-        <v>319</v>
-      </c>
-      <c r="C13" s="75">
-        <v>9</v>
-      </c>
-      <c r="D13" s="75">
-        <v>6</v>
-      </c>
-      <c r="E13" s="76">
-        <v>200000</v>
-      </c>
-      <c r="F13" s="76">
-        <v>380000</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H13" s="74">
-        <f t="shared" si="1"/>
-        <v>60000</v>
-      </c>
-      <c r="I13" s="52">
-        <v>29</v>
-      </c>
-      <c r="J13" s="52">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="2"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11">
-      <c r="B14" t="s">
-        <v>320</v>
-      </c>
-      <c r="C14" s="75">
-        <v>7</v>
-      </c>
-      <c r="D14" s="75">
-        <v>5</v>
-      </c>
-      <c r="E14" s="76">
-        <v>210000</v>
-      </c>
-      <c r="F14" s="76">
-        <v>270000</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H14" s="74">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-      <c r="I14" s="52">
-        <v>16</v>
-      </c>
-      <c r="J14" s="52">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="2"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11">
-      <c r="B15" t="s">
-        <v>321</v>
-      </c>
-      <c r="C15" s="75">
-        <v>8</v>
-      </c>
-      <c r="D15" s="75">
-        <v>6</v>
-      </c>
-      <c r="E15" s="76">
-        <v>430000</v>
-      </c>
-      <c r="F15" s="76">
-        <v>490000</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H15" s="74">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-      <c r="I15" s="52">
-        <v>23</v>
-      </c>
-      <c r="J15" s="52">
-        <v>2</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="2"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11">
-      <c r="B16" t="s">
-        <v>322</v>
-      </c>
-      <c r="C16" s="75">
-        <v>4</v>
-      </c>
-      <c r="D16" s="75">
-        <v>3</v>
-      </c>
-      <c r="E16" s="76">
-        <v>160000</v>
-      </c>
-      <c r="F16" s="76">
-        <v>200000</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H16" s="74">
-        <f t="shared" si="1"/>
-        <v>40000</v>
-      </c>
-      <c r="I16" s="52">
-        <v>30</v>
-      </c>
-      <c r="J16" s="52">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="2"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11">
-      <c r="B17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C17" s="75">
-        <v>5</v>
-      </c>
-      <c r="D17" s="75">
-        <v>3</v>
-      </c>
-      <c r="E17" s="76">
-        <v>250000</v>
-      </c>
-      <c r="F17" s="76">
-        <v>350000</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H17" s="74">
-        <f t="shared" si="1"/>
-        <v>50000</v>
-      </c>
-      <c r="I17" s="52">
-        <v>29</v>
-      </c>
-      <c r="J17" s="52">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="2"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11">
-      <c r="B18" t="s">
-        <v>324</v>
-      </c>
-      <c r="C18" s="75">
-        <v>2</v>
-      </c>
-      <c r="D18" s="75">
-        <v>1</v>
-      </c>
-      <c r="E18" s="76">
-        <v>100000</v>
-      </c>
-      <c r="F18" s="76">
-        <v>200000</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H18" s="74">
-        <f t="shared" si="1"/>
-        <v>100000</v>
-      </c>
-      <c r="I18" s="52">
-        <v>38</v>
-      </c>
-      <c r="J18" s="52">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11">
-      <c r="B19" t="s">
-        <v>325</v>
-      </c>
-      <c r="C19" s="75">
-        <v>6</v>
-      </c>
-      <c r="D19" s="75">
-        <v>3</v>
-      </c>
-      <c r="E19" s="76">
-        <v>330000</v>
-      </c>
-      <c r="F19" s="76">
-        <v>510000</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H19" s="74">
-        <f t="shared" si="1"/>
-        <v>60000</v>
-      </c>
-      <c r="I19" s="52">
-        <v>34</v>
-      </c>
-      <c r="J19" s="52">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11">
-      <c r="K21" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11">
-      <c r="H22" t="s">
-        <v>335</v>
-      </c>
-      <c r="I22" s="52">
-        <v>40</v>
-      </c>
-      <c r="J22" s="78" t="s">
-        <v>278</v>
-      </c>
-      <c r="K22">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" ht="13.9" thickBot="1"/>
-    <row r="24" spans="2:11" ht="13.9" thickBot="1">
-      <c r="H24" t="s">
-        <v>92</v>
-      </c>
-      <c r="I24" s="77">
-        <f>SUM(E6:E19)+SUMPRODUCT(H6:H19,J6:J19)</f>
-        <v>4690000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005D21A9346877C94FBE0D2EF98A54C8DF" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="751dbf132c53fd3bc3488d6191458457">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -25593,15 +25985,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -25609,6 +25992,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50238CAA-F670-4524-9BD2-2D2D3FDCD917}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633191C1-D2B6-4B97-A701-AFB02492B9AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -25624,14 +26015,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50238CAA-F670-4524-9BD2-2D2D3FDCD917}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE94C634-99D9-44FC-B2A2-D1462FE9BD9E}">
   <ds:schemaRefs>

--- a/class_excel/data-files-optimization.xlsx
+++ b/class_excel/data-files-optimization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuna\Documents\GitHub\DADS7102\class_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D510CBA6-8ABE-406F-B988-C45F43F6368E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F36AFE4-3AE0-4202-AE77-8CB15A7135C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="954" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="954" firstSheet="14" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Advertising " sheetId="43" r:id="rId1"/>
@@ -953,6 +953,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -5270,9 +5273,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5310,9 +5313,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5345,9 +5348,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5380,9 +5400,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -12617,7 +12654,7 @@
         <v>3</v>
       </c>
       <c r="I11" s="11">
-        <f t="shared" si="1"/>
+        <f>SUMIF($A$8:$A$33,H11,$D$8:$D$33)</f>
         <v>280</v>
       </c>
       <c r="J11" s="11">
@@ -25863,6 +25900,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005D21A9346877C94FBE0D2EF98A54C8DF" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="751dbf132c53fd3bc3488d6191458457">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -25976,15 +26022,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -25992,6 +26029,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50238CAA-F670-4524-9BD2-2D2D3FDCD917}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633191C1-D2B6-4B97-A701-AFB02492B9AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26007,14 +26052,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50238CAA-F670-4524-9BD2-2D2D3FDCD917}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE94C634-99D9-44FC-B2A2-D1462FE9BD9E}">
   <ds:schemaRefs>

--- a/class_excel/data-files-optimization.xlsx
+++ b/class_excel/data-files-optimization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F36AFE4-3AE0-4202-AE77-8CB15A7135C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFFBA84-E961-4888-981A-999CAC82E9F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="954" firstSheet="15" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="954" firstSheet="24" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Advertising " sheetId="43" r:id="rId1"/>
@@ -3760,7 +3760,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3984,6 +3984,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="192" fontId="0" fillId="8" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Comma" xfId="6" builtinId="3"/>
@@ -23360,7 +23361,7 @@
       <c r="C7" s="142"/>
       <c r="D7" s="142"/>
       <c r="E7" s="142"/>
-      <c r="F7" s="91">
+      <c r="F7" s="143">
         <f>SUMPRODUCT(F2:F5,E2:E5)</f>
         <v>5456.5396875145925</v>
       </c>
@@ -25863,6 +25864,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005D21A9346877C94FBE0D2EF98A54C8DF" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="751dbf132c53fd3bc3488d6191458457">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -25976,15 +25986,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -25992,6 +25993,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50238CAA-F670-4524-9BD2-2D2D3FDCD917}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633191C1-D2B6-4B97-A701-AFB02492B9AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26007,14 +26016,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50238CAA-F670-4524-9BD2-2D2D3FDCD917}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE94C634-99D9-44FC-B2A2-D1462FE9BD9E}">
   <ds:schemaRefs>

--- a/class_excel/data-files-optimization.xlsx
+++ b/class_excel/data-files-optimization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B06A44-8632-4E1D-ADE5-ABA11AB2F8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA819BC-CC35-491A-B1B7-73DBFE6F65DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4425" yWindow="4185" windowWidth="21600" windowHeight="11295" tabRatio="954" firstSheet="19" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4425" yWindow="4185" windowWidth="21600" windowHeight="11295" tabRatio="954" firstSheet="22" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Advertising " sheetId="43" r:id="rId1"/>
@@ -105,7 +105,7 @@
     <definedName name="solver_adj" localSheetId="20" hidden="1">set_covering_model!$B$2:$G$2</definedName>
     <definedName name="solver_adj" localSheetId="34" hidden="1">'SVM1'!$B$2:$D$2,'SVM1'!$F$2</definedName>
     <definedName name="solver_adj" localSheetId="13" hidden="1">Transport1!$C$13:$F$15</definedName>
-    <definedName name="solver_adj" localSheetId="26" hidden="1">WorkerScheduling!$N$3:$T$3</definedName>
+    <definedName name="solver_adj" localSheetId="26" hidden="1">WorkerScheduling!#REF!</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="14" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="23" hidden="1">0.0001</definedName>
@@ -242,7 +242,7 @@
     <definedName name="solver_lhs1" localSheetId="18" hidden="1">RedBrandLogistics!$D$8:$D$33</definedName>
     <definedName name="solver_lhs1" localSheetId="20" hidden="1">set_covering_model!$B$2:$G$2</definedName>
     <definedName name="solver_lhs1" localSheetId="13" hidden="1">Transport1!$C$16:$F$16</definedName>
-    <definedName name="solver_lhs1" localSheetId="26" hidden="1">WorkerScheduling!$N$3:$T$3</definedName>
+    <definedName name="solver_lhs1" localSheetId="26" hidden="1">WorkerScheduling!#REF!</definedName>
     <definedName name="solver_lhs10" localSheetId="11" hidden="1">project!$I$18</definedName>
     <definedName name="solver_lhs11" localSheetId="11" hidden="1">project!$I$13</definedName>
     <definedName name="solver_lhs12" localSheetId="11" hidden="1">project!$I$15</definedName>
@@ -269,7 +269,7 @@
     <definedName name="solver_lhs2" localSheetId="18" hidden="1">RedBrandLogistics!$K$15:$K$16</definedName>
     <definedName name="solver_lhs2" localSheetId="20" hidden="1">set_covering_model!$H$3:$H$8</definedName>
     <definedName name="solver_lhs2" localSheetId="13" hidden="1">Transport1!$G$13:$G$15</definedName>
-    <definedName name="solver_lhs2" localSheetId="26" hidden="1">WorkerScheduling!$U$5:$U$11</definedName>
+    <definedName name="solver_lhs2" localSheetId="26" hidden="1">WorkerScheduling!#REF!</definedName>
     <definedName name="solver_lhs20" localSheetId="11" hidden="1">project!$I$9</definedName>
     <definedName name="solver_lhs21" localSheetId="11" hidden="1">project!$I$10</definedName>
     <definedName name="solver_lhs22" localSheetId="11" hidden="1">project!$I$11</definedName>
@@ -509,7 +509,7 @@
     <definedName name="solver_opt" localSheetId="20" hidden="1">set_covering_model!$C$10</definedName>
     <definedName name="solver_opt" localSheetId="34" hidden="1">'SVM1'!$F$2</definedName>
     <definedName name="solver_opt" localSheetId="13" hidden="1">Transport1!$B$21</definedName>
-    <definedName name="solver_opt" localSheetId="26" hidden="1">WorkerScheduling!$U$4</definedName>
+    <definedName name="solver_opt" localSheetId="26" hidden="1">WorkerScheduling!#REF!</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="14" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="23" hidden="1">0.000001</definedName>
@@ -679,7 +679,7 @@
     <definedName name="solver_rhs2" localSheetId="18" hidden="1">RedBrandLogistics!$M$15:$M$16</definedName>
     <definedName name="solver_rhs2" localSheetId="20" hidden="1">set_covering_model!$J$3:$J$8</definedName>
     <definedName name="solver_rhs2" localSheetId="13" hidden="1">Transport1!$I$13:$I$15</definedName>
-    <definedName name="solver_rhs2" localSheetId="26" hidden="1">WorkerScheduling!$W$5:$W$11</definedName>
+    <definedName name="solver_rhs2" localSheetId="26" hidden="1">WorkerScheduling!#REF!</definedName>
     <definedName name="solver_rhs20" localSheetId="11" hidden="1">CFinish</definedName>
     <definedName name="solver_rhs21" localSheetId="11" hidden="1">CFinish</definedName>
     <definedName name="solver_rhs22" localSheetId="11" hidden="1">EFinish</definedName>
@@ -19424,7 +19424,7 @@
         <v>1</v>
       </c>
       <c r="U5" s="11">
-        <f t="shared" ref="U5:U11" si="0">SUMPRODUCT(N5:T5,$N$3:$T$3)</f>
+        <f>SUMPRODUCT(N5:T5,$N$3:$T$3)</f>
         <v>17</v>
       </c>
       <c r="V5" s="96" t="s">
@@ -19466,7 +19466,7 @@
         <v>1</v>
       </c>
       <c r="U6" s="11">
-        <f t="shared" si="0"/>
+        <f>SUMPRODUCT(N6:T6,$N$3:$T$3)</f>
         <v>13</v>
       </c>
       <c r="V6" s="96" t="s">
@@ -19508,7 +19508,7 @@
         <v>1</v>
       </c>
       <c r="U7" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="U7:U11" si="0">SUMPRODUCT(N7:T7,$N$3:$T$3)</f>
         <v>16</v>
       </c>
       <c r="V7" s="96" t="s">
@@ -19550,7 +19550,7 @@
         <v>1</v>
       </c>
       <c r="U8" s="11">
-        <f t="shared" si="0"/>
+        <f>SUMPRODUCT(N8:T8,$N$3:$T$3)</f>
         <v>20</v>
       </c>
       <c r="V8" s="96" t="s">
@@ -19790,7 +19790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:23">
       <c r="A17" s="22" t="s">
         <v>208</v>
       </c>
@@ -19816,7 +19816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:23">
       <c r="A18" s="22" t="s">
         <v>209</v>
       </c>
@@ -19842,7 +19842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:23">
       <c r="A19" s="22" t="s">
         <v>210</v>
       </c>
@@ -19868,7 +19868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:23">
       <c r="A20" s="22" t="s">
         <v>211</v>
       </c>
@@ -19894,7 +19894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:23">
       <c r="B21" s="28"/>
       <c r="C21" s="28"/>
       <c r="D21" s="28"/>
@@ -19903,7 +19903,7 @@
       <c r="G21" s="28"/>
       <c r="H21" s="28"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:23">
       <c r="A22" s="25" t="s">
         <v>212</v>
       </c>
@@ -19915,7 +19915,7 @@
       <c r="G22" s="28"/>
       <c r="H22" s="28"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:23">
       <c r="A23" s="22" t="s">
         <v>213</v>
       </c>
@@ -19948,7 +19948,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:23">
       <c r="A24" s="22" t="s">
         <v>214</v>
       </c>
@@ -19974,12 +19974,36 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="25" spans="1:23">
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+      <c r="R25"/>
+      <c r="S25"/>
+      <c r="T25"/>
+      <c r="U25"/>
+      <c r="V25"/>
+      <c r="W25"/>
+    </row>
+    <row r="26" spans="1:23">
       <c r="A26" s="25" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="M26" s="8"/>
+      <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+      <c r="S26"/>
+      <c r="T26"/>
+      <c r="U26"/>
+      <c r="V26"/>
+      <c r="W26"/>
+    </row>
+    <row r="27" spans="1:23">
       <c r="A27" s="22" t="s">
         <v>215</v>
       </c>
@@ -25901,15 +25925,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005D21A9346877C94FBE0D2EF98A54C8DF" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="751dbf132c53fd3bc3488d6191458457">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -26023,6 +26038,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -26030,14 +26054,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50238CAA-F670-4524-9BD2-2D2D3FDCD917}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633191C1-D2B6-4B97-A701-AFB02492B9AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26053,6 +26069,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50238CAA-F670-4524-9BD2-2D2D3FDCD917}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE94C634-99D9-44FC-B2A2-D1462FE9BD9E}">
   <ds:schemaRefs>

--- a/class_excel/data-files-optimization.xlsx
+++ b/class_excel/data-files-optimization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA819BC-CC35-491A-B1B7-73DBFE6F65DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D51028-0B40-4280-B074-7525BEAE2B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4425" yWindow="4185" windowWidth="21600" windowHeight="11295" tabRatio="954" firstSheet="22" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="954" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Advertising " sheetId="43" r:id="rId1"/>
@@ -25925,6 +25925,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005D21A9346877C94FBE0D2EF98A54C8DF" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="751dbf132c53fd3bc3488d6191458457">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -26038,15 +26047,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -26054,6 +26054,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50238CAA-F670-4524-9BD2-2D2D3FDCD917}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633191C1-D2B6-4B97-A701-AFB02492B9AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26069,14 +26077,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50238CAA-F670-4524-9BD2-2D2D3FDCD917}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE94C634-99D9-44FC-B2A2-D1462FE9BD9E}">
   <ds:schemaRefs>
